--- a/precios_objetivo.xlsx
+++ b/precios_objetivo.xlsx
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>jue 01/10 10:00</t>
+          <t>vie 02/10 08:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -499,36 +499,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Azerbaijan vs Liechtenstein</t>
+          <t>Kazakhstan vs Moldova</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.18</v>
+        <v>1.97</v>
       </c>
       <c r="E2" t="n">
-        <v>9.300000000000001</v>
+        <v>3.67</v>
       </c>
       <c r="F2" t="n">
-        <v>40.82</v>
+        <v>4.99</v>
       </c>
       <c r="G2" t="n">
-        <v>1.16</v>
+        <v>1.93</v>
       </c>
       <c r="H2" t="n">
-        <v>9.119999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="I2" t="n">
-        <v>40.02</v>
+        <v>4.9</v>
       </c>
       <c r="J2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>jue 01/10 12:45</t>
+          <t>vie 02/10 10:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -538,40 +538,36 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wales vs Norway</t>
+          <t>Cyprus vs Armenia</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>7.82</v>
+        <v>2.43</v>
       </c>
       <c r="E3" t="n">
-        <v>5.42</v>
+        <v>3.59</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5</v>
+        <v>3.44</v>
       </c>
       <c r="G3" t="n">
-        <v>7.66</v>
+        <v>2.38</v>
       </c>
       <c r="H3" t="n">
-        <v>5.31</v>
+        <v>3.52</v>
       </c>
       <c r="I3" t="n">
-        <v>1.47</v>
+        <v>3.37</v>
       </c>
       <c r="J3" t="n">
-        <v>16</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>6.95, 5.00, 1.44</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>jue 01/10 12:45</t>
+          <t>vie 02/10 10:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -581,36 +577,36 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Republic of Ireland vs Austria</t>
+          <t>Latvia vs Montenegro</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3.88</v>
+        <v>5.26</v>
       </c>
       <c r="E4" t="n">
-        <v>3.53</v>
+        <v>3.82</v>
       </c>
       <c r="F4" t="n">
-        <v>2.28</v>
+        <v>1.89</v>
       </c>
       <c r="G4" t="n">
-        <v>3.8</v>
+        <v>5.16</v>
       </c>
       <c r="H4" t="n">
-        <v>3.46</v>
+        <v>3.75</v>
       </c>
       <c r="I4" t="n">
-        <v>2.23</v>
+        <v>1.85</v>
       </c>
       <c r="J4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>jue 01/10 12:45</t>
+          <t>vie 02/10 12:45</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -620,40 +616,36 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Denmark vs Portugal</t>
+          <t>Hungary vs Georgia</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3.8</v>
+        <v>2.25</v>
       </c>
       <c r="E5" t="n">
-        <v>3.97</v>
+        <v>3.62</v>
       </c>
       <c r="F5" t="n">
-        <v>2.15</v>
+        <v>3.85</v>
       </c>
       <c r="G5" t="n">
-        <v>3.73</v>
+        <v>2.2</v>
       </c>
       <c r="H5" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="I5" t="n">
-        <v>2.1</v>
+        <v>3.78</v>
       </c>
       <c r="J5" t="n">
-        <v>16</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>3.61, 3.69, 2.06</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>jue 01/10 12:45</t>
+          <t>vie 02/10 12:45</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -663,40 +655,40 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Germany vs Serbia</t>
+          <t>Belgium vs Turkey</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.25</v>
+        <v>1.58</v>
       </c>
       <c r="E6" t="n">
-        <v>7.91</v>
+        <v>5.22</v>
       </c>
       <c r="F6" t="n">
-        <v>17.72</v>
+        <v>6.39</v>
       </c>
       <c r="G6" t="n">
-        <v>1.23</v>
+        <v>1.55</v>
       </c>
       <c r="H6" t="n">
-        <v>7.76</v>
+        <v>5.12</v>
       </c>
       <c r="I6" t="n">
-        <v>17.38</v>
+        <v>6.26</v>
       </c>
       <c r="J6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1.21, 6.73, 14.54</t>
+          <t>1.53, 4.85, 5.67</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>jue 01/10 12:45</t>
+          <t>vie 02/10 12:45</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -706,36 +698,36 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Malta vs Gibraltar</t>
+          <t>Bosnia &amp; Herzegovina vs Sweden</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.35</v>
+        <v>2.85</v>
       </c>
       <c r="E7" t="n">
-        <v>5.66</v>
+        <v>3.88</v>
       </c>
       <c r="F7" t="n">
-        <v>15.38</v>
+        <v>2.69</v>
       </c>
       <c r="G7" t="n">
-        <v>1.33</v>
+        <v>2.8</v>
       </c>
       <c r="H7" t="n">
-        <v>5.55</v>
+        <v>3.8</v>
       </c>
       <c r="I7" t="n">
-        <v>15.08</v>
+        <v>2.64</v>
       </c>
       <c r="J7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>jue 01/10 12:45</t>
+          <t>vie 02/10 12:45</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -745,40 +737,36 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Greece vs Netherlands</t>
+          <t>Faroe Islands vs Slovakia</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3.77</v>
+        <v>7.23</v>
       </c>
       <c r="E8" t="n">
-        <v>3.91</v>
+        <v>4.18</v>
       </c>
       <c r="F8" t="n">
-        <v>2.18</v>
+        <v>1.66</v>
       </c>
       <c r="G8" t="n">
-        <v>3.7</v>
+        <v>7.08</v>
       </c>
       <c r="H8" t="n">
-        <v>3.83</v>
+        <v>4.1</v>
       </c>
       <c r="I8" t="n">
-        <v>2.13</v>
+        <v>1.63</v>
       </c>
       <c r="J8" t="n">
-        <v>16</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>3.51, 3.67, 2.10</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>jue 01/10 12:45</t>
+          <t>vie 02/10 12:45</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -788,79 +776,79 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Israel vs Kosovo</t>
+          <t>France vs Italy</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3.42</v>
+        <v>1.51</v>
       </c>
       <c r="E9" t="n">
-        <v>3.68</v>
+        <v>5.58</v>
       </c>
       <c r="F9" t="n">
-        <v>2.4</v>
+        <v>7.11</v>
       </c>
       <c r="G9" t="n">
-        <v>3.35</v>
+        <v>1.48</v>
       </c>
       <c r="H9" t="n">
-        <v>3.61</v>
+        <v>5.47</v>
       </c>
       <c r="I9" t="n">
-        <v>2.35</v>
+        <v>6.97</v>
       </c>
       <c r="J9" t="n">
-        <v>14</v>
-      </c>
-      <c r="K9" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>1.45, 5.20, 6.38</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>jue 01/10 19:30</t>
+          <t>vie 02/10 12:45</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Nations League</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Seattle Sounders FC vs Sporting Kansas City</t>
+          <t>Ukraine vs Northern Ireland</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.57</v>
+        <v>2.02</v>
       </c>
       <c r="E10" t="n">
-        <v>5.41</v>
+        <v>3.59</v>
       </c>
       <c r="F10" t="n">
-        <v>6.23</v>
+        <v>4.86</v>
       </c>
       <c r="G10" t="n">
-        <v>1.54</v>
+        <v>1.98</v>
       </c>
       <c r="H10" t="n">
-        <v>5.3</v>
+        <v>3.52</v>
       </c>
       <c r="I10" t="n">
-        <v>6.11</v>
+        <v>4.77</v>
       </c>
       <c r="J10" t="n">
-        <v>21</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>1.52, 4.99, 5.35</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>vie 02/10 08:00</t>
+          <t>vie 02/10 12:45</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -870,26 +858,26 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan vs Moldova</t>
+          <t>Poland vs Romania</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.81</v>
+        <v>1.6</v>
       </c>
       <c r="E11" t="n">
-        <v>3.97</v>
+        <v>4.76</v>
       </c>
       <c r="F11" t="n">
-        <v>5.71</v>
+        <v>6.97</v>
       </c>
       <c r="G11" t="n">
-        <v>1.77</v>
+        <v>1.56</v>
       </c>
       <c r="H11" t="n">
-        <v>3.89</v>
+        <v>4.67</v>
       </c>
       <c r="I11" t="n">
-        <v>5.6</v>
+        <v>6.83</v>
       </c>
       <c r="J11" t="n">
         <v>13</v>
@@ -899,163 +887,179 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>vie 02/10 10:00</t>
+          <t>vie 02/10 16:15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nations League</t>
+          <t>Argentina Primera</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cyprus vs Armenia</t>
+          <t>Independiente vs Instituto de Córdoba</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2.43</v>
+        <v>2.53</v>
       </c>
       <c r="E12" t="n">
-        <v>3.58</v>
+        <v>3.32</v>
       </c>
       <c r="F12" t="n">
-        <v>3.44</v>
+        <v>3.52</v>
       </c>
       <c r="G12" t="n">
-        <v>2.39</v>
+        <v>2.48</v>
       </c>
       <c r="H12" t="n">
-        <v>3.51</v>
+        <v>3.26</v>
       </c>
       <c r="I12" t="n">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="J12" t="n">
-        <v>14</v>
-      </c>
-      <c r="K12" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2.43, 3.12, 3.26</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>vie 02/10 10:00</t>
+          <t>vie 02/10 17:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nations League</t>
+          <t>Brasil Serie A</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia vs Montenegro</t>
+          <t>Sao Paulo vs Santos</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.99</v>
+        <v>2.18</v>
       </c>
       <c r="E13" t="n">
-        <v>3.8</v>
+        <v>3.69</v>
       </c>
       <c r="F13" t="n">
-        <v>1.93</v>
+        <v>4</v>
       </c>
       <c r="G13" t="n">
-        <v>4.89</v>
+        <v>2.13</v>
       </c>
       <c r="H13" t="n">
-        <v>3.73</v>
+        <v>3.62</v>
       </c>
       <c r="I13" t="n">
-        <v>1.9</v>
+        <v>3.92</v>
       </c>
       <c r="J13" t="n">
-        <v>14</v>
-      </c>
-      <c r="K13" t="inlineStr"/>
+        <v>21</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2.09, 3.43, 3.71</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>vie 02/10 12:45</t>
+          <t>vie 02/10 18:30</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nations League</t>
+          <t>Argentina Primera</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ukraine vs Northern Ireland</t>
+          <t>Independiente Rivadavia vs Gimnasia La Plata</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="E14" t="n">
-        <v>3.63</v>
+        <v>3.74</v>
       </c>
       <c r="F14" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="I14" t="n">
         <v>4.75</v>
       </c>
-      <c r="G14" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="H14" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="I14" t="n">
-        <v>4.65</v>
-      </c>
       <c r="J14" t="n">
-        <v>14</v>
-      </c>
-      <c r="K14" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>1.88, 3.59, 4.30</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>vie 02/10 12:45</t>
+          <t>vie 02/10 18:30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nations League</t>
+          <t>Argentina Primera</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland vs Romania</t>
+          <t>Boca Juniors vs Union Santa Fe</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="E15" t="n">
-        <v>4.67</v>
+        <v>4.34</v>
       </c>
       <c r="F15" t="n">
-        <v>6.74</v>
+        <v>7.24</v>
       </c>
       <c r="G15" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="H15" t="n">
-        <v>4.58</v>
+        <v>4.25</v>
       </c>
       <c r="I15" t="n">
-        <v>6.61</v>
+        <v>7.1</v>
       </c>
       <c r="J15" t="n">
-        <v>14</v>
-      </c>
-      <c r="K15" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>1.59, 3.96, 6.14</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>vie 02/10 12:45</t>
+          <t>sáb 03/10 07:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1065,36 +1069,36 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hungary vs Georgia</t>
+          <t>Finland vs Albania</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2.22</v>
+        <v>2.56</v>
       </c>
       <c r="E16" t="n">
-        <v>3.67</v>
+        <v>3.47</v>
       </c>
       <c r="F16" t="n">
-        <v>3.87</v>
+        <v>3.32</v>
       </c>
       <c r="G16" t="n">
-        <v>2.18</v>
+        <v>2.51</v>
       </c>
       <c r="H16" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="I16" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="J16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>vie 02/10 12:45</t>
+          <t>sáb 03/10 10:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1104,40 +1108,40 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>France vs Italy</t>
+          <t>Croatia vs England</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.48</v>
+        <v>4.39</v>
       </c>
       <c r="E17" t="n">
-        <v>5.7</v>
+        <v>4.25</v>
       </c>
       <c r="F17" t="n">
-        <v>7.67</v>
+        <v>1.93</v>
       </c>
       <c r="G17" t="n">
-        <v>1.45</v>
+        <v>4.3</v>
       </c>
       <c r="H17" t="n">
-        <v>5.59</v>
+        <v>4.17</v>
       </c>
       <c r="I17" t="n">
-        <v>7.52</v>
+        <v>1.9</v>
       </c>
       <c r="J17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1.44, 5.20, 6.64</t>
+          <t>4.13, 4.08, 1.82</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>vie 02/10 12:45</t>
+          <t>sáb 03/10 10:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1147,40 +1151,36 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Belgium vs Turkey</t>
+          <t>Belarus vs San Marino</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1.57</v>
+        <v>1.14</v>
       </c>
       <c r="E18" t="n">
-        <v>5.32</v>
+        <v>11.91</v>
       </c>
       <c r="F18" t="n">
-        <v>6.42</v>
+        <v>50.94</v>
       </c>
       <c r="G18" t="n">
-        <v>1.54</v>
+        <v>1.12</v>
       </c>
       <c r="H18" t="n">
-        <v>5.21</v>
+        <v>11.68</v>
       </c>
       <c r="I18" t="n">
-        <v>6.3</v>
+        <v>49.94</v>
       </c>
       <c r="J18" t="n">
-        <v>16</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>1.52, 4.84, 5.76</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>vie 02/10 12:45</t>
+          <t>sáb 03/10 10:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1190,36 +1190,36 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bosnia &amp; Herzegovina vs Sweden</t>
+          <t>Iceland vs Bulgaria</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3.25</v>
+        <v>1.49</v>
       </c>
       <c r="E19" t="n">
-        <v>3.84</v>
+        <v>5.04</v>
       </c>
       <c r="F19" t="n">
-        <v>2.42</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>3.19</v>
+        <v>1.46</v>
       </c>
       <c r="H19" t="n">
-        <v>3.77</v>
+        <v>4.94</v>
       </c>
       <c r="I19" t="n">
-        <v>2.38</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>vie 02/10 12:45</t>
+          <t>sáb 03/10 10:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1229,36 +1229,36 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Faroe Islands vs Slovakia</t>
+          <t>Estonia vs Luxembourg</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>7.09</v>
+        <v>3.25</v>
       </c>
       <c r="E20" t="n">
-        <v>4.08</v>
+        <v>3.36</v>
       </c>
       <c r="F20" t="n">
-        <v>1.68</v>
+        <v>2.67</v>
       </c>
       <c r="G20" t="n">
-        <v>6.95</v>
+        <v>3.18</v>
       </c>
       <c r="H20" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="I20" t="n">
-        <v>1.65</v>
+        <v>2.62</v>
       </c>
       <c r="J20" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>vie 02/10 16:15</t>
+          <t>sáb 03/10 11:45</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1268,329 +1268,333 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Independiente vs Instituto de Córdoba</t>
+          <t>Defensa y Justicia vs San Lorenzo</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2.46</v>
+        <v>2.24</v>
       </c>
       <c r="E21" t="n">
-        <v>3.36</v>
+        <v>3.21</v>
       </c>
       <c r="F21" t="n">
-        <v>3.63</v>
+        <v>4.51</v>
       </c>
       <c r="G21" t="n">
-        <v>2.41</v>
+        <v>2.19</v>
       </c>
       <c r="H21" t="n">
-        <v>3.29</v>
+        <v>3.15</v>
       </c>
       <c r="I21" t="n">
-        <v>3.56</v>
+        <v>4.42</v>
       </c>
       <c r="J21" t="n">
         <v>13</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2.35, 3.12, 3.31</t>
+          <t>2.16, 2.87, 4.18</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>vie 02/10 17:00</t>
+          <t>sáb 03/10 12:45</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Brasil Serie A</t>
+          <t>Nations League</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sao Paulo vs Santos</t>
+          <t>Switzerland vs Slovenia</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2.16</v>
+        <v>1.4</v>
       </c>
       <c r="E22" t="n">
-        <v>3.7</v>
+        <v>5.46</v>
       </c>
       <c r="F22" t="n">
-        <v>4.06</v>
+        <v>12.4</v>
       </c>
       <c r="G22" t="n">
-        <v>2.11</v>
+        <v>1.37</v>
       </c>
       <c r="H22" t="n">
-        <v>3.63</v>
+        <v>5.36</v>
       </c>
       <c r="I22" t="n">
-        <v>3.98</v>
+        <v>12.16</v>
       </c>
       <c r="J22" t="n">
-        <v>22</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>2.08, 3.41, 3.65</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>vie 02/10 18:30</t>
+          <t>sáb 03/10 12:45</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Argentina Primera</t>
+          <t>Nations League</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia vs Gimnasia La Plata</t>
+          <t>Spain vs Czech Republic</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1.93</v>
+        <v>1.11</v>
       </c>
       <c r="E23" t="n">
-        <v>3.89</v>
+        <v>14.92</v>
       </c>
       <c r="F23" t="n">
-        <v>4.85</v>
+        <v>71.7</v>
       </c>
       <c r="G23" t="n">
-        <v>1.9</v>
+        <v>1.09</v>
       </c>
       <c r="H23" t="n">
-        <v>3.81</v>
+        <v>14.63</v>
       </c>
       <c r="I23" t="n">
-        <v>4.76</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1.82, 3.66, 4.35</t>
+          <t>1.06, 12.87, 27.84</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>vie 02/10 18:30</t>
+          <t>sáb 03/10 12:45</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Argentina Primera</t>
+          <t>Nations League</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Boca Juniors vs Union Santa Fe</t>
+          <t>North Macedonia vs Scotland</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1.64</v>
+        <v>5.33</v>
       </c>
       <c r="E24" t="n">
-        <v>4.3</v>
+        <v>3.87</v>
       </c>
       <c r="F24" t="n">
-        <v>7.23</v>
+        <v>1.87</v>
       </c>
       <c r="G24" t="n">
-        <v>1.61</v>
+        <v>5.22</v>
       </c>
       <c r="H24" t="n">
-        <v>4.22</v>
+        <v>3.79</v>
       </c>
       <c r="I24" t="n">
-        <v>7.09</v>
+        <v>1.84</v>
       </c>
       <c r="J24" t="n">
-        <v>12</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>1.57, 3.94, 5.96</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>sáb 03/10 07:00</t>
+          <t>sáb 03/10 14:00</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nations League</t>
+          <t>Argentina Primera</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Finland vs Albania</t>
+          <t>Newells Old Boys vs Lanus</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2.59</v>
+        <v>3.1</v>
       </c>
       <c r="E25" t="n">
-        <v>3.49</v>
+        <v>3.22</v>
       </c>
       <c r="F25" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="G25" t="n">
-        <v>2.54</v>
+        <v>3.04</v>
       </c>
       <c r="H25" t="n">
-        <v>3.42</v>
+        <v>3.16</v>
       </c>
       <c r="I25" t="n">
-        <v>3.19</v>
+        <v>2.82</v>
       </c>
       <c r="J25" t="n">
-        <v>14</v>
-      </c>
-      <c r="K25" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2.83, 2.98, 2.78</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>sáb 03/10 10:00</t>
+          <t>sáb 03/10 14:00</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nations League</t>
+          <t>Argentina Primera</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Belarus vs San Marino</t>
+          <t>Atlético Tucuman vs Barracas Central</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1.15</v>
+        <v>2.04</v>
       </c>
       <c r="E26" t="n">
-        <v>11.39</v>
+        <v>3.35</v>
       </c>
       <c r="F26" t="n">
-        <v>42.74</v>
+        <v>5.21</v>
       </c>
       <c r="G26" t="n">
-        <v>1.13</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>11.17</v>
+        <v>3.29</v>
       </c>
       <c r="I26" t="n">
-        <v>41.91</v>
+        <v>5.1</v>
       </c>
       <c r="J26" t="n">
-        <v>12</v>
-      </c>
-      <c r="K26" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>1.96, 3.06, 4.65</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>sáb 03/10 10:00</t>
+          <t>sáb 03/10 15:30</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nations League</t>
+          <t>Brasil Serie A</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Iceland vs Bulgaria</t>
+          <t>Atletico Mineiro vs Bragantino-SP</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1.49</v>
+        <v>2.2</v>
       </c>
       <c r="E27" t="n">
-        <v>4.98</v>
+        <v>3.8</v>
       </c>
       <c r="F27" t="n">
-        <v>9.210000000000001</v>
+        <v>3.81</v>
       </c>
       <c r="G27" t="n">
-        <v>1.46</v>
+        <v>2.16</v>
       </c>
       <c r="H27" t="n">
-        <v>4.88</v>
+        <v>3.72</v>
       </c>
       <c r="I27" t="n">
-        <v>9.029999999999999</v>
+        <v>3.74</v>
       </c>
       <c r="J27" t="n">
-        <v>12</v>
-      </c>
-      <c r="K27" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2.09, 3.49, 3.52</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>sáb 03/10 10:00</t>
+          <t>dom 04/10 11:45</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nations League</t>
+          <t>Argentina Primera</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Croatia vs England</t>
+          <t>Atlético Huracán vs Aldosivi Mar del Plata</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>4.3</v>
+        <v>1.78</v>
       </c>
       <c r="E28" t="n">
-        <v>4.09</v>
+        <v>3.75</v>
       </c>
       <c r="F28" t="n">
-        <v>1.99</v>
+        <v>6.63</v>
       </c>
       <c r="G28" t="n">
-        <v>4.21</v>
+        <v>1.74</v>
       </c>
       <c r="H28" t="n">
-        <v>4.01</v>
+        <v>3.68</v>
       </c>
       <c r="I28" t="n">
-        <v>1.95</v>
+        <v>6.5</v>
       </c>
       <c r="J28" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>4.00, 3.94, 1.88</t>
+          <t>1.70, 3.45, 5.58</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>sáb 03/10 10:00</t>
+          <t>dom 04/10 12:45</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1600,79 +1604,83 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Estonia vs Luxembourg</t>
+          <t>Wales vs Denmark</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3.17</v>
+        <v>4.19</v>
       </c>
       <c r="E29" t="n">
-        <v>3.41</v>
+        <v>4.11</v>
       </c>
       <c r="F29" t="n">
-        <v>2.69</v>
+        <v>2.01</v>
       </c>
       <c r="G29" t="n">
-        <v>3.11</v>
+        <v>4.11</v>
       </c>
       <c r="H29" t="n">
-        <v>3.34</v>
+        <v>4.03</v>
       </c>
       <c r="I29" t="n">
-        <v>2.64</v>
+        <v>1.97</v>
       </c>
       <c r="J29" t="n">
-        <v>9</v>
-      </c>
-      <c r="K29" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>3.84, 3.73, 1.91</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>sáb 03/10 11:45</t>
+          <t>dom 04/10 12:45</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Argentina Primera</t>
+          <t>Nations League</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Defensa y Justicia vs San Lorenzo</t>
+          <t>Greece vs Germany</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2.31</v>
+        <v>4.1</v>
       </c>
       <c r="E30" t="n">
-        <v>3.21</v>
+        <v>4.11</v>
       </c>
       <c r="F30" t="n">
-        <v>4.23</v>
+        <v>2.03</v>
       </c>
       <c r="G30" t="n">
-        <v>2.27</v>
+        <v>4.02</v>
       </c>
       <c r="H30" t="n">
-        <v>3.15</v>
+        <v>4.03</v>
       </c>
       <c r="I30" t="n">
-        <v>4.15</v>
+        <v>1.99</v>
       </c>
       <c r="J30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2.18, 2.87, 4.10</t>
+          <t>3.76, 3.82, 1.91</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>sáb 03/10 12:45</t>
+          <t>dom 04/10 12:45</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1682,40 +1690,36 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain vs Czech Republic</t>
+          <t>Republic of Ireland vs Israel</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1.12</v>
+        <v>2.1</v>
       </c>
       <c r="E31" t="n">
-        <v>14.69</v>
+        <v>3.83</v>
       </c>
       <c r="F31" t="n">
-        <v>61.32</v>
+        <v>4.13</v>
       </c>
       <c r="G31" t="n">
-        <v>1.09</v>
+        <v>2.05</v>
       </c>
       <c r="H31" t="n">
-        <v>14.4</v>
+        <v>3.75</v>
       </c>
       <c r="I31" t="n">
-        <v>60.12</v>
+        <v>4.05</v>
       </c>
       <c r="J31" t="n">
-        <v>13</v>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>1.07, 12.65, 27.34</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>sáb 03/10 12:45</t>
+          <t>dom 04/10 12:45</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1725,36 +1729,40 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>North Macedonia vs Scotland</t>
+          <t>Netherlands vs Serbia</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>5.41</v>
+        <v>1.22</v>
       </c>
       <c r="E32" t="n">
-        <v>3.87</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>1.86</v>
+        <v>21.53</v>
       </c>
       <c r="G32" t="n">
-        <v>5.3</v>
+        <v>1.2</v>
       </c>
       <c r="H32" t="n">
-        <v>3.8</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>1.83</v>
+        <v>21.11</v>
       </c>
       <c r="J32" t="n">
-        <v>11</v>
-      </c>
-      <c r="K32" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>1.16, 7.86, 14.12</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>sáb 03/10 12:45</t>
+          <t>dom 04/10 12:45</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1764,36 +1772,40 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Switzerland vs Slovenia</t>
+          <t>Portugal vs Norway</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1.4</v>
+        <v>1.76</v>
       </c>
       <c r="E33" t="n">
-        <v>5.5</v>
+        <v>4.83</v>
       </c>
       <c r="F33" t="n">
-        <v>11.85</v>
+        <v>4.87</v>
       </c>
       <c r="G33" t="n">
-        <v>1.37</v>
+        <v>1.73</v>
       </c>
       <c r="H33" t="n">
-        <v>5.39</v>
+        <v>4.74</v>
       </c>
       <c r="I33" t="n">
-        <v>11.61</v>
+        <v>4.77</v>
       </c>
       <c r="J33" t="n">
-        <v>12</v>
-      </c>
-      <c r="K33" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>1.64, 4.51, 4.48</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>sáb 03/10 14:00</t>
+          <t>dom 04/10 14:00</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1803,40 +1815,40 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Newells Old Boys vs Lanus</t>
+          <t>Talleres vs Belgrano de Cordoba</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>3.11</v>
+        <v>2.72</v>
       </c>
       <c r="E34" t="n">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="F34" t="n">
-        <v>2.87</v>
+        <v>3.19</v>
       </c>
       <c r="G34" t="n">
-        <v>3.05</v>
+        <v>2.67</v>
       </c>
       <c r="H34" t="n">
-        <v>3.16</v>
+        <v>3.27</v>
       </c>
       <c r="I34" t="n">
-        <v>2.81</v>
+        <v>3.13</v>
       </c>
       <c r="J34" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2.84, 2.98, 2.76</t>
+          <t>2.60, 2.99, 3.04</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>sáb 03/10 14:00</t>
+          <t>dom 04/10 16:15</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1846,126 +1858,122 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlético Tucuman vs Barracas Central</t>
+          <t>Argentinos Juniors vs CA Tigre BA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="E35" t="n">
-        <v>3.33</v>
+        <v>3.57</v>
       </c>
       <c r="F35" t="n">
-        <v>5.21</v>
+        <v>5.41</v>
       </c>
       <c r="G35" t="n">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="H35" t="n">
-        <v>3.27</v>
+        <v>3.5</v>
       </c>
       <c r="I35" t="n">
-        <v>5.1</v>
+        <v>5.31</v>
       </c>
       <c r="J35" t="n">
         <v>12</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1.95, 3.06, 4.70</t>
+          <t>1.83, 3.34, 4.84</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>sáb 03/10 15:30</t>
+          <t>dom 04/10 18:30</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Brasil Serie A</t>
+          <t>Argentina Primera</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Atletico Mineiro vs Bragantino-SP</t>
+          <t>Estudiantes de Río Cuarto vs Racing Club</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2.2</v>
+        <v>4.66</v>
       </c>
       <c r="E36" t="n">
-        <v>3.76</v>
+        <v>3.34</v>
       </c>
       <c r="F36" t="n">
-        <v>3.85</v>
+        <v>2.14</v>
       </c>
       <c r="G36" t="n">
-        <v>2.15</v>
+        <v>4.57</v>
       </c>
       <c r="H36" t="n">
-        <v>3.69</v>
+        <v>3.28</v>
       </c>
       <c r="I36" t="n">
-        <v>3.78</v>
+        <v>2.1</v>
       </c>
       <c r="J36" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2.10, 3.50, 3.47</t>
+          <t>4.30, 3.14, 2.00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>dom 04/10 11:45</t>
+          <t>lun 05/10 12:45</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Argentina Primera</t>
+          <t>Nations League</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlético Huracán vs Aldosivi Mar del Plata</t>
+          <t>Italy vs Turkey</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="E37" t="n">
-        <v>3.74</v>
+        <v>4.76</v>
       </c>
       <c r="F37" t="n">
-        <v>6.66</v>
+        <v>5.87</v>
       </c>
       <c r="G37" t="n">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="H37" t="n">
-        <v>3.67</v>
+        <v>4.67</v>
       </c>
       <c r="I37" t="n">
-        <v>6.53</v>
+        <v>5.75</v>
       </c>
       <c r="J37" t="n">
-        <v>12</v>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>1.70, 3.45, 5.58</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>dom 04/10 12:45</t>
+          <t>lun 05/10 12:45</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1975,544 +1983,544 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Netherlands vs Serbia</t>
+          <t>France vs Belgium</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="E38" t="n">
-        <v>6.92</v>
+        <v>5.03</v>
       </c>
       <c r="F38" t="n">
-        <v>15.01</v>
+        <v>6.12</v>
       </c>
       <c r="G38" t="n">
-        <v>1.27</v>
+        <v>1.59</v>
       </c>
       <c r="H38" t="n">
-        <v>6.78</v>
+        <v>4.93</v>
       </c>
       <c r="I38" t="n">
-        <v>14.71</v>
+        <v>6</v>
       </c>
       <c r="J38" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>dom 04/10 12:45</t>
+          <t>lun 05/10 13:45</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nations League</t>
+          <t>Argentina Primera</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Greece vs Germany</t>
+          <t>Deportivo Riestra vs Central Córdoba</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>3.75</v>
+        <v>1.99</v>
       </c>
       <c r="E39" t="n">
-        <v>4.04</v>
+        <v>3.45</v>
       </c>
       <c r="F39" t="n">
-        <v>2.15</v>
+        <v>5.33</v>
       </c>
       <c r="G39" t="n">
-        <v>3.67</v>
+        <v>1.95</v>
       </c>
       <c r="H39" t="n">
-        <v>3.96</v>
+        <v>3.39</v>
       </c>
       <c r="I39" t="n">
-        <v>2.1</v>
+        <v>5.22</v>
       </c>
       <c r="J39" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>3.38, 3.64, 2.08</t>
+          <t>1.92, 3.08, 4.87</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>dom 04/10 12:45</t>
+          <t>lun 05/10 16:00</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nations League</t>
+          <t>Argentina Primera</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland vs Israel</t>
+          <t>Estudiantes vs Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2.02</v>
+        <v>1.81</v>
       </c>
       <c r="E40" t="n">
         <v>3.93</v>
       </c>
       <c r="F40" t="n">
-        <v>4.35</v>
+        <v>5.8</v>
       </c>
       <c r="G40" t="n">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="H40" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="I40" t="n">
-        <v>4.27</v>
+        <v>5.69</v>
       </c>
       <c r="J40" t="n">
         <v>11</v>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>1.72, 3.62, 5.08</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>dom 04/10 12:45</t>
+          <t>lun 05/10 16:00</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nations League</t>
+          <t>Argentina Primera</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Wales vs Denmark</t>
+          <t>Velez Sarsfield BA vs Platense</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>4.51</v>
+        <v>2.01</v>
       </c>
       <c r="E41" t="n">
-        <v>4.27</v>
+        <v>3.4</v>
       </c>
       <c r="F41" t="n">
-        <v>1.91</v>
+        <v>5.3</v>
       </c>
       <c r="G41" t="n">
-        <v>4.42</v>
+        <v>1.97</v>
       </c>
       <c r="H41" t="n">
-        <v>4.18</v>
+        <v>3.33</v>
       </c>
       <c r="I41" t="n">
-        <v>1.87</v>
+        <v>5.2</v>
       </c>
       <c r="J41" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>4.20, 3.84, 1.81</t>
+          <t>1.93, 3.15, 4.63</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>dom 04/10 12:45</t>
+          <t>lun 05/10 18:15</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nations League</t>
+          <t>Argentina Primera</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portugal vs Norway</t>
+          <t>Banfield vs Rosario Central</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1.89</v>
+        <v>4.68</v>
       </c>
       <c r="E42" t="n">
-        <v>4.57</v>
+        <v>3.68</v>
       </c>
       <c r="F42" t="n">
-        <v>4.28</v>
+        <v>2.02</v>
       </c>
       <c r="G42" t="n">
-        <v>1.86</v>
+        <v>4.59</v>
       </c>
       <c r="H42" t="n">
-        <v>4.48</v>
+        <v>3.61</v>
       </c>
       <c r="I42" t="n">
-        <v>4.19</v>
+        <v>1.98</v>
       </c>
       <c r="J42" t="n">
-        <v>12</v>
-      </c>
-      <c r="K42" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>4.24, 3.38, 1.92</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>dom 04/10 14:00</t>
+          <t>mar 06/10 12:45</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Argentina Primera</t>
+          <t>Nations League</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Talleres vs Belgrano de Cordoba</t>
+          <t>England vs Czech Republic</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2.72</v>
+        <v>1.25</v>
       </c>
       <c r="E43" t="n">
-        <v>3.35</v>
+        <v>7.5</v>
       </c>
       <c r="F43" t="n">
-        <v>3.19</v>
+        <v>21.67</v>
       </c>
       <c r="G43" t="n">
-        <v>2.66</v>
+        <v>1.22</v>
       </c>
       <c r="H43" t="n">
-        <v>3.29</v>
+        <v>7.36</v>
       </c>
       <c r="I43" t="n">
-        <v>3.12</v>
+        <v>21.24</v>
       </c>
       <c r="J43" t="n">
-        <v>12</v>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>2.58, 3.02, 3.02</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>dom 04/10 16:15</t>
+          <t>mar 06/10 12:45</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Argentina Primera</t>
+          <t>Nations League</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Argentinos Juniors vs CA Tigre BA</t>
+          <t>Croatia vs Spain</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1.94</v>
+        <v>7.96</v>
       </c>
       <c r="E44" t="n">
-        <v>3.58</v>
+        <v>5.24</v>
       </c>
       <c r="F44" t="n">
-        <v>5.43</v>
+        <v>1.51</v>
       </c>
       <c r="G44" t="n">
-        <v>1.9</v>
+        <v>7.81</v>
       </c>
       <c r="H44" t="n">
-        <v>3.51</v>
+        <v>5.14</v>
       </c>
       <c r="I44" t="n">
-        <v>5.33</v>
+        <v>1.48</v>
       </c>
       <c r="J44" t="n">
-        <v>12</v>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>1.79, 3.41, 5.00</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>dom 04/10 18:30</t>
+          <t>mar 06/10 18:30</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Argentina Primera</t>
+          <t>MLS</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Estudiantes de Río Cuarto vs Racing Club</t>
+          <t>Chicago Fire vs Vancouver Whitecaps FC</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>4.68</v>
+        <v>3.06</v>
       </c>
       <c r="E45" t="n">
-        <v>3.36</v>
+        <v>4.26</v>
       </c>
       <c r="F45" t="n">
-        <v>2.13</v>
+        <v>2.39</v>
       </c>
       <c r="G45" t="n">
-        <v>4.59</v>
+        <v>3</v>
       </c>
       <c r="H45" t="n">
-        <v>3.29</v>
+        <v>4.18</v>
       </c>
       <c r="I45" t="n">
-        <v>2.09</v>
+        <v>2.34</v>
       </c>
       <c r="J45" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>4.30, 3.14, 2.00</t>
+          <t>2.83, 3.87, 2.28</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>lun 05/10 13:45</t>
+          <t>mié 07/10 16:30</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Argentina Primera</t>
+          <t>Brasil Serie A</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Deportivo Riestra vs Central Córdoba</t>
+          <t>Internacional vs Corinthians</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1.99</v>
+        <v>2.23</v>
       </c>
       <c r="E46" t="n">
-        <v>3.46</v>
+        <v>3.58</v>
       </c>
       <c r="F46" t="n">
-        <v>5.33</v>
+        <v>3.94</v>
       </c>
       <c r="G46" t="n">
-        <v>1.95</v>
+        <v>2.19</v>
       </c>
       <c r="H46" t="n">
-        <v>3.39</v>
+        <v>3.51</v>
       </c>
       <c r="I46" t="n">
-        <v>5.23</v>
+        <v>3.86</v>
       </c>
       <c r="J46" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>1.90, 3.14, 4.83</t>
+          <t>2.12, 3.35, 3.59</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>lun 05/10 16:00</t>
+          <t>mié 07/10 16:30</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Argentina Primera</t>
+          <t>Brasil Serie A</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Estudiantes vs Gimnasia Mendoza</t>
+          <t>Bragantino-SP vs Mirassol</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="E47" t="n">
-        <v>3.93</v>
+        <v>4.14</v>
       </c>
       <c r="F47" t="n">
-        <v>5.81</v>
+        <v>4.94</v>
       </c>
       <c r="G47" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="H47" t="n">
-        <v>3.86</v>
+        <v>4.06</v>
       </c>
       <c r="I47" t="n">
-        <v>5.7</v>
+        <v>4.84</v>
       </c>
       <c r="J47" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>1.72, 3.62, 5.08</t>
+          <t>1.80, 3.79, 4.34</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>lun 05/10 16:00</t>
+          <t>mié 07/10 16:30</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Argentina Primera</t>
+          <t>Brasil Serie A</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Velez Sarsfield BA vs Platense</t>
+          <t>Remo vs Grêmio</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="E48" t="n">
-        <v>3.4</v>
+        <v>3.77</v>
       </c>
       <c r="F48" t="n">
-        <v>5.34</v>
+        <v>3.46</v>
       </c>
       <c r="G48" t="n">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="H48" t="n">
-        <v>3.33</v>
+        <v>3.7</v>
       </c>
       <c r="I48" t="n">
-        <v>5.24</v>
+        <v>3.39</v>
       </c>
       <c r="J48" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>1.93, 3.15, 4.63</t>
+          <t>2.25, 3.50, 3.13</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>lun 05/10 18:15</t>
+          <t>mié 07/10 17:00</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Argentina Primera</t>
+          <t>Brasil Serie A</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Banfield vs Rosario Central</t>
+          <t>Vitoria vs Chapecoense</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4.68</v>
+        <v>1.77</v>
       </c>
       <c r="E49" t="n">
-        <v>3.68</v>
+        <v>4.26</v>
       </c>
       <c r="F49" t="n">
-        <v>2.02</v>
+        <v>5.59</v>
       </c>
       <c r="G49" t="n">
-        <v>4.59</v>
+        <v>1.73</v>
       </c>
       <c r="H49" t="n">
-        <v>3.61</v>
+        <v>4.17</v>
       </c>
       <c r="I49" t="n">
-        <v>1.98</v>
+        <v>5.48</v>
       </c>
       <c r="J49" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>4.26, 3.39, 1.92</t>
+          <t>1.66, 3.95, 5.08</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>mar 06/10 18:30</t>
+          <t>mié 07/10 17:30</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Brasil Serie A</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago Fire vs Vancouver Whitecaps FC</t>
+          <t>Botafogo vs Vasco da Gama</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>3.09</v>
+        <v>2.93</v>
       </c>
       <c r="E50" t="n">
-        <v>4.3</v>
+        <v>3.77</v>
       </c>
       <c r="F50" t="n">
-        <v>2.36</v>
+        <v>2.67</v>
       </c>
       <c r="G50" t="n">
-        <v>3.03</v>
+        <v>2.87</v>
       </c>
       <c r="H50" t="n">
-        <v>4.22</v>
+        <v>3.7</v>
       </c>
       <c r="I50" t="n">
-        <v>2.31</v>
+        <v>2.62</v>
       </c>
       <c r="J50" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2.86, 3.87, 2.26</t>
+          <t>2.73, 3.52, 2.52</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>mié 07/10 16:30</t>
+          <t>mié 07/10 18:30</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2522,40 +2530,40 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bragantino-SP vs Mirassol</t>
+          <t>Cruzeiro vs Sao Paulo</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>4.14</v>
+        <v>3.87</v>
       </c>
       <c r="F51" t="n">
-        <v>4.97</v>
+        <v>4.49</v>
       </c>
       <c r="G51" t="n">
-        <v>1.82</v>
+        <v>1.96</v>
       </c>
       <c r="H51" t="n">
-        <v>4.06</v>
+        <v>3.79</v>
       </c>
       <c r="I51" t="n">
-        <v>4.88</v>
+        <v>4.41</v>
       </c>
       <c r="J51" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>1.80, 3.79, 4.34</t>
+          <t>1.92, 3.53, 4.06</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>mié 07/10 16:30</t>
+          <t>jue 08/10 16:30</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2565,40 +2573,40 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Internacional vs Corinthians</t>
+          <t>Santos vs Flamengo</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2.23</v>
+        <v>4.63</v>
       </c>
       <c r="E52" t="n">
-        <v>3.58</v>
+        <v>4.07</v>
       </c>
       <c r="F52" t="n">
-        <v>3.95</v>
+        <v>1.93</v>
       </c>
       <c r="G52" t="n">
-        <v>2.19</v>
+        <v>4.54</v>
       </c>
       <c r="H52" t="n">
-        <v>3.51</v>
+        <v>3.99</v>
       </c>
       <c r="I52" t="n">
-        <v>3.87</v>
+        <v>1.89</v>
       </c>
       <c r="J52" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2.12, 3.35, 3.59</t>
+          <t>4.12, 3.77, 1.84</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>mié 07/10 16:30</t>
+          <t>jue 08/10 17:00</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2608,40 +2616,40 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remo vs Grêmio</t>
+          <t>Atletico Paranaense vs Atletico Mineiro</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2.34</v>
+        <v>2.17</v>
       </c>
       <c r="E53" t="n">
-        <v>3.76</v>
+        <v>3.59</v>
       </c>
       <c r="F53" t="n">
-        <v>3.49</v>
+        <v>4.15</v>
       </c>
       <c r="G53" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="H53" t="n">
-        <v>3.69</v>
+        <v>3.52</v>
       </c>
       <c r="I53" t="n">
-        <v>3.42</v>
+        <v>4.07</v>
       </c>
       <c r="J53" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2.25, 3.50, 3.13</t>
+          <t>2.07, 3.19, 3.95</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>mié 07/10 17:00</t>
+          <t>jue 08/10 18:30</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2651,40 +2659,40 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Vitoria vs Chapecoense</t>
+          <t>Palmeiras vs Bahia</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="E54" t="n">
-        <v>4.26</v>
+        <v>4.8</v>
       </c>
       <c r="F54" t="n">
-        <v>5.6</v>
+        <v>6.34</v>
       </c>
       <c r="G54" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="H54" t="n">
-        <v>4.18</v>
+        <v>4.71</v>
       </c>
       <c r="I54" t="n">
-        <v>5.49</v>
+        <v>6.21</v>
       </c>
       <c r="J54" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>1.66, 3.95, 5.08</t>
+          <t>1.56, 4.34, 5.56</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>mié 07/10 17:30</t>
+          <t>jue 08/10 18:30</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2694,384 +2702,368 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Botafogo vs Vasco da Gama</t>
+          <t>Fluminense vs Coritiba</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2.96</v>
+        <v>1.56</v>
       </c>
       <c r="E55" t="n">
-        <v>3.74</v>
+        <v>4.72</v>
       </c>
       <c r="F55" t="n">
-        <v>2.66</v>
+        <v>7.79</v>
       </c>
       <c r="G55" t="n">
-        <v>2.91</v>
+        <v>1.53</v>
       </c>
       <c r="H55" t="n">
-        <v>3.67</v>
+        <v>4.62</v>
       </c>
       <c r="I55" t="n">
-        <v>2.61</v>
+        <v>7.64</v>
       </c>
       <c r="J55" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2.74, 3.42, 2.56</t>
+          <t>1.50, 4.28, 6.57</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>mié 07/10 18:30</t>
+          <t>vie 09/10 11:30</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Brasil Serie A</t>
+          <t>Argentina Primera</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cruzeiro vs Sao Paulo</t>
+          <t>Aldosivi Mar del Plata vs Sarmiento de Junin</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>3.05</v>
       </c>
       <c r="E56" t="n">
-        <v>3.9</v>
+        <v>3.38</v>
       </c>
       <c r="F56" t="n">
-        <v>4.49</v>
+        <v>2.81</v>
       </c>
       <c r="G56" t="n">
-        <v>1.96</v>
+        <v>2.99</v>
       </c>
       <c r="H56" t="n">
-        <v>3.82</v>
+        <v>3.31</v>
       </c>
       <c r="I56" t="n">
-        <v>4.4</v>
+        <v>2.75</v>
       </c>
       <c r="J56" t="n">
-        <v>18</v>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>1.92, 3.53, 4.06</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="K56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>jue 08/10 16:30</t>
+          <t>vie 09/10 12:30</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Brasil Serie A</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Santos vs Flamengo</t>
+          <t>Borussia Dortmund vs Werder Bremen</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>4.64</v>
+        <v>1.42</v>
       </c>
       <c r="E57" t="n">
-        <v>4.06</v>
+        <v>6.19</v>
       </c>
       <c r="F57" t="n">
-        <v>1.93</v>
+        <v>8.82</v>
       </c>
       <c r="G57" t="n">
-        <v>4.55</v>
+        <v>1.39</v>
       </c>
       <c r="H57" t="n">
-        <v>3.98</v>
+        <v>6.07</v>
       </c>
       <c r="I57" t="n">
-        <v>1.89</v>
+        <v>8.65</v>
       </c>
       <c r="J57" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>4.12, 3.77, 1.84</t>
+          <t>1.36, 5.50, 7.11</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>jue 08/10 17:00</t>
+          <t>vie 09/10 12:45</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Brasil Serie A</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atletico Paranaense vs Atletico Mineiro</t>
+          <t>RC Lens vs Lyon</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>2.17</v>
+        <v>2.34</v>
       </c>
       <c r="E58" t="n">
-        <v>3.56</v>
+        <v>4.09</v>
       </c>
       <c r="F58" t="n">
-        <v>4.2</v>
+        <v>3.23</v>
       </c>
       <c r="G58" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="H58" t="n">
-        <v>3.49</v>
+        <v>4.01</v>
       </c>
       <c r="I58" t="n">
-        <v>4.12</v>
+        <v>3.17</v>
       </c>
       <c r="J58" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2.10, 3.14, 3.94</t>
+          <t>2.21, 3.78, 2.99</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>jue 08/10 18:30</t>
+          <t>vie 09/10 13:00</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Brasil Serie A</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Palmeiras vs Bahia</t>
+          <t>Málaga vs Espanyol</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1.63</v>
+        <v>2.85</v>
       </c>
       <c r="E59" t="n">
-        <v>4.81</v>
+        <v>3.54</v>
       </c>
       <c r="F59" t="n">
-        <v>6.34</v>
+        <v>2.89</v>
       </c>
       <c r="G59" t="n">
-        <v>1.59</v>
+        <v>2.79</v>
       </c>
       <c r="H59" t="n">
-        <v>4.71</v>
+        <v>3.47</v>
       </c>
       <c r="I59" t="n">
-        <v>6.22</v>
+        <v>2.83</v>
       </c>
       <c r="J59" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>1.56, 4.36, 5.58</t>
+          <t>2.67, 3.25, 2.72</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>jue 08/10 18:30</t>
+          <t>vie 09/10 15:00</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Brasil Serie A</t>
+          <t>Argentina Primera</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Fluminense vs Coritiba</t>
+          <t>Gimnasia La Plata vs Atlético Tucuman</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1.57</v>
+        <v>2.34</v>
       </c>
       <c r="E60" t="n">
-        <v>4.7</v>
+        <v>3.41</v>
       </c>
       <c r="F60" t="n">
-        <v>7.73</v>
+        <v>3.86</v>
       </c>
       <c r="G60" t="n">
-        <v>1.54</v>
+        <v>2.29</v>
       </c>
       <c r="H60" t="n">
-        <v>4.61</v>
+        <v>3.34</v>
       </c>
       <c r="I60" t="n">
-        <v>7.58</v>
+        <v>3.78</v>
       </c>
       <c r="J60" t="n">
-        <v>18</v>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>1.50, 4.28, 6.57</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="K60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>vie 09/10 12:30</t>
+          <t>vie 09/10 16:30</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Bundesliga</t>
+          <t>Argentina Primera</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Borussia Dortmund vs Werder Bremen</t>
+          <t>Instituto de Córdoba vs Boca Juniors</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1.42</v>
+        <v>3.05</v>
       </c>
       <c r="E61" t="n">
-        <v>6.19</v>
+        <v>3.19</v>
       </c>
       <c r="F61" t="n">
-        <v>8.84</v>
+        <v>2.95</v>
       </c>
       <c r="G61" t="n">
-        <v>1.39</v>
+        <v>2.99</v>
       </c>
       <c r="H61" t="n">
-        <v>6.07</v>
+        <v>3.13</v>
       </c>
       <c r="I61" t="n">
-        <v>8.66</v>
+        <v>2.89</v>
       </c>
       <c r="J61" t="n">
-        <v>20</v>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>1.36, 5.50, 7.11</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="K61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>vie 09/10 12:45</t>
+          <t>vie 09/10 18:45</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Argentina Primera</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>RC Lens vs Lyon</t>
+          <t>Union Santa Fe vs Defensa y Justicia</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="E62" t="n">
-        <v>4.09</v>
+        <v>3.51</v>
       </c>
       <c r="F62" t="n">
-        <v>3.29</v>
+        <v>3.64</v>
       </c>
       <c r="G62" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="H62" t="n">
-        <v>4.01</v>
+        <v>3.44</v>
       </c>
       <c r="I62" t="n">
-        <v>3.23</v>
+        <v>3.57</v>
       </c>
       <c r="J62" t="n">
-        <v>20</v>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>2.21, 3.78, 2.99</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="K62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>vie 09/10 13:00</t>
+          <t>vie 09/10 19:00</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Liga MX</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Málaga vs Espanyol</t>
+          <t>Puebla vs León</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>2.85</v>
+        <v>3.22</v>
       </c>
       <c r="E63" t="n">
-        <v>3.54</v>
+        <v>3.73</v>
       </c>
       <c r="F63" t="n">
-        <v>2.89</v>
+        <v>2.48</v>
       </c>
       <c r="G63" t="n">
-        <v>2.79</v>
+        <v>3.16</v>
       </c>
       <c r="H63" t="n">
-        <v>3.47</v>
+        <v>3.66</v>
       </c>
       <c r="I63" t="n">
-        <v>2.83</v>
+        <v>2.44</v>
       </c>
       <c r="J63" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2.67, 3.26, 2.72</t>
+          <t>2.92, 3.37, 2.43</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>vie 09/10 19:00</t>
+          <t>vie 09/10 21:00</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3081,197 +3073,205 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Puebla vs León</t>
+          <t>Tigres vs Toluca</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>3.31</v>
+        <v>2.99</v>
       </c>
       <c r="E64" t="n">
-        <v>3.74</v>
+        <v>3.83</v>
       </c>
       <c r="F64" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="G64" t="n">
-        <v>3.24</v>
+        <v>2.93</v>
       </c>
       <c r="H64" t="n">
-        <v>3.66</v>
+        <v>3.76</v>
       </c>
       <c r="I64" t="n">
-        <v>2.39</v>
+        <v>2.55</v>
       </c>
       <c r="J64" t="n">
         <v>12</v>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>2.77, 3.53, 2.47</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>vie 09/10 21:00</t>
+          <t>sáb 10/10 05:30</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Liga MX</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tigres vs Toluca</t>
+          <t>Arsenal vs Leeds United</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>3.06</v>
+        <v>1.44</v>
       </c>
       <c r="E65" t="n">
-        <v>3.84</v>
+        <v>5.57</v>
       </c>
       <c r="F65" t="n">
-        <v>2.55</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="G65" t="n">
-        <v>3</v>
+        <v>1.41</v>
       </c>
       <c r="H65" t="n">
-        <v>3.76</v>
+        <v>5.46</v>
       </c>
       <c r="I65" t="n">
-        <v>2.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J65" t="n">
-        <v>12</v>
-      </c>
-      <c r="K65" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>1.37, 5.01, 7.82</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>sáb 10/10 05:30</t>
+          <t>sáb 10/10 06:00</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Arsenal vs Leeds United</t>
+          <t>Rayo Vallecano vs Athletic Bilbao</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1.44</v>
+        <v>3.21</v>
       </c>
       <c r="E66" t="n">
-        <v>5.52</v>
+        <v>3.7</v>
       </c>
       <c r="F66" t="n">
-        <v>9.369999999999999</v>
+        <v>2.51</v>
       </c>
       <c r="G66" t="n">
-        <v>1.42</v>
+        <v>3.15</v>
       </c>
       <c r="H66" t="n">
-        <v>5.41</v>
+        <v>3.63</v>
       </c>
       <c r="I66" t="n">
-        <v>9.19</v>
+        <v>2.46</v>
       </c>
       <c r="J66" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>1.38, 4.94, 7.67</t>
+          <t>2.97, 3.45, 2.37</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>sáb 10/10 06:00</t>
+          <t>sáb 10/10 07:00</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Rayo Vallecano vs Athletic Bilbao</t>
+          <t>Genoa vs Fiorentina</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="E67" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="F67" t="n">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="G67" t="n">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="H67" t="n">
-        <v>3.63</v>
+        <v>3.58</v>
       </c>
       <c r="I67" t="n">
-        <v>2.46</v>
+        <v>2.41</v>
       </c>
       <c r="J67" t="n">
         <v>18</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2.93, 3.45, 2.39</t>
+          <t>3.14, 3.33, 2.32</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>sáb 10/10 07:00</t>
+          <t>sáb 10/10 07:30</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Genoa vs Fiorentina</t>
+          <t>SC Paderborn vs VfB Stuttgart</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>3.34</v>
+        <v>5.32</v>
       </c>
       <c r="E68" t="n">
-        <v>3.65</v>
+        <v>5.08</v>
       </c>
       <c r="F68" t="n">
-        <v>2.46</v>
+        <v>1.68</v>
       </c>
       <c r="G68" t="n">
-        <v>3.27</v>
+        <v>5.21</v>
       </c>
       <c r="H68" t="n">
-        <v>3.57</v>
+        <v>4.98</v>
       </c>
       <c r="I68" t="n">
-        <v>2.41</v>
+        <v>1.65</v>
       </c>
       <c r="J68" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>3.14, 3.33, 2.32</t>
+          <t>4.85, 4.65, 1.57</t>
         </is>
       </c>
     </row>
@@ -3288,33 +3288,33 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SC Paderborn vs VfB Stuttgart</t>
+          <t>TSG Hoffenheim vs Hamburger SV</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>5.33</v>
+        <v>1.49</v>
       </c>
       <c r="E69" t="n">
-        <v>5.08</v>
+        <v>5.66</v>
       </c>
       <c r="F69" t="n">
-        <v>1.68</v>
+        <v>7.56</v>
       </c>
       <c r="G69" t="n">
-        <v>5.23</v>
+        <v>1.46</v>
       </c>
       <c r="H69" t="n">
-        <v>4.98</v>
+        <v>5.55</v>
       </c>
       <c r="I69" t="n">
-        <v>1.64</v>
+        <v>7.41</v>
       </c>
       <c r="J69" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>4.85, 4.65, 1.57</t>
+          <t>1.45, 4.65, 6.62</t>
         </is>
       </c>
     </row>
@@ -3331,33 +3331,33 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>FSV Mainz 05 vs Bayer Leverkusen</t>
+          <t>Union Berlin vs Elversberg</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>3.12</v>
+        <v>2.37</v>
       </c>
       <c r="E70" t="n">
-        <v>4.23</v>
+        <v>4.17</v>
       </c>
       <c r="F70" t="n">
-        <v>2.36</v>
+        <v>3.14</v>
       </c>
       <c r="G70" t="n">
-        <v>3.06</v>
+        <v>2.32</v>
       </c>
       <c r="H70" t="n">
-        <v>4.14</v>
+        <v>4.09</v>
       </c>
       <c r="I70" t="n">
-        <v>2.31</v>
+        <v>3.08</v>
       </c>
       <c r="J70" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2.90, 3.90, 2.22</t>
+          <t>2.19, 3.96, 2.93</t>
         </is>
       </c>
     </row>
@@ -3374,33 +3374,33 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Augsburg vs Bayern Munich</t>
+          <t>FSV Mainz 05 vs Bayer Leverkusen</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>12.42</v>
+        <v>3.12</v>
       </c>
       <c r="E71" t="n">
-        <v>8.949999999999999</v>
+        <v>4.21</v>
       </c>
       <c r="F71" t="n">
-        <v>1.27</v>
+        <v>2.36</v>
       </c>
       <c r="G71" t="n">
-        <v>12.17</v>
+        <v>3.06</v>
       </c>
       <c r="H71" t="n">
-        <v>8.77</v>
+        <v>4.13</v>
       </c>
       <c r="I71" t="n">
-        <v>1.24</v>
+        <v>2.32</v>
       </c>
       <c r="J71" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>8.39, 8.28, 1.22</t>
+          <t>2.90, 3.90, 2.22</t>
         </is>
       </c>
     </row>
@@ -3417,76 +3417,76 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>TSG Hoffenheim vs Hamburger SV</t>
+          <t>Augsburg vs Bayern Munich</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1.49</v>
+        <v>12.61</v>
       </c>
       <c r="E72" t="n">
-        <v>5.63</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="F72" t="n">
-        <v>7.6</v>
+        <v>1.27</v>
       </c>
       <c r="G72" t="n">
-        <v>1.46</v>
+        <v>12.36</v>
       </c>
       <c r="H72" t="n">
-        <v>5.52</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I72" t="n">
-        <v>7.45</v>
+        <v>1.24</v>
       </c>
       <c r="J72" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>1.45, 4.65, 6.62</t>
+          <t>8.39, 8.28, 1.22</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>sáb 10/10 07:30</t>
+          <t>sáb 10/10 08:00</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Bundesliga</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Union Berlin vs Elversberg</t>
+          <t>Chelsea vs Bournemouth</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>2.36</v>
+        <v>1.81</v>
       </c>
       <c r="E73" t="n">
-        <v>4.18</v>
+        <v>4.54</v>
       </c>
       <c r="F73" t="n">
-        <v>3.14</v>
+        <v>4.81</v>
       </c>
       <c r="G73" t="n">
-        <v>2.32</v>
+        <v>1.78</v>
       </c>
       <c r="H73" t="n">
-        <v>4.1</v>
+        <v>4.45</v>
       </c>
       <c r="I73" t="n">
-        <v>3.08</v>
+        <v>4.72</v>
       </c>
       <c r="J73" t="n">
         <v>20</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2.19, 3.96, 2.93</t>
+          <t>1.71, 4.08, 4.42</t>
         </is>
       </c>
     </row>
@@ -3503,33 +3503,33 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Aston Villa vs Brentford</t>
+          <t>Ipswich Town vs Fulham</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="E74" t="n">
-        <v>3.86</v>
+        <v>3.83</v>
       </c>
       <c r="F74" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="G74" t="n">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="H74" t="n">
-        <v>3.79</v>
+        <v>3.76</v>
       </c>
       <c r="I74" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="J74" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2.63, 3.54, 2.58</t>
+          <t>2.66, 3.60, 2.52</t>
         </is>
       </c>
     </row>
@@ -3546,33 +3546,33 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chelsea vs Bournemouth</t>
+          <t>Sunderland vs Brighton and Hove Albion</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1.81</v>
+        <v>3.12</v>
       </c>
       <c r="E75" t="n">
-        <v>4.55</v>
+        <v>3.77</v>
       </c>
       <c r="F75" t="n">
-        <v>4.81</v>
+        <v>2.53</v>
       </c>
       <c r="G75" t="n">
-        <v>1.77</v>
+        <v>3.06</v>
       </c>
       <c r="H75" t="n">
-        <v>4.46</v>
+        <v>3.69</v>
       </c>
       <c r="I75" t="n">
-        <v>4.71</v>
+        <v>2.48</v>
       </c>
       <c r="J75" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>1.71, 4.08, 4.42</t>
+          <t>2.87, 3.52, 2.40</t>
         </is>
       </c>
     </row>
@@ -3589,205 +3589,205 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Ipswich Town vs Fulham</t>
+          <t>Aston Villa vs Brentford</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="E76" t="n">
-        <v>3.84</v>
+        <v>3.86</v>
       </c>
       <c r="F76" t="n">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="G76" t="n">
-        <v>2.81</v>
+        <v>2.72</v>
       </c>
       <c r="H76" t="n">
-        <v>3.76</v>
+        <v>3.79</v>
       </c>
       <c r="I76" t="n">
-        <v>2.64</v>
+        <v>2.71</v>
       </c>
       <c r="J76" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2.66, 3.60, 2.52</t>
+          <t>2.63, 3.54, 2.58</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>sáb 10/10 08:00</t>
+          <t>sáb 10/10 08:15</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Sunderland vs Brighton and Hove Albion</t>
+          <t>Alavés vs Atlético Madrid</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>3.13</v>
+        <v>4.61</v>
       </c>
       <c r="E77" t="n">
-        <v>3.77</v>
+        <v>4.04</v>
       </c>
       <c r="F77" t="n">
-        <v>2.53</v>
+        <v>1.94</v>
       </c>
       <c r="G77" t="n">
-        <v>3.06</v>
+        <v>4.52</v>
       </c>
       <c r="H77" t="n">
-        <v>3.69</v>
+        <v>3.96</v>
       </c>
       <c r="I77" t="n">
-        <v>2.48</v>
+        <v>1.9</v>
       </c>
       <c r="J77" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2.87, 3.52, 2.40</t>
+          <t>4.25, 3.75, 1.81</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>sáb 10/10 08:15</t>
+          <t>sáb 10/10 09:15</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Alavés vs Atlético Madrid</t>
+          <t>Lille vs Le Havre</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>4.58</v>
+        <v>1.52</v>
       </c>
       <c r="E78" t="n">
-        <v>4.03</v>
+        <v>5.05</v>
       </c>
       <c r="F78" t="n">
-        <v>1.95</v>
+        <v>8.07</v>
       </c>
       <c r="G78" t="n">
-        <v>4.49</v>
+        <v>1.49</v>
       </c>
       <c r="H78" t="n">
-        <v>3.95</v>
+        <v>4.95</v>
       </c>
       <c r="I78" t="n">
-        <v>1.91</v>
+        <v>7.91</v>
       </c>
       <c r="J78" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>4.25, 3.75, 1.81</t>
+          <t>1.45, 4.62, 6.65</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>sáb 10/10 09:15</t>
+          <t>sáb 10/10 10:00</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Lille vs Le Havre</t>
+          <t>Inter Milan vs Parma</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1.52</v>
+        <v>1.18</v>
       </c>
       <c r="E79" t="n">
-        <v>5.05</v>
+        <v>10.41</v>
       </c>
       <c r="F79" t="n">
-        <v>8.06</v>
+        <v>25.63</v>
       </c>
       <c r="G79" t="n">
-        <v>1.49</v>
+        <v>1.16</v>
       </c>
       <c r="H79" t="n">
-        <v>4.95</v>
+        <v>10.2</v>
       </c>
       <c r="I79" t="n">
-        <v>7.9</v>
+        <v>25.13</v>
       </c>
       <c r="J79" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>1.45, 4.62, 6.65</t>
+          <t>1.14, 9.00, 15.02</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>sáb 10/10 10:00</t>
+          <t>sáb 10/10 10:30</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Inter Milan vs Parma</t>
+          <t>Barcelona vs Getafe</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="E80" t="n">
-        <v>10.4</v>
+        <v>20.42</v>
       </c>
       <c r="F80" t="n">
-        <v>25.84</v>
+        <v>72.86</v>
       </c>
       <c r="G80" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="H80" t="n">
-        <v>10.19</v>
+        <v>20.02</v>
       </c>
       <c r="I80" t="n">
-        <v>25.34</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="J80" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>1.14, 9.00, 15.02</t>
+          <t>1.05, 17.94, 28.51</t>
         </is>
       </c>
     </row>
@@ -3799,38 +3799,38 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Bundesliga</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>RB Leipzig vs Eintracht Frankfurt</t>
+          <t>Manchester United vs Tottenham Hotspur</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E81" t="n">
-        <v>5.52</v>
+        <v>4.6</v>
       </c>
       <c r="F81" t="n">
-        <v>5.7</v>
+        <v>4.82</v>
       </c>
       <c r="G81" t="n">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="H81" t="n">
-        <v>5.41</v>
+        <v>4.51</v>
       </c>
       <c r="I81" t="n">
-        <v>5.58</v>
+        <v>4.73</v>
       </c>
       <c r="J81" t="n">
         <v>20</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>1.52, 4.94, 5.09</t>
+          <t>1.70, 4.24, 4.31</t>
         </is>
       </c>
     </row>
@@ -3842,120 +3842,116 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Manchester United vs Tottenham Hotspur</t>
+          <t>RB Leipzig vs Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="E82" t="n">
-        <v>4.59</v>
+        <v>5.49</v>
       </c>
       <c r="F82" t="n">
-        <v>4.82</v>
+        <v>5.7</v>
       </c>
       <c r="G82" t="n">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="H82" t="n">
-        <v>4.5</v>
+        <v>5.38</v>
       </c>
       <c r="I82" t="n">
-        <v>4.73</v>
+        <v>5.59</v>
       </c>
       <c r="J82" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>1.70, 4.24, 4.31</t>
+          <t>1.52, 4.94, 5.09</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>sáb 10/10 10:30</t>
+          <t>sáb 10/10 11:00</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>MLS</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Barcelona vs Getafe</t>
+          <t>Toronto FC vs CF Montreal</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1.09</v>
+        <v>1.88</v>
       </c>
       <c r="E83" t="n">
-        <v>20.88</v>
+        <v>4.48</v>
       </c>
       <c r="F83" t="n">
-        <v>76.86</v>
+        <v>4.44</v>
       </c>
       <c r="G83" t="n">
-        <v>1.07</v>
+        <v>1.84</v>
       </c>
       <c r="H83" t="n">
-        <v>20.47</v>
+        <v>4.39</v>
       </c>
       <c r="I83" t="n">
-        <v>75.34999999999999</v>
+        <v>4.35</v>
       </c>
       <c r="J83" t="n">
-        <v>18</v>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>1.05, 17.33, 27.11</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="K83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>sáb 10/10 11:00</t>
+          <t>sáb 10/10 11:45</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Argentina Primera</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Toronto FC vs CF Montreal</t>
+          <t>Barracas Central vs Atlético Huracán</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1.86</v>
+        <v>3.5</v>
       </c>
       <c r="E84" t="n">
-        <v>4.52</v>
+        <v>3.06</v>
       </c>
       <c r="F84" t="n">
-        <v>4.52</v>
+        <v>2.72</v>
       </c>
       <c r="G84" t="n">
-        <v>1.82</v>
+        <v>3.43</v>
       </c>
       <c r="H84" t="n">
-        <v>4.43</v>
+        <v>3</v>
       </c>
       <c r="I84" t="n">
-        <v>4.43</v>
+        <v>2.66</v>
       </c>
       <c r="J84" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K84" t="inlineStr"/>
     </row>
@@ -3979,19 +3975,19 @@
         <v>1.86</v>
       </c>
       <c r="E85" t="n">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="F85" t="n">
-        <v>4.49</v>
+        <v>4.52</v>
       </c>
       <c r="G85" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="H85" t="n">
-        <v>4.46</v>
+        <v>4.41</v>
       </c>
       <c r="I85" t="n">
-        <v>4.4</v>
+        <v>4.44</v>
       </c>
       <c r="J85" t="n">
         <v>11</v>
@@ -4006,38 +4002,38 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Napoli vs Frosinone</t>
+          <t>Lorient vs Paris FC</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1.5</v>
+        <v>3.27</v>
       </c>
       <c r="E86" t="n">
-        <v>5.36</v>
+        <v>3.7</v>
       </c>
       <c r="F86" t="n">
-        <v>7.8</v>
+        <v>2.47</v>
       </c>
       <c r="G86" t="n">
-        <v>1.47</v>
+        <v>3.2</v>
       </c>
       <c r="H86" t="n">
-        <v>5.26</v>
+        <v>3.63</v>
       </c>
       <c r="I86" t="n">
-        <v>7.64</v>
+        <v>2.43</v>
       </c>
       <c r="J86" t="n">
         <v>19</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>1.44, 4.92, 6.24</t>
+          <t>3.09, 3.31, 2.36</t>
         </is>
       </c>
     </row>
@@ -4061,22 +4057,22 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.12</v>
+        <v>4.13</v>
       </c>
       <c r="F87" t="n">
-        <v>4.23</v>
+        <v>4.2</v>
       </c>
       <c r="G87" t="n">
         <v>1.96</v>
       </c>
       <c r="H87" t="n">
-        <v>4.04</v>
+        <v>4.05</v>
       </c>
       <c r="I87" t="n">
-        <v>4.14</v>
+        <v>4.12</v>
       </c>
       <c r="J87" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -4092,38 +4088,38 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AS Monaco vs Toulouse</t>
+          <t>Napoli vs Frosinone</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1.77</v>
+        <v>1.51</v>
       </c>
       <c r="E88" t="n">
-        <v>4.47</v>
+        <v>5.44</v>
       </c>
       <c r="F88" t="n">
-        <v>5.2</v>
+        <v>7.5</v>
       </c>
       <c r="G88" t="n">
-        <v>1.74</v>
+        <v>1.48</v>
       </c>
       <c r="H88" t="n">
-        <v>4.39</v>
+        <v>5.33</v>
       </c>
       <c r="I88" t="n">
-        <v>5.1</v>
+        <v>7.35</v>
       </c>
       <c r="J88" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>1.67, 4.20, 4.63</t>
+          <t>1.44, 4.95, 6.26</t>
         </is>
       </c>
     </row>
@@ -4147,26 +4143,26 @@
         <v>1.11</v>
       </c>
       <c r="E89" t="n">
-        <v>16.35</v>
+        <v>16.3</v>
       </c>
       <c r="F89" t="n">
-        <v>49.07</v>
+        <v>50.69</v>
       </c>
       <c r="G89" t="n">
         <v>1.09</v>
       </c>
       <c r="H89" t="n">
-        <v>16.03</v>
+        <v>15.98</v>
       </c>
       <c r="I89" t="n">
-        <v>48.11</v>
+        <v>49.69</v>
       </c>
       <c r="J89" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>1.07, 13.36, 22.01</t>
+          <t>1.08, 12.88, 20.87</t>
         </is>
       </c>
     </row>
@@ -4183,33 +4179,33 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Lorient vs Paris FC</t>
+          <t>AS Monaco vs Toulouse</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>3.25</v>
+        <v>1.76</v>
       </c>
       <c r="E90" t="n">
-        <v>3.69</v>
+        <v>4.51</v>
       </c>
       <c r="F90" t="n">
-        <v>2.49</v>
+        <v>5.21</v>
       </c>
       <c r="G90" t="n">
-        <v>3.19</v>
+        <v>1.73</v>
       </c>
       <c r="H90" t="n">
-        <v>3.62</v>
+        <v>4.42</v>
       </c>
       <c r="I90" t="n">
-        <v>2.44</v>
+        <v>5.11</v>
       </c>
       <c r="J90" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>3.09, 3.31, 2.36</t>
+          <t>1.67, 4.20, 4.63</t>
         </is>
       </c>
     </row>
@@ -4230,29 +4226,29 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="E91" t="n">
-        <v>6.74</v>
+        <v>6.68</v>
       </c>
       <c r="F91" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="G91" t="n">
         <v>1.36</v>
       </c>
       <c r="H91" t="n">
-        <v>6.61</v>
+        <v>6.55</v>
       </c>
       <c r="I91" t="n">
-        <v>9.02</v>
+        <v>8.92</v>
       </c>
       <c r="J91" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>1.33, 5.90, 7.37</t>
+          <t>1.33, 5.92, 7.39</t>
         </is>
       </c>
     </row>
@@ -4351,10 +4347,10 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="E94" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="F94" t="n">
         <v>2.46</v>
@@ -4363,13 +4359,13 @@
         <v>3.15</v>
       </c>
       <c r="H94" t="n">
-        <v>3.74</v>
+        <v>3.73</v>
       </c>
       <c r="I94" t="n">
         <v>2.41</v>
       </c>
       <c r="J94" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K94" t="inlineStr"/>
     </row>
@@ -4396,19 +4392,19 @@
         <v>3.94</v>
       </c>
       <c r="F95" t="n">
-        <v>3.89</v>
+        <v>3.88</v>
       </c>
       <c r="G95" t="n">
         <v>2.09</v>
       </c>
       <c r="H95" t="n">
-        <v>3.87</v>
+        <v>3.86</v>
       </c>
       <c r="I95" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="J95" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K95" t="inlineStr"/>
     </row>
@@ -4425,29 +4421,29 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Orlando City SC vs Columbus Crew SC</t>
+          <t>New England Revolution vs Seattle Sounders FC</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>2.13</v>
+        <v>1.83</v>
       </c>
       <c r="E96" t="n">
-        <v>4.38</v>
+        <v>4.64</v>
       </c>
       <c r="F96" t="n">
-        <v>3.54</v>
+        <v>4.6</v>
       </c>
       <c r="G96" t="n">
-        <v>2.09</v>
+        <v>1.79</v>
       </c>
       <c r="H96" t="n">
-        <v>4.29</v>
+        <v>4.55</v>
       </c>
       <c r="I96" t="n">
-        <v>3.47</v>
+        <v>4.51</v>
       </c>
       <c r="J96" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K96" t="inlineStr"/>
     </row>
@@ -4464,26 +4460,26 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Atlanta United FC vs FC Cincinnati</t>
+          <t>Inter Miami CF vs D.C. United</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>2.48</v>
+        <v>1.44</v>
       </c>
       <c r="E97" t="n">
-        <v>4.37</v>
+        <v>6.15</v>
       </c>
       <c r="F97" t="n">
-        <v>2.87</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="G97" t="n">
-        <v>2.43</v>
+        <v>1.41</v>
       </c>
       <c r="H97" t="n">
-        <v>4.29</v>
+        <v>6.03</v>
       </c>
       <c r="I97" t="n">
-        <v>2.82</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="J97" t="n">
         <v>12</v>
@@ -4503,26 +4499,26 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Inter Miami CF vs D.C. United</t>
+          <t>Orlando City SC vs Columbus Crew SC</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1.43</v>
+        <v>2.13</v>
       </c>
       <c r="E98" t="n">
-        <v>6.18</v>
+        <v>4.33</v>
       </c>
       <c r="F98" t="n">
-        <v>8.52</v>
+        <v>3.56</v>
       </c>
       <c r="G98" t="n">
-        <v>1.4</v>
+        <v>2.09</v>
       </c>
       <c r="H98" t="n">
-        <v>6.06</v>
+        <v>4.25</v>
       </c>
       <c r="I98" t="n">
-        <v>8.35</v>
+        <v>3.49</v>
       </c>
       <c r="J98" t="n">
         <v>12</v>
@@ -4542,29 +4538,29 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>New England Revolution vs Seattle Sounders FC</t>
+          <t>Charlotte FC vs FC Dallas</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1.82</v>
+        <v>2.2</v>
       </c>
       <c r="E99" t="n">
-        <v>4.65</v>
+        <v>4.29</v>
       </c>
       <c r="F99" t="n">
-        <v>4.61</v>
+        <v>3.41</v>
       </c>
       <c r="G99" t="n">
-        <v>1.79</v>
+        <v>2.16</v>
       </c>
       <c r="H99" t="n">
-        <v>4.56</v>
+        <v>4.21</v>
       </c>
       <c r="I99" t="n">
-        <v>4.52</v>
+        <v>3.34</v>
       </c>
       <c r="J99" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K99" t="inlineStr"/>
     </row>
@@ -4581,26 +4577,26 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Philadelphia Union vs Real Salt Lake</t>
+          <t>Atlanta United FC vs FC Cincinnati</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1.38</v>
+        <v>2.5</v>
       </c>
       <c r="E100" t="n">
-        <v>6.31</v>
+        <v>4.35</v>
       </c>
       <c r="F100" t="n">
-        <v>10.05</v>
+        <v>2.85</v>
       </c>
       <c r="G100" t="n">
-        <v>1.36</v>
+        <v>2.45</v>
       </c>
       <c r="H100" t="n">
-        <v>6.19</v>
+        <v>4.27</v>
       </c>
       <c r="I100" t="n">
-        <v>9.859999999999999</v>
+        <v>2.79</v>
       </c>
       <c r="J100" t="n">
         <v>12</v>
@@ -4620,29 +4616,29 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Charlotte FC vs FC Dallas</t>
+          <t>New York Red Bulls vs San Diego FC</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="E101" t="n">
-        <v>4.27</v>
+        <v>4.41</v>
       </c>
       <c r="F101" t="n">
-        <v>3.65</v>
+        <v>3.14</v>
       </c>
       <c r="G101" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="H101" t="n">
-        <v>4.18</v>
+        <v>4.32</v>
       </c>
       <c r="I101" t="n">
-        <v>3.58</v>
+        <v>3.08</v>
       </c>
       <c r="J101" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K101" t="inlineStr"/>
     </row>
@@ -4659,29 +4655,29 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>New York Red Bulls vs San Diego FC</t>
+          <t>Philadelphia Union vs Real Salt Lake</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>2.22</v>
+        <v>1.4</v>
       </c>
       <c r="E102" t="n">
-        <v>4.44</v>
+        <v>6.25</v>
       </c>
       <c r="F102" t="n">
-        <v>3.27</v>
+        <v>9.33</v>
       </c>
       <c r="G102" t="n">
-        <v>2.18</v>
+        <v>1.37</v>
       </c>
       <c r="H102" t="n">
-        <v>4.36</v>
+        <v>6.13</v>
       </c>
       <c r="I102" t="n">
-        <v>3.21</v>
+        <v>9.15</v>
       </c>
       <c r="J102" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K102" t="inlineStr"/>
     </row>
@@ -4698,29 +4694,29 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Austin FC vs Nashville SC</t>
+          <t>Sporting Kansas City vs Portland Timbers</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>4.01</v>
+        <v>2.78</v>
       </c>
       <c r="E103" t="n">
-        <v>4.13</v>
+        <v>4.44</v>
       </c>
       <c r="F103" t="n">
-        <v>2.05</v>
+        <v>2.53</v>
       </c>
       <c r="G103" t="n">
-        <v>3.93</v>
+        <v>2.73</v>
       </c>
       <c r="H103" t="n">
-        <v>4.05</v>
+        <v>4.35</v>
       </c>
       <c r="I103" t="n">
-        <v>2.01</v>
+        <v>2.48</v>
       </c>
       <c r="J103" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K103" t="inlineStr"/>
     </row>
@@ -4732,34 +4728,34 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Argentina Primera</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Minnesota United FC vs Houston Dynamo</t>
+          <t>River Plate vs Estudiantes de Río Cuarto</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>2.27</v>
+        <v>1.25</v>
       </c>
       <c r="E104" t="n">
-        <v>4.01</v>
+        <v>6.7</v>
       </c>
       <c r="F104" t="n">
-        <v>3.44</v>
+        <v>31.17</v>
       </c>
       <c r="G104" t="n">
-        <v>2.23</v>
+        <v>1.23</v>
       </c>
       <c r="H104" t="n">
-        <v>3.93</v>
+        <v>6.57</v>
       </c>
       <c r="I104" t="n">
-        <v>3.37</v>
+        <v>30.56</v>
       </c>
       <c r="J104" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K104" t="inlineStr"/>
     </row>
@@ -4771,34 +4767,34 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Argentina Primera</t>
+          <t>MLS</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>River Plate vs Estudiantes de Río Cuarto</t>
+          <t>Minnesota United FC vs Houston Dynamo</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1.25</v>
+        <v>2.27</v>
       </c>
       <c r="E105" t="n">
-        <v>6.7</v>
+        <v>4</v>
       </c>
       <c r="F105" t="n">
-        <v>31.17</v>
+        <v>3.46</v>
       </c>
       <c r="G105" t="n">
-        <v>1.23</v>
+        <v>2.22</v>
       </c>
       <c r="H105" t="n">
-        <v>6.57</v>
+        <v>3.92</v>
       </c>
       <c r="I105" t="n">
-        <v>30.56</v>
+        <v>3.39</v>
       </c>
       <c r="J105" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K105" t="inlineStr"/>
     </row>
@@ -4815,29 +4811,29 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Sporting Kansas City vs Portland Timbers</t>
+          <t>Austin FC vs Nashville SC</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>2.79</v>
+        <v>4.01</v>
       </c>
       <c r="E106" t="n">
-        <v>4.44</v>
+        <v>4.13</v>
       </c>
       <c r="F106" t="n">
-        <v>2.52</v>
+        <v>2.05</v>
       </c>
       <c r="G106" t="n">
-        <v>2.73</v>
+        <v>3.93</v>
       </c>
       <c r="H106" t="n">
-        <v>4.35</v>
+        <v>4.05</v>
       </c>
       <c r="I106" t="n">
-        <v>2.48</v>
+        <v>2.01</v>
       </c>
       <c r="J106" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K106" t="inlineStr"/>
     </row>
@@ -4858,25 +4854,25 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="E107" t="n">
-        <v>3.91</v>
+        <v>3.9</v>
       </c>
       <c r="F107" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="G107" t="n">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="H107" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="I107" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="J107" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K107" t="inlineStr"/>
     </row>
@@ -4897,22 +4893,22 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="E108" t="n">
-        <v>4.45</v>
+        <v>4.43</v>
       </c>
       <c r="F108" t="n">
-        <v>4.66</v>
+        <v>4.58</v>
       </c>
       <c r="G108" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="H108" t="n">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="I108" t="n">
-        <v>4.57</v>
+        <v>4.49</v>
       </c>
       <c r="J108" t="n">
         <v>12</v>
@@ -4936,22 +4932,22 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="E109" t="n">
-        <v>4.16</v>
+        <v>4.15</v>
       </c>
       <c r="F109" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="G109" t="n">
         <v>2.79</v>
       </c>
       <c r="H109" t="n">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="I109" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="J109" t="n">
         <v>11</v>
@@ -4975,25 +4971,25 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="E110" t="n">
-        <v>4.14</v>
+        <v>4.12</v>
       </c>
       <c r="F110" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="G110" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="H110" t="n">
-        <v>4.06</v>
+        <v>4.04</v>
       </c>
       <c r="I110" t="n">
-        <v>4.02</v>
+        <v>4.01</v>
       </c>
       <c r="J110" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K110" t="inlineStr"/>
     </row>
@@ -5014,25 +5010,25 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="E111" t="n">
         <v>3.88</v>
       </c>
       <c r="F111" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="G111" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="H111" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="I111" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="J111" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
@@ -5057,25 +5053,25 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="E112" t="n">
         <v>3.51</v>
       </c>
       <c r="F112" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="G112" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="H112" t="n">
         <v>3.44</v>
       </c>
       <c r="I112" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="J112" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
@@ -5091,38 +5087,38 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Hull City vs Everton</t>
+          <t>Lazio vs Monza</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>4.03</v>
+        <v>1.66</v>
       </c>
       <c r="E113" t="n">
-        <v>3.65</v>
+        <v>4.43</v>
       </c>
       <c r="F113" t="n">
-        <v>2.18</v>
+        <v>6.55</v>
       </c>
       <c r="G113" t="n">
-        <v>3.95</v>
+        <v>1.63</v>
       </c>
       <c r="H113" t="n">
-        <v>3.58</v>
+        <v>4.34</v>
       </c>
       <c r="I113" t="n">
-        <v>2.14</v>
+        <v>6.42</v>
       </c>
       <c r="J113" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>3.72, 3.41, 2.04</t>
+          <t>1.55, 4.13, 5.95</t>
         </is>
       </c>
     </row>
@@ -5161,7 +5157,7 @@
         <v>2.81</v>
       </c>
       <c r="J114" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
@@ -5177,38 +5173,38 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Nice vs Strasbourg</t>
+          <t>Lecce vs Bologna</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>2.36</v>
+        <v>4.58</v>
       </c>
       <c r="E115" t="n">
-        <v>3.95</v>
+        <v>3.69</v>
       </c>
       <c r="F115" t="n">
-        <v>3.29</v>
+        <v>2.04</v>
       </c>
       <c r="G115" t="n">
-        <v>2.32</v>
+        <v>4.49</v>
       </c>
       <c r="H115" t="n">
-        <v>3.87</v>
+        <v>3.62</v>
       </c>
       <c r="I115" t="n">
-        <v>3.23</v>
+        <v>2</v>
       </c>
       <c r="J115" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>2.22, 3.64, 3.07</t>
+          <t>4.45, 3.33, 1.89</t>
         </is>
       </c>
     </row>
@@ -5220,38 +5216,38 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Lazio vs Monza</t>
+          <t>Nice vs Strasbourg</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1.69</v>
+        <v>2.38</v>
       </c>
       <c r="E116" t="n">
-        <v>4.34</v>
+        <v>3.95</v>
       </c>
       <c r="F116" t="n">
-        <v>6.32</v>
+        <v>3.26</v>
       </c>
       <c r="G116" t="n">
-        <v>1.66</v>
+        <v>2.33</v>
       </c>
       <c r="H116" t="n">
-        <v>4.25</v>
+        <v>3.87</v>
       </c>
       <c r="I116" t="n">
-        <v>6.19</v>
+        <v>3.2</v>
       </c>
       <c r="J116" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>1.58, 4.04, 5.69</t>
+          <t>2.22, 3.64, 3.07</t>
         </is>
       </c>
     </row>
@@ -5263,38 +5259,38 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Lecce vs Bologna</t>
+          <t>Hull City vs Everton</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>4.54</v>
+        <v>4.02</v>
       </c>
       <c r="E117" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="F117" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="G117" t="n">
-        <v>4.45</v>
+        <v>3.94</v>
       </c>
       <c r="H117" t="n">
-        <v>3.63</v>
+        <v>3.58</v>
       </c>
       <c r="I117" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="J117" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>4.40, 3.29, 1.92</t>
+          <t>3.72, 3.41, 2.04</t>
         </is>
       </c>
     </row>
@@ -5318,22 +5314,22 @@
         <v>2.06</v>
       </c>
       <c r="E118" t="n">
-        <v>4.44</v>
+        <v>4.43</v>
       </c>
       <c r="F118" t="n">
-        <v>3.7</v>
+        <v>3.71</v>
       </c>
       <c r="G118" t="n">
         <v>2.02</v>
       </c>
       <c r="H118" t="n">
-        <v>4.35</v>
+        <v>4.34</v>
       </c>
       <c r="I118" t="n">
-        <v>3.63</v>
+        <v>3.64</v>
       </c>
       <c r="J118" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
@@ -5358,25 +5354,25 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="E119" t="n">
-        <v>4.18</v>
+        <v>4.19</v>
       </c>
       <c r="F119" t="n">
-        <v>5.29</v>
+        <v>5.24</v>
       </c>
       <c r="G119" t="n">
         <v>1.78</v>
       </c>
       <c r="H119" t="n">
-        <v>4.1</v>
+        <v>4.11</v>
       </c>
       <c r="I119" t="n">
-        <v>5.18</v>
+        <v>5.14</v>
       </c>
       <c r="J119" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
@@ -5407,7 +5403,7 @@
         <v>5.57</v>
       </c>
       <c r="F120" t="n">
-        <v>7.73</v>
+        <v>7.67</v>
       </c>
       <c r="G120" t="n">
         <v>1.46</v>
@@ -5416,10 +5412,10 @@
         <v>5.46</v>
       </c>
       <c r="I120" t="n">
-        <v>7.58</v>
+        <v>7.52</v>
       </c>
       <c r="J120" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
@@ -5435,38 +5431,38 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Liverpool vs Manchester City</t>
+          <t>SC Freiburg vs FC Schalke 04</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>2.75</v>
+        <v>1.71</v>
       </c>
       <c r="E121" t="n">
-        <v>4.03</v>
+        <v>4.54</v>
       </c>
       <c r="F121" t="n">
-        <v>2.71</v>
+        <v>5.71</v>
       </c>
       <c r="G121" t="n">
-        <v>2.7</v>
+        <v>1.68</v>
       </c>
       <c r="H121" t="n">
-        <v>3.95</v>
+        <v>4.45</v>
       </c>
       <c r="I121" t="n">
-        <v>2.65</v>
+        <v>5.6</v>
       </c>
       <c r="J121" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>2.57, 3.69, 2.57</t>
+          <t>1.63, 3.93, 5.33</t>
         </is>
       </c>
     </row>
@@ -5478,38 +5474,38 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Bundesliga</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>SC Freiburg vs FC Schalke 04</t>
+          <t>Liverpool vs Manchester City</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1.71</v>
+        <v>2.73</v>
       </c>
       <c r="E122" t="n">
-        <v>4.5</v>
+        <v>4.04</v>
       </c>
       <c r="F122" t="n">
-        <v>5.75</v>
+        <v>2.73</v>
       </c>
       <c r="G122" t="n">
-        <v>1.68</v>
+        <v>2.68</v>
       </c>
       <c r="H122" t="n">
-        <v>4.41</v>
+        <v>3.96</v>
       </c>
       <c r="I122" t="n">
-        <v>5.64</v>
+        <v>2.67</v>
       </c>
       <c r="J122" t="n">
         <v>20</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>1.63, 3.92, 5.32</t>
+          <t>2.57, 3.69, 2.57</t>
         </is>
       </c>
     </row>
@@ -5533,26 +5529,26 @@
         <v>4.7</v>
       </c>
       <c r="E123" t="n">
-        <v>4.06</v>
+        <v>4.08</v>
       </c>
       <c r="F123" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="G123" t="n">
-        <v>4.6</v>
+        <v>4.61</v>
       </c>
       <c r="H123" t="n">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="I123" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="J123" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>4.32, 3.77, 1.79</t>
+          <t>4.35, 3.80, 1.79</t>
         </is>
       </c>
     </row>
@@ -5573,29 +5569,29 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="E124" t="n">
-        <v>4.42</v>
+        <v>4.44</v>
       </c>
       <c r="F124" t="n">
-        <v>5.37</v>
+        <v>5.5</v>
       </c>
       <c r="G124" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="H124" t="n">
-        <v>4.33</v>
+        <v>4.35</v>
       </c>
       <c r="I124" t="n">
-        <v>5.27</v>
+        <v>5.39</v>
       </c>
       <c r="J124" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>1.65, 4.06, 4.93</t>
+          <t>1.65, 4.06, 4.94</t>
         </is>
       </c>
     </row>
@@ -5646,38 +5642,38 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Cagliari vs Juventus</t>
+          <t>Troyes vs Marseille</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>7.2</v>
+        <v>4.28</v>
       </c>
       <c r="E126" t="n">
-        <v>4.36</v>
+        <v>4.25</v>
       </c>
       <c r="F126" t="n">
-        <v>1.63</v>
+        <v>1.96</v>
       </c>
       <c r="G126" t="n">
-        <v>7.06</v>
+        <v>4.19</v>
       </c>
       <c r="H126" t="n">
-        <v>4.28</v>
+        <v>4.17</v>
       </c>
       <c r="I126" t="n">
-        <v>1.6</v>
+        <v>1.92</v>
       </c>
       <c r="J126" t="n">
         <v>19</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>6.23, 4.02, 1.55</t>
+          <t>3.97, 3.92, 1.83</t>
         </is>
       </c>
     </row>
@@ -5689,38 +5685,38 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Troyes vs Marseille</t>
+          <t>Cagliari vs Juventus</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>4.23</v>
+        <v>7.21</v>
       </c>
       <c r="E127" t="n">
-        <v>4.25</v>
+        <v>4.37</v>
       </c>
       <c r="F127" t="n">
-        <v>1.97</v>
+        <v>1.63</v>
       </c>
       <c r="G127" t="n">
-        <v>4.15</v>
+        <v>7.07</v>
       </c>
       <c r="H127" t="n">
-        <v>4.16</v>
+        <v>4.28</v>
       </c>
       <c r="I127" t="n">
-        <v>1.93</v>
+        <v>1.6</v>
       </c>
       <c r="J127" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>3.97, 3.92, 1.83</t>
+          <t>6.22, 4.02, 1.55</t>
         </is>
       </c>
     </row>
@@ -5753,13 +5749,13 @@
         <v>2.28</v>
       </c>
       <c r="H128" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="I128" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="J128" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K128" t="inlineStr"/>
     </row>
@@ -5897,10 +5893,10 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="E132" t="n">
-        <v>5.01</v>
+        <v>4.93</v>
       </c>
       <c r="F132" t="n">
         <v>6.14</v>
@@ -5909,10 +5905,10 @@
         <v>1.59</v>
       </c>
       <c r="H132" t="n">
-        <v>4.91</v>
+        <v>4.84</v>
       </c>
       <c r="I132" t="n">
-        <v>6.02</v>
+        <v>6.01</v>
       </c>
       <c r="J132" t="n">
         <v>11</v>
@@ -5936,25 +5932,25 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="E133" t="n">
-        <v>4.04</v>
+        <v>4.03</v>
       </c>
       <c r="F133" t="n">
-        <v>4.03</v>
+        <v>3.99</v>
       </c>
       <c r="G133" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H133" t="n">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="I133" t="n">
-        <v>3.95</v>
+        <v>3.91</v>
       </c>
       <c r="J133" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K133" t="inlineStr"/>
     </row>
@@ -5975,25 +5971,25 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="E134" t="n">
-        <v>4.42</v>
+        <v>4.34</v>
       </c>
       <c r="F134" t="n">
-        <v>5.67</v>
+        <v>5.65</v>
       </c>
       <c r="G134" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="H134" t="n">
-        <v>4.33</v>
+        <v>4.26</v>
       </c>
       <c r="I134" t="n">
-        <v>5.56</v>
+        <v>5.54</v>
       </c>
       <c r="J134" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K134" t="inlineStr"/>
     </row>
@@ -6053,25 +6049,25 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>3.85</v>
+        <v>3.83</v>
       </c>
       <c r="E136" t="n">
-        <v>4.06</v>
+        <v>4.05</v>
       </c>
       <c r="F136" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="G136" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="H136" t="n">
-        <v>3.98</v>
+        <v>3.97</v>
       </c>
       <c r="I136" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="J136" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K136" t="inlineStr"/>
     </row>
@@ -6092,29 +6088,29 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="E137" t="n">
-        <v>4.54</v>
+        <v>4.56</v>
       </c>
       <c r="F137" t="n">
-        <v>5.99</v>
+        <v>6.02</v>
       </c>
       <c r="G137" t="n">
         <v>1.65</v>
       </c>
       <c r="H137" t="n">
-        <v>4.45</v>
+        <v>4.47</v>
       </c>
       <c r="I137" t="n">
-        <v>5.87</v>
+        <v>5.9</v>
       </c>
       <c r="J137" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>1.58, 3.98, 5.76</t>
+          <t>1.57, 4.03, 5.82</t>
         </is>
       </c>
     </row>
@@ -6141,7 +6137,7 @@
         <v>3.64</v>
       </c>
       <c r="F138" t="n">
-        <v>3.32</v>
+        <v>3.33</v>
       </c>
       <c r="G138" t="n">
         <v>2.42</v>
@@ -6153,7 +6149,7 @@
         <v>3.26</v>
       </c>
       <c r="J138" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
@@ -6169,36 +6165,40 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Argentina Primera</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Lanus vs Velez Sarsfield BA</t>
+          <t>Coventry City vs Newcastle United</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>2.36</v>
+        <v>3.53</v>
       </c>
       <c r="E139" t="n">
-        <v>3.2</v>
+        <v>3.92</v>
       </c>
       <c r="F139" t="n">
-        <v>4.08</v>
+        <v>2.26</v>
       </c>
       <c r="G139" t="n">
-        <v>2.32</v>
+        <v>3.46</v>
       </c>
       <c r="H139" t="n">
-        <v>3.14</v>
+        <v>3.84</v>
       </c>
       <c r="I139" t="n">
-        <v>4</v>
+        <v>2.22</v>
       </c>
       <c r="J139" t="n">
-        <v>7</v>
-      </c>
-      <c r="K139" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>3.26, 3.60, 2.15</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -6220,7 +6220,7 @@
         <v>2.82</v>
       </c>
       <c r="E140" t="n">
-        <v>3.58</v>
+        <v>3.59</v>
       </c>
       <c r="F140" t="n">
         <v>2.89</v>
@@ -6229,13 +6229,13 @@
         <v>2.76</v>
       </c>
       <c r="H140" t="n">
-        <v>3.51</v>
+        <v>3.52</v>
       </c>
       <c r="I140" t="n">
         <v>2.83</v>
       </c>
       <c r="J140" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
@@ -6251,40 +6251,36 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Argentina Primera</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Coventry City vs Newcastle United</t>
+          <t>Lanus vs Velez Sarsfield BA</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>3.51</v>
+        <v>2.36</v>
       </c>
       <c r="E141" t="n">
-        <v>3.92</v>
+        <v>3.2</v>
       </c>
       <c r="F141" t="n">
-        <v>2.27</v>
+        <v>4.08</v>
       </c>
       <c r="G141" t="n">
-        <v>3.44</v>
+        <v>2.32</v>
       </c>
       <c r="H141" t="n">
-        <v>3.84</v>
+        <v>3.14</v>
       </c>
       <c r="I141" t="n">
-        <v>2.22</v>
+        <v>4</v>
       </c>
       <c r="J141" t="n">
-        <v>21</v>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>3.26, 3.60, 2.15</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="K141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -6342,29 +6338,29 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="E143" t="n">
-        <v>4.04</v>
+        <v>4.07</v>
       </c>
       <c r="F143" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="G143" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="H143" t="n">
-        <v>3.96</v>
+        <v>3.99</v>
       </c>
       <c r="I143" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="J143" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>2.47, 3.79, 2.62</t>
+          <t>2.48, 3.81, 2.61</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6381,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>3.85</v>
+        <v>3.88</v>
       </c>
       <c r="E144" t="n">
         <v>4.12</v>
@@ -6394,16 +6390,16 @@
         <v>2.09</v>
       </c>
       <c r="G144" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="H144" t="n">
         <v>4.04</v>
       </c>
       <c r="I144" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="J144" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
@@ -6424,33 +6420,33 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Viking FK vs Bayern Munich</t>
+          <t>RB Leipzig vs PSV Eindhoven</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>28.24</v>
+        <v>2.14</v>
       </c>
       <c r="E145" t="n">
-        <v>14.3</v>
+        <v>4.42</v>
       </c>
       <c r="F145" t="n">
-        <v>1.14</v>
+        <v>3.49</v>
       </c>
       <c r="G145" t="n">
-        <v>27.68</v>
+        <v>2.1</v>
       </c>
       <c r="H145" t="n">
-        <v>14.02</v>
+        <v>4.33</v>
       </c>
       <c r="I145" t="n">
-        <v>1.12</v>
+        <v>3.42</v>
       </c>
       <c r="J145" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>14.62, 12.14, 1.10</t>
+          <t>2.02, 4.22, 3.14</t>
         </is>
       </c>
     </row>
@@ -6467,31 +6463,35 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Galatasaray vs Barcelona</t>
+          <t>Villarreal vs Napoli</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>9.92</v>
+        <v>2.39</v>
       </c>
       <c r="E146" t="n">
-        <v>6.87</v>
+        <v>3.85</v>
       </c>
       <c r="F146" t="n">
-        <v>1.36</v>
+        <v>3.31</v>
       </c>
       <c r="G146" t="n">
-        <v>9.73</v>
+        <v>2.34</v>
       </c>
       <c r="H146" t="n">
-        <v>6.74</v>
+        <v>3.77</v>
       </c>
       <c r="I146" t="n">
-        <v>1.34</v>
+        <v>3.25</v>
       </c>
       <c r="J146" t="n">
         <v>18</v>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>2.20, 3.63, 3.12</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -6513,22 +6513,22 @@
         <v>1.32</v>
       </c>
       <c r="E147" t="n">
-        <v>6.36</v>
+        <v>6.39</v>
       </c>
       <c r="F147" t="n">
-        <v>15.1</v>
+        <v>15.06</v>
       </c>
       <c r="G147" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="H147" t="n">
-        <v>6.23</v>
+        <v>6.26</v>
       </c>
       <c r="I147" t="n">
-        <v>14.8</v>
+        <v>14.76</v>
       </c>
       <c r="J147" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K147" t="inlineStr"/>
     </row>
@@ -6545,33 +6545,33 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>RB Leipzig vs PSV Eindhoven</t>
+          <t>Atlético Madrid vs Manchester United</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>2.14</v>
+        <v>2.35</v>
       </c>
       <c r="E148" t="n">
-        <v>4.41</v>
+        <v>4.19</v>
       </c>
       <c r="F148" t="n">
-        <v>3.49</v>
+        <v>3.16</v>
       </c>
       <c r="G148" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="H148" t="n">
-        <v>4.33</v>
+        <v>4.11</v>
       </c>
       <c r="I148" t="n">
-        <v>3.42</v>
+        <v>3.1</v>
       </c>
       <c r="J148" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>2.02, 4.22, 3.14</t>
+          <t>2.26, 3.74, 2.94</t>
         </is>
       </c>
     </row>
@@ -6588,35 +6588,31 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Inter Milan vs Club Brugge</t>
+          <t>Galatasaray vs Barcelona</t>
         </is>
       </c>
       <c r="D149" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="E149" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="F149" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="G149" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="H149" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="I149" t="n">
         <v>1.34</v>
       </c>
-      <c r="E149" t="n">
-        <v>6.41</v>
-      </c>
-      <c r="F149" t="n">
-        <v>12.61</v>
-      </c>
-      <c r="G149" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="H149" t="n">
-        <v>6.28</v>
-      </c>
-      <c r="I149" t="n">
-        <v>12.37</v>
-      </c>
       <c r="J149" t="n">
-        <v>19</v>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>1.27, 5.87, 9.43</t>
-        </is>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="K149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -6631,33 +6627,33 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Villarreal vs Napoli</t>
+          <t>Viking FK vs Bayern Munich</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>2.39</v>
+        <v>27.97</v>
       </c>
       <c r="E150" t="n">
-        <v>3.84</v>
+        <v>14.16</v>
       </c>
       <c r="F150" t="n">
-        <v>3.31</v>
+        <v>1.14</v>
       </c>
       <c r="G150" t="n">
-        <v>2.35</v>
+        <v>27.42</v>
       </c>
       <c r="H150" t="n">
-        <v>3.76</v>
+        <v>13.89</v>
       </c>
       <c r="I150" t="n">
-        <v>3.24</v>
+        <v>1.12</v>
       </c>
       <c r="J150" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>2.20, 3.63, 3.12</t>
+          <t>14.53, 12.17, 1.10</t>
         </is>
       </c>
     </row>
@@ -6674,33 +6670,33 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Atlético Madrid vs Manchester United</t>
+          <t>Inter Milan vs Club Brugge</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>2.35</v>
+        <v>1.34</v>
       </c>
       <c r="E151" t="n">
-        <v>4.21</v>
+        <v>6.42</v>
       </c>
       <c r="F151" t="n">
-        <v>3.15</v>
+        <v>12.48</v>
       </c>
       <c r="G151" t="n">
-        <v>2.3</v>
+        <v>1.32</v>
       </c>
       <c r="H151" t="n">
-        <v>4.12</v>
+        <v>6.29</v>
       </c>
       <c r="I151" t="n">
-        <v>3.09</v>
+        <v>12.24</v>
       </c>
       <c r="J151" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>2.26, 3.74, 2.94</t>
+          <t>1.27, 5.90, 9.45</t>
         </is>
       </c>
     </row>
@@ -6724,7 +6720,7 @@
         <v>3.89</v>
       </c>
       <c r="E152" t="n">
-        <v>4.49</v>
+        <v>4.5</v>
       </c>
       <c r="F152" t="n">
         <v>2</v>
@@ -6733,17 +6729,17 @@
         <v>3.81</v>
       </c>
       <c r="H152" t="n">
-        <v>4.4</v>
+        <v>4.41</v>
       </c>
       <c r="I152" t="n">
         <v>1.96</v>
       </c>
       <c r="J152" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>3.49, 4.29, 1.88</t>
+          <t>3.49, 4.32, 1.87</t>
         </is>
       </c>
     </row>
@@ -6764,25 +6760,25 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="E153" t="n">
-        <v>7.04</v>
+        <v>7.06</v>
       </c>
       <c r="F153" t="n">
         <v>1.32</v>
       </c>
       <c r="G153" t="n">
-        <v>11.86</v>
+        <v>11.77</v>
       </c>
       <c r="H153" t="n">
-        <v>6.9</v>
+        <v>6.92</v>
       </c>
       <c r="I153" t="n">
         <v>1.3</v>
       </c>
       <c r="J153" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
@@ -6803,33 +6799,33 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>ŠK Slovan Bratislava vs VfB Stuttgart</t>
+          <t>AS Roma vs Real Madrid</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>9.869999999999999</v>
+        <v>3.64</v>
       </c>
       <c r="E154" t="n">
-        <v>6.39</v>
+        <v>4.23</v>
       </c>
       <c r="F154" t="n">
-        <v>1.38</v>
+        <v>2.13</v>
       </c>
       <c r="G154" t="n">
-        <v>9.68</v>
+        <v>3.57</v>
       </c>
       <c r="H154" t="n">
-        <v>6.27</v>
+        <v>4.15</v>
       </c>
       <c r="I154" t="n">
-        <v>1.36</v>
+        <v>2.09</v>
       </c>
       <c r="J154" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>8.31, 5.84, 1.29</t>
+          <t>3.30, 3.82, 2.05</t>
         </is>
       </c>
     </row>
@@ -6868,7 +6864,7 @@
         <v>2.66</v>
       </c>
       <c r="J155" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
@@ -6889,35 +6885,31 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>AS Roma vs Real Madrid</t>
+          <t>Aston Villa vs Fenerbahce</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>3.66</v>
+        <v>1.82</v>
       </c>
       <c r="E156" t="n">
-        <v>4.23</v>
+        <v>4.26</v>
       </c>
       <c r="F156" t="n">
-        <v>2.13</v>
+        <v>5.08</v>
       </c>
       <c r="G156" t="n">
-        <v>3.59</v>
+        <v>1.79</v>
       </c>
       <c r="H156" t="n">
-        <v>4.14</v>
+        <v>4.18</v>
       </c>
       <c r="I156" t="n">
-        <v>2.08</v>
+        <v>4.98</v>
       </c>
       <c r="J156" t="n">
-        <v>19</v>
-      </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>3.30, 3.82, 2.05</t>
-        </is>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="K156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6932,31 +6924,35 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Aston Villa vs Fenerbahce</t>
+          <t>Bodø/Glimt vs Borussia Dortmund</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1.83</v>
+        <v>3.38</v>
       </c>
       <c r="E157" t="n">
-        <v>4.22</v>
+        <v>4.39</v>
       </c>
       <c r="F157" t="n">
-        <v>5.05</v>
+        <v>2.19</v>
       </c>
       <c r="G157" t="n">
-        <v>1.8</v>
+        <v>3.31</v>
       </c>
       <c r="H157" t="n">
-        <v>4.13</v>
+        <v>4.3</v>
       </c>
       <c r="I157" t="n">
-        <v>4.95</v>
+        <v>2.15</v>
       </c>
       <c r="J157" t="n">
         <v>18</v>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>3.11, 4.06, 2.07</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6971,33 +6967,33 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Bodø/Glimt vs Borussia Dortmund</t>
+          <t>Manchester City vs Paris Saint Germain</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>3.36</v>
+        <v>2.3</v>
       </c>
       <c r="E158" t="n">
-        <v>4.39</v>
+        <v>4.31</v>
       </c>
       <c r="F158" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="G158" t="n">
-        <v>3.3</v>
+        <v>2.25</v>
       </c>
       <c r="H158" t="n">
-        <v>4.3</v>
+        <v>4.22</v>
       </c>
       <c r="I158" t="n">
-        <v>2.15</v>
+        <v>3.14</v>
       </c>
       <c r="J158" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>3.11, 4.06, 2.07</t>
+          <t>2.15, 3.95, 3.01</t>
         </is>
       </c>
     </row>
@@ -7018,29 +7014,29 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="E159" t="n">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="F159" t="n">
-        <v>3.57</v>
+        <v>3.44</v>
       </c>
       <c r="G159" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="H159" t="n">
         <v>3.88</v>
       </c>
       <c r="I159" t="n">
-        <v>3.5</v>
+        <v>3.37</v>
       </c>
       <c r="J159" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>2.16, 3.63, 3.20</t>
+          <t>2.22, 3.66, 3.06</t>
         </is>
       </c>
     </row>
@@ -7057,33 +7053,33 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Manchester City vs Paris Saint Germain</t>
+          <t>ŠK Slovan Bratislava vs VfB Stuttgart</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>2.28</v>
+        <v>10</v>
       </c>
       <c r="E160" t="n">
-        <v>4.3</v>
+        <v>6.37</v>
       </c>
       <c r="F160" t="n">
-        <v>3.23</v>
+        <v>1.38</v>
       </c>
       <c r="G160" t="n">
-        <v>2.24</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H160" t="n">
-        <v>4.21</v>
+        <v>6.24</v>
       </c>
       <c r="I160" t="n">
-        <v>3.16</v>
+        <v>1.36</v>
       </c>
       <c r="J160" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>2.12, 3.94, 3.07</t>
+          <t>8.31, 5.84, 1.29</t>
         </is>
       </c>
     </row>
@@ -7100,33 +7096,33 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Salzburg vs AC Milan</t>
+          <t>Lyon vs Crystal Palace</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>4.38</v>
+        <v>2.29</v>
       </c>
       <c r="E161" t="n">
-        <v>4.32</v>
+        <v>4.03</v>
       </c>
       <c r="F161" t="n">
-        <v>1.92</v>
+        <v>3.38</v>
       </c>
       <c r="G161" t="n">
-        <v>4.3</v>
+        <v>2.25</v>
       </c>
       <c r="H161" t="n">
-        <v>4.23</v>
+        <v>3.95</v>
       </c>
       <c r="I161" t="n">
-        <v>1.88</v>
+        <v>3.31</v>
       </c>
       <c r="J161" t="n">
         <v>16</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>4.01, 3.97, 1.81</t>
+          <t>2.17, 3.70, 3.13</t>
         </is>
       </c>
     </row>
@@ -7143,31 +7139,35 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Torreense vs Sunderland</t>
+          <t>Lech Poznań vs Bayer Leverkusen</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>7.24</v>
+        <v>5.11</v>
       </c>
       <c r="E162" t="n">
-        <v>5.42</v>
+        <v>4.68</v>
       </c>
       <c r="F162" t="n">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="G162" t="n">
-        <v>7.1</v>
+        <v>5.01</v>
       </c>
       <c r="H162" t="n">
-        <v>5.32</v>
+        <v>4.59</v>
       </c>
       <c r="I162" t="n">
-        <v>1.49</v>
+        <v>1.72</v>
       </c>
       <c r="J162" t="n">
-        <v>14</v>
-      </c>
-      <c r="K162" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>4.47, 4.34, 1.67</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -7182,33 +7182,33 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>NK Celje vs Omonoia FC</t>
+          <t>Salzburg vs AC Milan</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>2.57</v>
+        <v>4.4</v>
       </c>
       <c r="E163" t="n">
-        <v>3.7</v>
+        <v>4.28</v>
       </c>
       <c r="F163" t="n">
-        <v>3.12</v>
+        <v>1.92</v>
       </c>
       <c r="G163" t="n">
-        <v>2.52</v>
+        <v>4.32</v>
       </c>
       <c r="H163" t="n">
-        <v>3.63</v>
+        <v>4.2</v>
       </c>
       <c r="I163" t="n">
-        <v>3.06</v>
+        <v>1.89</v>
       </c>
       <c r="J163" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>2.41, 3.44, 2.90</t>
+          <t>4.01, 3.97, 1.81</t>
         </is>
       </c>
     </row>
@@ -7225,33 +7225,33 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Sparta Prague vs Lillestrom</t>
+          <t>AZ Alkmaar vs Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="E164" t="n">
-        <v>5.76</v>
+        <v>6.17</v>
       </c>
       <c r="F164" t="n">
-        <v>10.3</v>
+        <v>10.99</v>
       </c>
       <c r="G164" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="H164" t="n">
-        <v>5.65</v>
+        <v>6.05</v>
       </c>
       <c r="I164" t="n">
-        <v>10.09</v>
+        <v>10.77</v>
       </c>
       <c r="J164" t="n">
         <v>16</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>1.36, 5.15, 7.81</t>
+          <t>1.31, 5.67, 8.58</t>
         </is>
       </c>
     </row>
@@ -7268,35 +7268,31 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Lyon vs Crystal Palace</t>
+          <t>Torreense vs Sunderland</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>2.29</v>
+        <v>7.2</v>
       </c>
       <c r="E165" t="n">
-        <v>4.03</v>
+        <v>5.4</v>
       </c>
       <c r="F165" t="n">
-        <v>3.38</v>
+        <v>1.52</v>
       </c>
       <c r="G165" t="n">
-        <v>2.25</v>
+        <v>7.06</v>
       </c>
       <c r="H165" t="n">
-        <v>3.95</v>
+        <v>5.3</v>
       </c>
       <c r="I165" t="n">
-        <v>3.32</v>
+        <v>1.49</v>
       </c>
       <c r="J165" t="n">
-        <v>16</v>
-      </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>2.17, 3.70, 3.13</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="K165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -7311,33 +7307,33 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Lech Poznań vs Bayer Leverkusen</t>
+          <t>Sparta Prague vs Lillestrom</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>5.09</v>
+        <v>1.41</v>
       </c>
       <c r="E166" t="n">
-        <v>4.68</v>
+        <v>5.78</v>
       </c>
       <c r="F166" t="n">
-        <v>1.75</v>
+        <v>10.28</v>
       </c>
       <c r="G166" t="n">
-        <v>4.99</v>
+        <v>1.38</v>
       </c>
       <c r="H166" t="n">
-        <v>4.59</v>
+        <v>5.67</v>
       </c>
       <c r="I166" t="n">
-        <v>1.72</v>
+        <v>10.08</v>
       </c>
       <c r="J166" t="n">
         <v>16</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>4.47, 4.34, 1.67</t>
+          <t>1.36, 5.15, 7.81</t>
         </is>
       </c>
     </row>
@@ -7354,33 +7350,33 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>AZ Alkmaar vs Hapoel Be'er Sheva</t>
+          <t>NK Celje vs Omonoia FC</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1.38</v>
+        <v>2.56</v>
       </c>
       <c r="E167" t="n">
-        <v>6.17</v>
+        <v>3.71</v>
       </c>
       <c r="F167" t="n">
-        <v>10.98</v>
+        <v>3.11</v>
       </c>
       <c r="G167" t="n">
-        <v>1.35</v>
+        <v>2.51</v>
       </c>
       <c r="H167" t="n">
-        <v>6.04</v>
+        <v>3.64</v>
       </c>
       <c r="I167" t="n">
-        <v>10.77</v>
+        <v>3.05</v>
       </c>
       <c r="J167" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>1.31, 5.67, 8.58</t>
+          <t>2.41, 3.44, 2.90</t>
         </is>
       </c>
     </row>
@@ -7413,7 +7409,7 @@
         <v>2.42</v>
       </c>
       <c r="H168" t="n">
-        <v>3.8</v>
+        <v>3.81</v>
       </c>
       <c r="I168" t="n">
         <v>3.09</v>
@@ -7423,7 +7419,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>2.32, 3.65, 2.91</t>
+          <t>2.31, 3.63, 2.93</t>
         </is>
       </c>
     </row>
@@ -7440,33 +7436,33 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb vs Anderlecht</t>
+          <t>Celta Vigo vs Juventus</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>2</v>
+        <v>3.81</v>
       </c>
       <c r="E169" t="n">
-        <v>4</v>
+        <v>3.81</v>
       </c>
       <c r="F169" t="n">
-        <v>4.37</v>
+        <v>2.19</v>
       </c>
       <c r="G169" t="n">
-        <v>1.96</v>
+        <v>3.74</v>
       </c>
       <c r="H169" t="n">
-        <v>3.92</v>
+        <v>3.74</v>
       </c>
       <c r="I169" t="n">
-        <v>4.28</v>
+        <v>2.15</v>
       </c>
       <c r="J169" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>1.84, 3.74, 4.13</t>
+          <t>3.48, 3.46, 2.11</t>
         </is>
       </c>
     </row>
@@ -7483,31 +7479,35 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Benfica vs Celtic</t>
+          <t>Dinamo Zagreb vs Anderlecht</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1.31</v>
+        <v>1.99</v>
       </c>
       <c r="E170" t="n">
-        <v>6.89</v>
+        <v>3.99</v>
       </c>
       <c r="F170" t="n">
-        <v>14.38</v>
+        <v>4.39</v>
       </c>
       <c r="G170" t="n">
-        <v>1.28</v>
+        <v>1.95</v>
       </c>
       <c r="H170" t="n">
-        <v>6.76</v>
+        <v>3.91</v>
       </c>
       <c r="I170" t="n">
-        <v>14.1</v>
+        <v>4.3</v>
       </c>
       <c r="J170" t="n">
-        <v>15</v>
-      </c>
-      <c r="K170" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>1.84, 3.74, 4.13</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -7522,35 +7522,31 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>TSG Hoffenheim vs Besiktas JK</t>
+          <t>Benfica vs Celtic</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>2.09</v>
+        <v>1.31</v>
       </c>
       <c r="E171" t="n">
-        <v>4.32</v>
+        <v>6.9</v>
       </c>
       <c r="F171" t="n">
-        <v>3.68</v>
+        <v>14.19</v>
       </c>
       <c r="G171" t="n">
-        <v>2.05</v>
+        <v>1.28</v>
       </c>
       <c r="H171" t="n">
-        <v>4.24</v>
+        <v>6.76</v>
       </c>
       <c r="I171" t="n">
-        <v>3.61</v>
+        <v>13.91</v>
       </c>
       <c r="J171" t="n">
-        <v>16</v>
-      </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>1.91, 4.04, 3.56</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="K171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -7565,33 +7561,33 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Celta Vigo vs Juventus</t>
+          <t>TSG Hoffenheim vs Besiktas JK</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="E172" t="n">
-        <v>3.82</v>
+        <v>4.33</v>
       </c>
       <c r="F172" t="n">
-        <v>2.2</v>
+        <v>3.66</v>
       </c>
       <c r="G172" t="n">
-        <v>3.72</v>
+        <v>2.06</v>
       </c>
       <c r="H172" t="n">
-        <v>3.75</v>
+        <v>4.24</v>
       </c>
       <c r="I172" t="n">
-        <v>2.15</v>
+        <v>3.59</v>
       </c>
       <c r="J172" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>3.48, 3.46, 2.11</t>
+          <t>1.91, 4.04, 3.56</t>
         </is>
       </c>
     </row>
@@ -7615,19 +7611,19 @@
         <v>1.48</v>
       </c>
       <c r="E173" t="n">
-        <v>5.38</v>
+        <v>5.35</v>
       </c>
       <c r="F173" t="n">
-        <v>8.51</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="G173" t="n">
         <v>1.45</v>
       </c>
       <c r="H173" t="n">
-        <v>5.27</v>
+        <v>5.25</v>
       </c>
       <c r="I173" t="n">
-        <v>8.34</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="J173" t="n">
         <v>16</v>
@@ -7651,33 +7647,33 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Ferencváros TC vs Viktoria Plzeň</t>
+          <t>Rennes vs OFI Crete</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>2.01</v>
+        <v>1.39</v>
       </c>
       <c r="E174" t="n">
-        <v>4.16</v>
+        <v>5.97</v>
       </c>
       <c r="F174" t="n">
-        <v>4.12</v>
+        <v>10.58</v>
       </c>
       <c r="G174" t="n">
-        <v>1.97</v>
+        <v>1.36</v>
       </c>
       <c r="H174" t="n">
-        <v>4.08</v>
+        <v>5.86</v>
       </c>
       <c r="I174" t="n">
-        <v>4.04</v>
+        <v>10.37</v>
       </c>
       <c r="J174" t="n">
         <v>16</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>1.89, 4.00, 3.66</t>
+          <t>1.32, 5.46, 8.43</t>
         </is>
       </c>
     </row>
@@ -7694,33 +7690,33 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Marseille vs Olympiakos Piraeus</t>
+          <t>NEC Nijmegen vs PFC Levski Sofia</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>2.23</v>
+        <v>1.97</v>
       </c>
       <c r="E175" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="F175" t="n">
-        <v>3.56</v>
+        <v>4.37</v>
       </c>
       <c r="G175" t="n">
-        <v>2.18</v>
+        <v>1.93</v>
       </c>
       <c r="H175" t="n">
-        <v>3.92</v>
+        <v>4.02</v>
       </c>
       <c r="I175" t="n">
-        <v>3.49</v>
+        <v>4.29</v>
       </c>
       <c r="J175" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>2.12, 3.63, 3.30</t>
+          <t>1.86, 3.78, 4.00</t>
         </is>
       </c>
     </row>
@@ -7737,33 +7733,33 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>NEC Nijmegen vs PFC Levski Sofia</t>
+          <t>Marseille vs Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1.97</v>
+        <v>2.23</v>
       </c>
       <c r="E176" t="n">
-        <v>4.09</v>
+        <v>4</v>
       </c>
       <c r="F176" t="n">
-        <v>4.38</v>
+        <v>3.55</v>
       </c>
       <c r="G176" t="n">
-        <v>1.93</v>
+        <v>2.19</v>
       </c>
       <c r="H176" t="n">
-        <v>4.01</v>
+        <v>3.93</v>
       </c>
       <c r="I176" t="n">
-        <v>4.3</v>
+        <v>3.48</v>
       </c>
       <c r="J176" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>1.86, 3.78, 4.00</t>
+          <t>2.12, 3.63, 3.30</t>
         </is>
       </c>
     </row>
@@ -7780,33 +7776,33 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Rennes vs OFI Crete</t>
+          <t>Ferencváros TC vs Viktoria Plzeň</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>1.39</v>
+        <v>2.01</v>
       </c>
       <c r="E177" t="n">
-        <v>5.98</v>
+        <v>4.17</v>
       </c>
       <c r="F177" t="n">
-        <v>10.72</v>
+        <v>4.11</v>
       </c>
       <c r="G177" t="n">
-        <v>1.36</v>
+        <v>1.97</v>
       </c>
       <c r="H177" t="n">
-        <v>5.86</v>
+        <v>4.09</v>
       </c>
       <c r="I177" t="n">
-        <v>10.51</v>
+        <v>4.03</v>
       </c>
       <c r="J177" t="n">
         <v>16</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>1.32, 5.46, 8.43</t>
+          <t>1.89, 4.00, 3.66</t>
         </is>
       </c>
     </row>
@@ -7830,19 +7826,19 @@
         <v>1.25</v>
       </c>
       <c r="E178" t="n">
-        <v>8.18</v>
+        <v>8.1</v>
       </c>
       <c r="F178" t="n">
-        <v>17.06</v>
+        <v>17.07</v>
       </c>
       <c r="G178" t="n">
         <v>1.23</v>
       </c>
       <c r="H178" t="n">
-        <v>8.02</v>
+        <v>7.94</v>
       </c>
       <c r="I178" t="n">
-        <v>16.73</v>
+        <v>16.74</v>
       </c>
       <c r="J178" t="n">
         <v>16</v>
@@ -7873,22 +7869,22 @@
         <v>2.06</v>
       </c>
       <c r="E179" t="n">
-        <v>4.51</v>
+        <v>4.52</v>
       </c>
       <c r="F179" t="n">
-        <v>3.67</v>
+        <v>3.66</v>
       </c>
       <c r="G179" t="n">
         <v>2.02</v>
       </c>
       <c r="H179" t="n">
-        <v>4.42</v>
+        <v>4.43</v>
       </c>
       <c r="I179" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="J179" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
@@ -7913,25 +7909,25 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="E180" t="n">
-        <v>3.81</v>
+        <v>3.83</v>
       </c>
       <c r="F180" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="G180" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="H180" t="n">
-        <v>3.74</v>
+        <v>3.76</v>
       </c>
       <c r="I180" t="n">
         <v>2.94</v>
       </c>
       <c r="J180" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
@@ -7959,26 +7955,26 @@
         <v>3.36</v>
       </c>
       <c r="E181" t="n">
-        <v>3.81</v>
+        <v>3.79</v>
       </c>
       <c r="F181" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="G181" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="H181" t="n">
-        <v>3.73</v>
+        <v>3.71</v>
       </c>
       <c r="I181" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="J181" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>3.14, 3.44, 2.27</t>
+          <t>3.12, 3.43, 2.29</t>
         </is>
       </c>
     </row>
@@ -7999,29 +7995,29 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="E182" t="n">
-        <v>3.8</v>
+        <v>3.81</v>
       </c>
       <c r="F182" t="n">
-        <v>3.81</v>
+        <v>3.78</v>
       </c>
       <c r="G182" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="H182" t="n">
-        <v>3.73</v>
+        <v>3.74</v>
       </c>
       <c r="I182" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="J182" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>2.09, 3.48, 3.51</t>
+          <t>2.08, 3.48, 3.54</t>
         </is>
       </c>
     </row>
@@ -8042,25 +8038,25 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="E183" t="n">
-        <v>4.06</v>
+        <v>4.07</v>
       </c>
       <c r="F183" t="n">
         <v>2.45</v>
       </c>
       <c r="G183" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="H183" t="n">
-        <v>3.98</v>
+        <v>3.99</v>
       </c>
       <c r="I183" t="n">
         <v>2.4</v>
       </c>
       <c r="J183" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
@@ -8085,25 +8081,25 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>4.56</v>
+        <v>4.55</v>
       </c>
       <c r="E184" t="n">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="F184" t="n">
         <v>1.94</v>
       </c>
       <c r="G184" t="n">
-        <v>4.47</v>
+        <v>4.46</v>
       </c>
       <c r="H184" t="n">
-        <v>4</v>
+        <v>3.99</v>
       </c>
       <c r="I184" t="n">
         <v>1.9</v>
       </c>
       <c r="J184" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
@@ -8128,25 +8124,25 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>5.02</v>
+        <v>5.03</v>
       </c>
       <c r="E185" t="n">
-        <v>4.35</v>
+        <v>4.32</v>
       </c>
       <c r="F185" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="G185" t="n">
-        <v>4.92</v>
+        <v>4.93</v>
       </c>
       <c r="H185" t="n">
-        <v>4.27</v>
+        <v>4.23</v>
       </c>
       <c r="I185" t="n">
         <v>1.78</v>
       </c>
       <c r="J185" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
@@ -8167,33 +8163,33 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Elversberg vs Augsburg</t>
+          <t>Werder Bremen vs SC Paderborn</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>2.61</v>
+        <v>1.89</v>
       </c>
       <c r="E186" t="n">
-        <v>4.17</v>
+        <v>4.45</v>
       </c>
       <c r="F186" t="n">
-        <v>2.8</v>
+        <v>4.43</v>
       </c>
       <c r="G186" t="n">
-        <v>2.55</v>
+        <v>1.85</v>
       </c>
       <c r="H186" t="n">
-        <v>4.09</v>
+        <v>4.36</v>
       </c>
       <c r="I186" t="n">
-        <v>2.75</v>
+        <v>4.34</v>
       </c>
       <c r="J186" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>2.46, 3.80, 2.63</t>
+          <t>1.77, 4.17, 4.02</t>
         </is>
       </c>
     </row>
@@ -8210,33 +8206,33 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Union Berlin vs Borussia Dortmund</t>
+          <t>Hamburger SV vs VfB Stuttgart</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>5.02</v>
+        <v>4.1</v>
       </c>
       <c r="E187" t="n">
-        <v>4.71</v>
+        <v>4.51</v>
       </c>
       <c r="F187" t="n">
-        <v>1.76</v>
+        <v>1.94</v>
       </c>
       <c r="G187" t="n">
-        <v>4.92</v>
+        <v>4.02</v>
       </c>
       <c r="H187" t="n">
-        <v>4.61</v>
+        <v>4.42</v>
       </c>
       <c r="I187" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="J187" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>4.44, 4.23, 1.68</t>
+          <t>4.04, 3.89, 1.83</t>
         </is>
       </c>
     </row>
@@ -8253,33 +8249,33 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>FC Schalke 04 vs FSV Mainz 05</t>
+          <t>Union Berlin vs Borussia Dortmund</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>3.2</v>
+        <v>5.06</v>
       </c>
       <c r="E188" t="n">
-        <v>3.99</v>
+        <v>4.66</v>
       </c>
       <c r="F188" t="n">
-        <v>2.4</v>
+        <v>1.76</v>
       </c>
       <c r="G188" t="n">
-        <v>3.14</v>
+        <v>4.96</v>
       </c>
       <c r="H188" t="n">
-        <v>3.91</v>
+        <v>4.57</v>
       </c>
       <c r="I188" t="n">
-        <v>2.35</v>
+        <v>1.73</v>
       </c>
       <c r="J188" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>3.05, 3.60, 2.25</t>
+          <t>4.44, 4.23, 1.68</t>
         </is>
       </c>
     </row>
@@ -8296,33 +8292,33 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Hamburger SV vs VfB Stuttgart</t>
+          <t>FC Schalke 04 vs FSV Mainz 05</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>4.13</v>
+        <v>3.2</v>
       </c>
       <c r="E189" t="n">
-        <v>4.49</v>
+        <v>3.99</v>
       </c>
       <c r="F189" t="n">
-        <v>1.94</v>
+        <v>2.39</v>
       </c>
       <c r="G189" t="n">
-        <v>4.05</v>
+        <v>3.14</v>
       </c>
       <c r="H189" t="n">
-        <v>4.4</v>
+        <v>3.92</v>
       </c>
       <c r="I189" t="n">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="J189" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>4.04, 3.89, 1.83</t>
+          <t>3.05, 3.60, 2.25</t>
         </is>
       </c>
     </row>
@@ -8339,33 +8335,33 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Werder Bremen vs SC Paderborn</t>
+          <t>Elversberg vs Augsburg</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>1.89</v>
+        <v>2.6</v>
       </c>
       <c r="E190" t="n">
-        <v>4.46</v>
+        <v>4.21</v>
       </c>
       <c r="F190" t="n">
-        <v>4.43</v>
+        <v>2.8</v>
       </c>
       <c r="G190" t="n">
-        <v>1.85</v>
+        <v>2.55</v>
       </c>
       <c r="H190" t="n">
-        <v>4.37</v>
+        <v>4.13</v>
       </c>
       <c r="I190" t="n">
-        <v>4.34</v>
+        <v>2.74</v>
       </c>
       <c r="J190" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>1.77, 4.17, 4.02</t>
+          <t>2.46, 3.80, 2.63</t>
         </is>
       </c>
     </row>
@@ -8382,33 +8378,33 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Fulham vs Hull City</t>
+          <t>Brentford vs Liverpool</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>1.76</v>
+        <v>2.96</v>
       </c>
       <c r="E191" t="n">
-        <v>4.42</v>
+        <v>4.05</v>
       </c>
       <c r="F191" t="n">
-        <v>5.4</v>
+        <v>2.53</v>
       </c>
       <c r="G191" t="n">
-        <v>1.72</v>
+        <v>2.9</v>
       </c>
       <c r="H191" t="n">
-        <v>4.33</v>
+        <v>3.97</v>
       </c>
       <c r="I191" t="n">
-        <v>5.3</v>
+        <v>2.48</v>
       </c>
       <c r="J191" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>1.67, 4.00, 4.85</t>
+          <t>2.77, 3.59, 2.43</t>
         </is>
       </c>
     </row>
@@ -8425,33 +8421,33 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Brentford vs Liverpool</t>
+          <t>Fulham vs Hull City</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>2.96</v>
+        <v>1.76</v>
       </c>
       <c r="E192" t="n">
-        <v>4.04</v>
+        <v>4.39</v>
       </c>
       <c r="F192" t="n">
-        <v>2.53</v>
+        <v>5.4</v>
       </c>
       <c r="G192" t="n">
-        <v>2.9</v>
+        <v>1.73</v>
       </c>
       <c r="H192" t="n">
-        <v>3.96</v>
+        <v>4.3</v>
       </c>
       <c r="I192" t="n">
-        <v>2.48</v>
+        <v>5.29</v>
       </c>
       <c r="J192" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>2.77, 3.59, 2.43</t>
+          <t>1.67, 4.00, 4.85</t>
         </is>
       </c>
     </row>
@@ -8475,22 +8471,22 @@
         <v>1.28</v>
       </c>
       <c r="E193" t="n">
-        <v>7.74</v>
+        <v>7.78</v>
       </c>
       <c r="F193" t="n">
-        <v>14.15</v>
+        <v>14.53</v>
       </c>
       <c r="G193" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="H193" t="n">
-        <v>7.59</v>
+        <v>7.63</v>
       </c>
       <c r="I193" t="n">
-        <v>13.88</v>
+        <v>14.24</v>
       </c>
       <c r="J193" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
@@ -8515,25 +8511,25 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="E194" t="n">
-        <v>5.34</v>
+        <v>5.35</v>
       </c>
       <c r="F194" t="n">
-        <v>7.29</v>
+        <v>7.16</v>
       </c>
       <c r="G194" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="H194" t="n">
         <v>5.24</v>
       </c>
       <c r="I194" t="n">
-        <v>7.15</v>
+        <v>7.02</v>
       </c>
       <c r="J194" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
@@ -8558,25 +8554,25 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>7.24</v>
+        <v>7.41</v>
       </c>
       <c r="E195" t="n">
-        <v>5.97</v>
+        <v>5.98</v>
       </c>
       <c r="F195" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="G195" t="n">
-        <v>7.1</v>
+        <v>7.26</v>
       </c>
       <c r="H195" t="n">
-        <v>5.85</v>
+        <v>5.86</v>
       </c>
       <c r="I195" t="n">
         <v>1.45</v>
       </c>
       <c r="J195" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
@@ -8601,7 +8597,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>5.76</v>
+        <v>5.75</v>
       </c>
       <c r="E196" t="n">
         <v>4.44</v>
@@ -8610,7 +8606,7 @@
         <v>1.72</v>
       </c>
       <c r="G196" t="n">
-        <v>5.65</v>
+        <v>5.64</v>
       </c>
       <c r="H196" t="n">
         <v>4.35</v>
@@ -8619,7 +8615,7 @@
         <v>1.69</v>
       </c>
       <c r="J196" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
@@ -8644,25 +8640,25 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>5.92</v>
+        <v>5.85</v>
       </c>
       <c r="E197" t="n">
-        <v>5.93</v>
+        <v>5.96</v>
       </c>
       <c r="F197" t="n">
         <v>1.56</v>
       </c>
       <c r="G197" t="n">
-        <v>5.81</v>
+        <v>5.73</v>
       </c>
       <c r="H197" t="n">
-        <v>5.81</v>
+        <v>5.84</v>
       </c>
       <c r="I197" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="J197" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K197" t="inlineStr"/>
     </row>
@@ -8674,40 +8670,36 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Newcastle United vs Aston Villa</t>
+          <t>Bayern Munich vs RB Leipzig</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>2.2</v>
+        <v>1.29</v>
       </c>
       <c r="E198" t="n">
-        <v>4.13</v>
+        <v>7.96</v>
       </c>
       <c r="F198" t="n">
-        <v>3.51</v>
+        <v>12.14</v>
       </c>
       <c r="G198" t="n">
-        <v>2.16</v>
+        <v>1.27</v>
       </c>
       <c r="H198" t="n">
-        <v>4.05</v>
+        <v>7.81</v>
       </c>
       <c r="I198" t="n">
-        <v>3.44</v>
+        <v>11.9</v>
       </c>
       <c r="J198" t="n">
-        <v>17</v>
-      </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t>2.08, 3.85, 3.21</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="K198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -8717,36 +8709,40 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Bundesliga</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Bayern Munich vs RB Leipzig</t>
+          <t>Newcastle United vs Aston Villa</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>1.3</v>
+        <v>2.19</v>
       </c>
       <c r="E199" t="n">
-        <v>7.9</v>
+        <v>4.15</v>
       </c>
       <c r="F199" t="n">
-        <v>12.2</v>
+        <v>3.53</v>
       </c>
       <c r="G199" t="n">
-        <v>1.27</v>
+        <v>2.15</v>
       </c>
       <c r="H199" t="n">
-        <v>7.75</v>
+        <v>4.07</v>
       </c>
       <c r="I199" t="n">
-        <v>11.96</v>
+        <v>3.46</v>
       </c>
       <c r="J199" t="n">
-        <v>12</v>
-      </c>
-      <c r="K199" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>2.08, 3.85, 3.21</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -8756,38 +8752,38 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>AS Roma vs Genoa</t>
+          <t>Lille vs Brest</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>1.35</v>
+        <v>1.68</v>
       </c>
       <c r="E200" t="n">
-        <v>6.31</v>
+        <v>4.63</v>
       </c>
       <c r="F200" t="n">
-        <v>12.6</v>
+        <v>5.86</v>
       </c>
       <c r="G200" t="n">
-        <v>1.32</v>
+        <v>1.65</v>
       </c>
       <c r="H200" t="n">
-        <v>6.18</v>
+        <v>4.53</v>
       </c>
       <c r="I200" t="n">
-        <v>12.36</v>
+        <v>5.75</v>
       </c>
       <c r="J200" t="n">
         <v>16</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>1.30, 5.57, 9.05</t>
+          <t>1.58, 4.20, 5.40</t>
         </is>
       </c>
     </row>
@@ -8814,10 +8810,10 @@
         <v>4.32</v>
       </c>
       <c r="F201" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="G201" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="H201" t="n">
         <v>4.24</v>
@@ -8826,7 +8822,7 @@
         <v>1.88</v>
       </c>
       <c r="J201" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
@@ -8842,38 +8838,38 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Lille vs Brest</t>
+          <t>AS Roma vs Genoa</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>1.68</v>
+        <v>1.35</v>
       </c>
       <c r="E202" t="n">
-        <v>4.63</v>
+        <v>6.25</v>
       </c>
       <c r="F202" t="n">
-        <v>5.87</v>
+        <v>12.7</v>
       </c>
       <c r="G202" t="n">
-        <v>1.65</v>
+        <v>1.32</v>
       </c>
       <c r="H202" t="n">
-        <v>4.54</v>
+        <v>6.13</v>
       </c>
       <c r="I202" t="n">
-        <v>5.75</v>
+        <v>12.45</v>
       </c>
       <c r="J202" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>1.58, 4.20, 5.40</t>
+          <t>1.30, 5.57, 9.05</t>
         </is>
       </c>
     </row>
@@ -8894,25 +8890,25 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>3.82</v>
+        <v>3.79</v>
       </c>
       <c r="E203" t="n">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="F203" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="G203" t="n">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="H203" t="n">
-        <v>3.67</v>
+        <v>3.69</v>
       </c>
       <c r="I203" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="J203" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
@@ -8937,25 +8933,25 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="E204" t="n">
-        <v>3.89</v>
+        <v>3.91</v>
       </c>
       <c r="F204" t="n">
-        <v>4.61</v>
+        <v>4.66</v>
       </c>
       <c r="G204" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="H204" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="I204" t="n">
-        <v>4.52</v>
+        <v>4.57</v>
       </c>
       <c r="J204" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K204" t="inlineStr">
         <is>
@@ -8980,22 +8976,22 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="E205" t="n">
         <v>3.97</v>
       </c>
       <c r="F205" t="n">
-        <v>4.48</v>
+        <v>4.51</v>
       </c>
       <c r="G205" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="H205" t="n">
-        <v>3.9</v>
+        <v>3.89</v>
       </c>
       <c r="I205" t="n">
-        <v>4.39</v>
+        <v>4.43</v>
       </c>
       <c r="J205" t="n">
         <v>11</v>
@@ -9014,38 +9010,38 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Angers vs Marseille</t>
+          <t>Brighton and Hove Albion vs Crystal Palace</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>3.33</v>
+        <v>1.65</v>
       </c>
       <c r="E206" t="n">
-        <v>4.03</v>
+        <v>4.86</v>
       </c>
       <c r="F206" t="n">
-        <v>2.32</v>
+        <v>5.91</v>
       </c>
       <c r="G206" t="n">
-        <v>3.27</v>
+        <v>1.62</v>
       </c>
       <c r="H206" t="n">
-        <v>3.95</v>
+        <v>4.76</v>
       </c>
       <c r="I206" t="n">
-        <v>2.27</v>
+        <v>5.79</v>
       </c>
       <c r="J206" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>3.08, 3.69, 2.20</t>
+          <t>1.58, 4.42, 5.06</t>
         </is>
       </c>
     </row>
@@ -9062,33 +9058,33 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Brighton and Hove Albion vs Crystal Palace</t>
+          <t>Leeds United vs Manchester United</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>1.65</v>
+        <v>3.04</v>
       </c>
       <c r="E207" t="n">
-        <v>4.89</v>
+        <v>4.04</v>
       </c>
       <c r="F207" t="n">
-        <v>5.92</v>
+        <v>2.48</v>
       </c>
       <c r="G207" t="n">
-        <v>1.61</v>
+        <v>2.98</v>
       </c>
       <c r="H207" t="n">
-        <v>4.79</v>
+        <v>3.96</v>
       </c>
       <c r="I207" t="n">
-        <v>5.81</v>
+        <v>2.43</v>
       </c>
       <c r="J207" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>1.58, 4.42, 5.06</t>
+          <t>2.81, 3.69, 2.37</t>
         </is>
       </c>
     </row>
@@ -9100,38 +9096,38 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Leeds United vs Manchester United</t>
+          <t>Fiorentina vs Como</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>3.04</v>
+        <v>3.72</v>
       </c>
       <c r="E208" t="n">
-        <v>4.03</v>
+        <v>3.99</v>
       </c>
       <c r="F208" t="n">
-        <v>2.48</v>
+        <v>2.17</v>
       </c>
       <c r="G208" t="n">
-        <v>2.98</v>
+        <v>3.64</v>
       </c>
       <c r="H208" t="n">
-        <v>3.95</v>
+        <v>3.91</v>
       </c>
       <c r="I208" t="n">
-        <v>2.43</v>
+        <v>2.13</v>
       </c>
       <c r="J208" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>2.81, 3.69, 2.37</t>
+          <t>3.36, 3.70, 2.07</t>
         </is>
       </c>
     </row>
@@ -9143,38 +9139,38 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Bournemouth vs Sunderland</t>
+          <t>Angers vs Marseille</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>2.11</v>
+        <v>3.32</v>
       </c>
       <c r="E209" t="n">
-        <v>3.95</v>
+        <v>4.02</v>
       </c>
       <c r="F209" t="n">
-        <v>3.97</v>
+        <v>2.32</v>
       </c>
       <c r="G209" t="n">
-        <v>2.06</v>
+        <v>3.26</v>
       </c>
       <c r="H209" t="n">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="I209" t="n">
-        <v>3.89</v>
+        <v>2.28</v>
       </c>
       <c r="J209" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>2.01, 3.58, 3.64</t>
+          <t>3.08, 3.69, 2.20</t>
         </is>
       </c>
     </row>
@@ -9186,38 +9182,38 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Fiorentina vs Como</t>
+          <t>Bournemouth vs Sunderland</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>3.73</v>
+        <v>2.1</v>
       </c>
       <c r="E210" t="n">
-        <v>3.99</v>
+        <v>3.95</v>
       </c>
       <c r="F210" t="n">
-        <v>2.17</v>
+        <v>3.97</v>
       </c>
       <c r="G210" t="n">
-        <v>3.66</v>
+        <v>2.06</v>
       </c>
       <c r="H210" t="n">
-        <v>3.91</v>
+        <v>3.88</v>
       </c>
       <c r="I210" t="n">
-        <v>2.12</v>
+        <v>3.89</v>
       </c>
       <c r="J210" t="n">
         <v>16</v>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>3.36, 3.70, 2.07</t>
+          <t>2.01, 3.58, 3.64</t>
         </is>
       </c>
     </row>
@@ -9241,22 +9237,22 @@
         <v>1.73</v>
       </c>
       <c r="E211" t="n">
-        <v>4.85</v>
+        <v>4.82</v>
       </c>
       <c r="F211" t="n">
-        <v>5.08</v>
+        <v>5.09</v>
       </c>
       <c r="G211" t="n">
         <v>1.7</v>
       </c>
       <c r="H211" t="n">
-        <v>4.75</v>
+        <v>4.73</v>
       </c>
       <c r="I211" t="n">
-        <v>4.98</v>
+        <v>4.99</v>
       </c>
       <c r="J211" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K211" t="inlineStr">
         <is>
@@ -9284,22 +9280,22 @@
         <v>2.12</v>
       </c>
       <c r="E212" t="n">
-        <v>3.69</v>
+        <v>3.73</v>
       </c>
       <c r="F212" t="n">
-        <v>4.2</v>
+        <v>4.16</v>
       </c>
       <c r="G212" t="n">
         <v>2.08</v>
       </c>
       <c r="H212" t="n">
-        <v>3.62</v>
+        <v>3.65</v>
       </c>
       <c r="I212" t="n">
-        <v>4.12</v>
+        <v>4.07</v>
       </c>
       <c r="J212" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K212" t="inlineStr">
         <is>
@@ -9320,33 +9316,33 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Paris FC vs Rennes</t>
+          <t>Le Havre vs Auxerre</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="E213" t="n">
-        <v>3.81</v>
+        <v>3.73</v>
       </c>
       <c r="F213" t="n">
-        <v>3.32</v>
+        <v>3.1</v>
       </c>
       <c r="G213" t="n">
-        <v>2.35</v>
+        <v>2.51</v>
       </c>
       <c r="H213" t="n">
-        <v>3.74</v>
+        <v>3.66</v>
       </c>
       <c r="I213" t="n">
-        <v>3.26</v>
+        <v>3.04</v>
       </c>
       <c r="J213" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>2.31, 3.23, 3.25</t>
+          <t>2.43, 3.40, 2.90</t>
         </is>
       </c>
     </row>
@@ -9363,33 +9359,33 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Le Havre vs Auxerre</t>
+          <t>Lorient vs AS Monaco</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>2.55</v>
+        <v>3.83</v>
       </c>
       <c r="E214" t="n">
-        <v>3.73</v>
+        <v>3.78</v>
       </c>
       <c r="F214" t="n">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="G214" t="n">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="H214" t="n">
-        <v>3.66</v>
+        <v>3.71</v>
       </c>
       <c r="I214" t="n">
-        <v>3.05</v>
+        <v>2.16</v>
       </c>
       <c r="J214" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>2.43, 3.40, 2.90</t>
+          <t>3.57, 3.40, 2.10</t>
         </is>
       </c>
     </row>
@@ -9406,33 +9402,33 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Lorient vs AS Monaco</t>
+          <t>Paris FC vs Rennes</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>3.83</v>
+        <v>2.4</v>
       </c>
       <c r="E215" t="n">
-        <v>3.78</v>
+        <v>3.82</v>
       </c>
       <c r="F215" t="n">
-        <v>2.2</v>
+        <v>3.32</v>
       </c>
       <c r="G215" t="n">
-        <v>3.76</v>
+        <v>2.35</v>
       </c>
       <c r="H215" t="n">
-        <v>3.71</v>
+        <v>3.74</v>
       </c>
       <c r="I215" t="n">
-        <v>2.15</v>
+        <v>3.26</v>
       </c>
       <c r="J215" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>3.57, 3.40, 2.10</t>
+          <t>2.31, 3.23, 3.25</t>
         </is>
       </c>
     </row>
@@ -9453,16 +9449,16 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>6.55</v>
+        <v>6.58</v>
       </c>
       <c r="E216" t="n">
         <v>4.33</v>
       </c>
       <c r="F216" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="G216" t="n">
-        <v>6.42</v>
+        <v>6.45</v>
       </c>
       <c r="H216" t="n">
         <v>4.24</v>
@@ -9471,7 +9467,7 @@
         <v>1.64</v>
       </c>
       <c r="J216" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K216" t="inlineStr">
         <is>
@@ -9496,25 +9492,25 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>3.82</v>
+        <v>3.79</v>
       </c>
       <c r="E217" t="n">
-        <v>4.59</v>
+        <v>4.57</v>
       </c>
       <c r="F217" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="G217" t="n">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="H217" t="n">
-        <v>4.5</v>
+        <v>4.48</v>
       </c>
       <c r="I217" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="J217" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K217" t="inlineStr">
         <is>
@@ -9542,26 +9538,26 @@
         <v>1.97</v>
       </c>
       <c r="E218" t="n">
-        <v>3.98</v>
+        <v>3.99</v>
       </c>
       <c r="F218" t="n">
-        <v>4.51</v>
+        <v>4.49</v>
       </c>
       <c r="G218" t="n">
         <v>1.93</v>
       </c>
       <c r="H218" t="n">
-        <v>3.91</v>
+        <v>3.92</v>
       </c>
       <c r="I218" t="n">
-        <v>4.42</v>
+        <v>4.4</v>
       </c>
       <c r="J218" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>1.87, 3.61, 4.17</t>
+          <t>1.85, 3.65, 4.16</t>
         </is>
       </c>
     </row>
@@ -9600,7 +9596,7 @@
         <v>2.29</v>
       </c>
       <c r="J219" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K219" t="inlineStr">
         <is>
@@ -9628,22 +9624,22 @@
         <v>1.74</v>
       </c>
       <c r="E220" t="n">
-        <v>4.21</v>
+        <v>4.22</v>
       </c>
       <c r="F220" t="n">
-        <v>6</v>
+        <v>5.98</v>
       </c>
       <c r="G220" t="n">
         <v>1.7</v>
       </c>
       <c r="H220" t="n">
-        <v>4.12</v>
+        <v>4.14</v>
       </c>
       <c r="I220" t="n">
-        <v>5.88</v>
+        <v>5.86</v>
       </c>
       <c r="J220" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K220" t="inlineStr">
         <is>
@@ -9668,25 +9664,25 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="E221" t="n">
-        <v>4.48</v>
+        <v>4.47</v>
       </c>
       <c r="F221" t="n">
-        <v>5.54</v>
+        <v>5.53</v>
       </c>
       <c r="G221" t="n">
         <v>1.7</v>
       </c>
       <c r="H221" t="n">
-        <v>4.39</v>
+        <v>4.38</v>
       </c>
       <c r="I221" t="n">
-        <v>5.43</v>
+        <v>5.42</v>
       </c>
       <c r="J221" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K221" t="inlineStr">
         <is>
@@ -9714,22 +9710,22 @@
         <v>1.3</v>
       </c>
       <c r="E222" t="n">
-        <v>7.25</v>
+        <v>7.36</v>
       </c>
       <c r="F222" t="n">
-        <v>13.45</v>
+        <v>13.46</v>
       </c>
       <c r="G222" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="H222" t="n">
-        <v>7.11</v>
+        <v>7.21</v>
       </c>
       <c r="I222" t="n">
-        <v>13.19</v>
+        <v>13.2</v>
       </c>
       <c r="J222" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K222" t="inlineStr"/>
     </row>
@@ -9750,29 +9746,29 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="E223" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="F223" t="n">
-        <v>4.07</v>
+        <v>3.93</v>
       </c>
       <c r="G223" t="n">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="H223" t="n">
-        <v>3.43</v>
+        <v>3.47</v>
       </c>
       <c r="I223" t="n">
-        <v>3.99</v>
+        <v>3.86</v>
       </c>
       <c r="J223" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>2.15, 3.12, 3.78</t>
+          <t>2.16, 3.18, 3.65</t>
         </is>
       </c>
     </row>
@@ -9796,7 +9792,7 @@
         <v>3.34</v>
       </c>
       <c r="E224" t="n">
-        <v>3.43</v>
+        <v>3.42</v>
       </c>
       <c r="F224" t="n">
         <v>2.57</v>
@@ -9805,17 +9801,17 @@
         <v>3.27</v>
       </c>
       <c r="H224" t="n">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="I224" t="n">
         <v>2.52</v>
       </c>
       <c r="J224" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>3.18, 3.07, 2.44</t>
+          <t>3.20, 3.01, 2.47</t>
         </is>
       </c>
     </row>
@@ -9827,38 +9823,38 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Getafe vs Rayo Vallecano</t>
+          <t>Tottenham Hotspur vs Coventry City</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>2.79</v>
+        <v>1.56</v>
       </c>
       <c r="E225" t="n">
-        <v>3.39</v>
+        <v>5.06</v>
       </c>
       <c r="F225" t="n">
-        <v>3.06</v>
+        <v>7.04</v>
       </c>
       <c r="G225" t="n">
-        <v>2.74</v>
+        <v>1.53</v>
       </c>
       <c r="H225" t="n">
-        <v>3.32</v>
+        <v>4.96</v>
       </c>
       <c r="I225" t="n">
-        <v>3</v>
+        <v>6.9</v>
       </c>
       <c r="J225" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>2.47, 3.10, 2.68</t>
+          <t>1.50, 4.56, 5.87</t>
         </is>
       </c>
     </row>
@@ -9870,38 +9866,38 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur vs Coventry City</t>
+          <t>Getafe vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>1.56</v>
+        <v>2.79</v>
       </c>
       <c r="E226" t="n">
-        <v>5.06</v>
+        <v>3.39</v>
       </c>
       <c r="F226" t="n">
-        <v>7.06</v>
+        <v>3.06</v>
       </c>
       <c r="G226" t="n">
-        <v>1.53</v>
+        <v>2.73</v>
       </c>
       <c r="H226" t="n">
-        <v>4.96</v>
+        <v>3.33</v>
       </c>
       <c r="I226" t="n">
-        <v>6.92</v>
+        <v>3</v>
       </c>
       <c r="J226" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>1.50, 4.56, 5.87</t>
+          <t>2.47, 3.10, 2.68</t>
         </is>
       </c>
     </row>

--- a/precios_objetivo.xlsx
+++ b/precios_objetivo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K182"/>
+  <dimension ref="A1:K170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -489,738 +489,738 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>vie 30/10 12:00</t>
+          <t>sáb 31/10 06:30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Le Havre vs Paris Saint Germain</t>
+          <t>Chelsea vs Manchester United</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11.88</v>
+        <v>2.32</v>
       </c>
       <c r="E2" t="n">
-        <v>7.37</v>
+        <v>3.87</v>
       </c>
       <c r="F2" t="n">
-        <v>1.31</v>
+        <v>3.43</v>
       </c>
       <c r="G2" t="n">
-        <v>11.65</v>
+        <v>2.28</v>
       </c>
       <c r="H2" t="n">
-        <v>7.22</v>
+        <v>3.8</v>
       </c>
       <c r="I2" t="n">
-        <v>1.29</v>
+        <v>3.37</v>
       </c>
       <c r="J2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>9.59, 6.69, 1.27</t>
+          <t>2.25, 3.76, 3.18</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>vie 30/10 12:00</t>
+          <t>sáb 31/10 07:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Nice vs Rennes</t>
+          <t>Levante vs Atlético Madrid</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2.9</v>
+        <v>6.87</v>
       </c>
       <c r="E3" t="n">
-        <v>4.1</v>
+        <v>5.27</v>
       </c>
       <c r="F3" t="n">
-        <v>2.55</v>
+        <v>1.55</v>
       </c>
       <c r="G3" t="n">
-        <v>2.85</v>
+        <v>6.74</v>
       </c>
       <c r="H3" t="n">
-        <v>4.02</v>
+        <v>5.17</v>
       </c>
       <c r="I3" t="n">
-        <v>2.5</v>
+        <v>1.52</v>
       </c>
       <c r="J3" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2.74, 3.82, 2.45</t>
+          <t>6.40, 4.85, 1.50</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>vie 30/10 13:30</t>
+          <t>sáb 31/10 08:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bundesliga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Elversberg vs FSV Mainz 05</t>
+          <t>Bologna vs Monza</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3.35</v>
+        <v>1.78</v>
       </c>
       <c r="E4" t="n">
-        <v>4.25</v>
+        <v>4.22</v>
       </c>
       <c r="F4" t="n">
-        <v>2.24</v>
+        <v>5.51</v>
       </c>
       <c r="G4" t="n">
-        <v>3.29</v>
+        <v>1.75</v>
       </c>
       <c r="H4" t="n">
-        <v>4.17</v>
+        <v>4.13</v>
       </c>
       <c r="I4" t="n">
-        <v>2.19</v>
+        <v>5.4</v>
       </c>
       <c r="J4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>3.11, 3.89, 2.20</t>
+          <t>1.72, 3.92, 5.16</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>vie 30/10 14:00</t>
+          <t>sáb 31/10 08:30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Villarreal vs Espanyol</t>
+          <t>Borussia Monchengladbach vs SC Paderborn</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.47</v>
+        <v>2.28</v>
       </c>
       <c r="E5" t="n">
-        <v>5.73</v>
+        <v>4.16</v>
       </c>
       <c r="F5" t="n">
-        <v>8.050000000000001</v>
+        <v>3.31</v>
       </c>
       <c r="G5" t="n">
-        <v>1.44</v>
+        <v>2.24</v>
       </c>
       <c r="H5" t="n">
-        <v>5.62</v>
+        <v>4.08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.89</v>
+        <v>3.25</v>
       </c>
       <c r="J5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.41, 5.25, 7.19</t>
+          <t>2.20, 3.85, 3.21</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>vie 30/10 14:05</t>
+          <t>sáb 31/10 08:30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lille vs RC Lens</t>
+          <t>FC Schalke 04 vs RB Leipzig</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2.82</v>
+        <v>4.4</v>
       </c>
       <c r="E6" t="n">
-        <v>3.78</v>
+        <v>4.3</v>
       </c>
       <c r="F6" t="n">
-        <v>2.77</v>
+        <v>1.92</v>
       </c>
       <c r="G6" t="n">
-        <v>2.76</v>
+        <v>4.32</v>
       </c>
       <c r="H6" t="n">
-        <v>3.71</v>
+        <v>4.22</v>
       </c>
       <c r="I6" t="n">
-        <v>2.72</v>
+        <v>1.88</v>
       </c>
       <c r="J6" t="n">
         <v>19</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2.78, 3.48, 2.59</t>
+          <t>4.28, 3.91, 1.86</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>vie 30/10 16:00</t>
+          <t>sáb 31/10 08:30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Argentina Primera</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estudiantes de Río Cuarto vs Gimnasia La Plata</t>
+          <t>Werder Bremen vs TSG Hoffenheim</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.08</v>
+        <v>2.63</v>
       </c>
       <c r="E7" t="n">
-        <v>3.65</v>
+        <v>4.27</v>
       </c>
       <c r="F7" t="n">
-        <v>1.96</v>
+        <v>2.74</v>
       </c>
       <c r="G7" t="n">
-        <v>4.98</v>
+        <v>2.58</v>
       </c>
       <c r="H7" t="n">
-        <v>3.57</v>
+        <v>4.18</v>
       </c>
       <c r="I7" t="n">
-        <v>1.93</v>
+        <v>2.68</v>
       </c>
       <c r="J7" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>4.53, 3.37, 1.92</t>
+          <t>2.50, 3.94, 2.69</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>vie 30/10 16:00</t>
+          <t>sáb 31/10 08:30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Argentina Primera</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlético Huracán vs CA Tigre BA</t>
+          <t>Bayer Leverkusen vs VfB Stuttgart</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2.38</v>
+        <v>1.75</v>
       </c>
       <c r="E8" t="n">
-        <v>3.22</v>
+        <v>4.99</v>
       </c>
       <c r="F8" t="n">
-        <v>3.99</v>
+        <v>4.81</v>
       </c>
       <c r="G8" t="n">
-        <v>2.34</v>
+        <v>1.71</v>
       </c>
       <c r="H8" t="n">
-        <v>3.16</v>
+        <v>4.89</v>
       </c>
       <c r="I8" t="n">
-        <v>3.92</v>
+        <v>4.72</v>
       </c>
       <c r="J8" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2.33, 2.99, 3.67</t>
+          <t>1.68, 4.56, 4.73</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>vie 30/10 17:00</t>
+          <t>sáb 31/10 08:30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Brasil Serie A</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Corinthians vs Mirassol</t>
+          <t>Augsburg vs SC Freiburg</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.89</v>
+        <v>3.05</v>
       </c>
       <c r="E9" t="n">
-        <v>3.95</v>
+        <v>4.08</v>
       </c>
       <c r="F9" t="n">
-        <v>5.04</v>
+        <v>2.45</v>
       </c>
       <c r="G9" t="n">
-        <v>1.86</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>3.87</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>4.94</v>
+        <v>2.4</v>
       </c>
       <c r="J9" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.85, 3.61, 4.59</t>
+          <t>2.88, 3.78, 2.42</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>vie 30/10 18:15</t>
+          <t>sáb 31/10 09:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Argentina Primera</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sarmiento de Junin vs Rosario Central</t>
+          <t>Bournemouth vs Leeds United</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4.53</v>
+        <v>2.2</v>
       </c>
       <c r="E10" t="n">
-        <v>3.67</v>
+        <v>3.66</v>
       </c>
       <c r="F10" t="n">
-        <v>2.05</v>
+        <v>3.97</v>
       </c>
       <c r="G10" t="n">
-        <v>4.44</v>
+        <v>2.16</v>
       </c>
       <c r="H10" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="I10" t="n">
-        <v>2.01</v>
+        <v>3.89</v>
       </c>
       <c r="J10" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4.21, 3.47, 1.95</t>
+          <t>2.13, 3.40, 3.81</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>vie 30/10 18:15</t>
+          <t>sáb 31/10 09:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Argentina Primera</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Racing Club vs Aldosivi Mar del Plata</t>
+          <t>Brentford vs Nottingham Forest</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.73</v>
+        <v>2.21</v>
       </c>
       <c r="E11" t="n">
-        <v>4.11</v>
+        <v>3.96</v>
       </c>
       <c r="F11" t="n">
-        <v>6.25</v>
+        <v>3.65</v>
       </c>
       <c r="G11" t="n">
-        <v>1.7</v>
+        <v>2.16</v>
       </c>
       <c r="H11" t="n">
-        <v>4.03</v>
+        <v>3.88</v>
       </c>
       <c r="I11" t="n">
-        <v>6.13</v>
+        <v>3.57</v>
       </c>
       <c r="J11" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.66, 3.90, 5.51</t>
+          <t>2.17, 3.73, 3.37</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>vie 30/10 19:00</t>
+          <t>sáb 31/10 09:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Liga MX</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlético San Luis vs Atlas</t>
+          <t>Manchester City vs Brighton and Hove Albion</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2.78</v>
+        <v>1.78</v>
       </c>
       <c r="E12" t="n">
-        <v>3.8</v>
+        <v>4.69</v>
       </c>
       <c r="F12" t="n">
-        <v>2.8</v>
+        <v>4.89</v>
       </c>
       <c r="G12" t="n">
-        <v>2.72</v>
+        <v>1.74</v>
       </c>
       <c r="H12" t="n">
-        <v>3.72</v>
+        <v>4.6</v>
       </c>
       <c r="I12" t="n">
-        <v>2.75</v>
+        <v>4.79</v>
       </c>
       <c r="J12" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2.72, 3.47, 2.64</t>
+          <t>1.74, 4.28, 4.52</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>vie 30/10 19:00</t>
+          <t>sáb 31/10 09:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Liga MX</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FC Juárez vs Querétaro</t>
+          <t>Coventry City vs Sunderland</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="E13" t="n">
-        <v>3.87</v>
+        <v>3.58</v>
       </c>
       <c r="F13" t="n">
-        <v>2.39</v>
+        <v>2.51</v>
       </c>
       <c r="G13" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="H13" t="n">
-        <v>3.8</v>
+        <v>3.51</v>
       </c>
       <c r="I13" t="n">
-        <v>2.35</v>
+        <v>2.46</v>
       </c>
       <c r="J13" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>3.03, 3.56, 2.35</t>
+          <t>3.16, 3.36, 2.43</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>vie 30/10 21:00</t>
+          <t>sáb 31/10 09:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Liga MX</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Puebla vs Pumas</t>
+          <t>Hull City vs Ipswich Town</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3.5</v>
+        <v>3.01</v>
       </c>
       <c r="E14" t="n">
-        <v>3.91</v>
+        <v>3.65</v>
       </c>
       <c r="F14" t="n">
-        <v>2.28</v>
+        <v>2.68</v>
       </c>
       <c r="G14" t="n">
-        <v>3.43</v>
+        <v>2.95</v>
       </c>
       <c r="H14" t="n">
-        <v>3.83</v>
+        <v>3.58</v>
       </c>
       <c r="I14" t="n">
-        <v>2.23</v>
+        <v>2.62</v>
       </c>
       <c r="J14" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>3.33, 3.65, 2.16</t>
+          <t>2.92, 3.33, 2.62</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>sáb 31/10 06:30</t>
+          <t>sáb 31/10 09:15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chelsea vs Manchester United</t>
+          <t>Rayo Vallecano vs Celta Vigo</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.91</v>
+        <v>2.65</v>
       </c>
       <c r="E15" t="n">
-        <v>4.29</v>
+        <v>3.44</v>
       </c>
       <c r="F15" t="n">
-        <v>4.46</v>
+        <v>3.2</v>
       </c>
       <c r="G15" t="n">
-        <v>1.87</v>
+        <v>2.6</v>
       </c>
       <c r="H15" t="n">
-        <v>4.21</v>
+        <v>3.37</v>
       </c>
       <c r="I15" t="n">
-        <v>4.37</v>
+        <v>3.14</v>
       </c>
       <c r="J15" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1.84, 4.01, 4.14</t>
+          <t>2.59, 3.22, 3.05</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>sáb 31/10 07:00</t>
+          <t>sáb 31/10 11:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Levante vs Atlético Madrid</t>
+          <t>Udinese vs AS Roma</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5.92</v>
+        <v>6.11</v>
       </c>
       <c r="E16" t="n">
-        <v>5.06</v>
+        <v>4.8</v>
       </c>
       <c r="F16" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="G16" t="n">
-        <v>5.8</v>
+        <v>5.99</v>
       </c>
       <c r="H16" t="n">
-        <v>4.96</v>
+        <v>4.7</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="J16" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>5.25, 4.89, 1.56</t>
+          <t>5.48, 4.44, 1.61</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>sáb 31/10 08:00</t>
+          <t>sáb 31/10 11:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>MLS</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bologna vs Monza</t>
+          <t>Charlotte FC vs Orlando City SC</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.79</v>
+        <v>1.96</v>
       </c>
       <c r="E17" t="n">
-        <v>4.26</v>
+        <v>4.89</v>
       </c>
       <c r="F17" t="n">
-        <v>5.37</v>
+        <v>3.77</v>
       </c>
       <c r="G17" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="H17" t="n">
-        <v>4.18</v>
+        <v>4.8</v>
       </c>
       <c r="I17" t="n">
-        <v>5.27</v>
+        <v>3.7</v>
       </c>
       <c r="J17" t="n">
         <v>20</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1.72, 4.04, 4.91</t>
+          <t>1.88, 4.51, 3.52</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>sáb 31/10 08:30</t>
+          <t>sáb 31/10 11:30</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bundesliga</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Werder Bremen vs TSG Hoffenheim</t>
+          <t>Real Betis vs Málaga</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.05</v>
+        <v>1.36</v>
       </c>
       <c r="E18" t="n">
-        <v>4.31</v>
+        <v>6.58</v>
       </c>
       <c r="F18" t="n">
-        <v>2.38</v>
+        <v>10.97</v>
       </c>
       <c r="G18" t="n">
-        <v>2.99</v>
+        <v>1.33</v>
       </c>
       <c r="H18" t="n">
-        <v>4.22</v>
+        <v>6.46</v>
       </c>
       <c r="I18" t="n">
-        <v>2.33</v>
+        <v>10.75</v>
       </c>
       <c r="J18" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2.86, 3.95, 2.32</t>
+          <t>1.32, 5.92, 9.72</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>sáb 31/10 08:30</t>
+          <t>sáb 31/10 11:30</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1230,857 +1230,857 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FC Schalke 04 vs RB Leipzig</t>
+          <t>Bayern Munich vs Borussia Dortmund</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>4.28</v>
+        <v>1.38</v>
       </c>
       <c r="E19" t="n">
-        <v>4.37</v>
+        <v>6.63</v>
       </c>
       <c r="F19" t="n">
-        <v>1.93</v>
+        <v>9.52</v>
       </c>
       <c r="G19" t="n">
-        <v>4.2</v>
+        <v>1.35</v>
       </c>
       <c r="H19" t="n">
-        <v>4.28</v>
+        <v>6.5</v>
       </c>
       <c r="I19" t="n">
-        <v>1.89</v>
+        <v>9.33</v>
       </c>
       <c r="J19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>4.15, 3.85, 1.87</t>
+          <t>1.32, 6.17, 8.74</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>sáb 31/10 08:30</t>
+          <t>sáb 31/10 11:30</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bundesliga</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Borussia Monchengladbach vs SC Paderborn</t>
+          <t>Tottenham Hotspur vs Crystal Palace</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.08</v>
+        <v>1.72</v>
       </c>
       <c r="E20" t="n">
-        <v>4.33</v>
+        <v>4.54</v>
       </c>
       <c r="F20" t="n">
-        <v>3.73</v>
+        <v>5.56</v>
       </c>
       <c r="G20" t="n">
-        <v>2.04</v>
+        <v>1.69</v>
       </c>
       <c r="H20" t="n">
-        <v>4.25</v>
+        <v>4.45</v>
       </c>
       <c r="I20" t="n">
-        <v>3.66</v>
+        <v>5.45</v>
       </c>
       <c r="J20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2.01, 3.97, 3.50</t>
+          <t>1.69, 4.16, 5.06</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>sáb 31/10 08:30</t>
+          <t>sáb 31/10 12:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bundesliga</t>
+          <t>MLS</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen vs VfB Stuttgart</t>
+          <t>Columbus Crew SC vs D.C. United</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1.87</v>
+        <v>1.47</v>
       </c>
       <c r="E21" t="n">
-        <v>4.84</v>
+        <v>5.82</v>
       </c>
       <c r="F21" t="n">
-        <v>4.19</v>
+        <v>7.87</v>
       </c>
       <c r="G21" t="n">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="H21" t="n">
-        <v>4.74</v>
+        <v>5.71</v>
       </c>
       <c r="I21" t="n">
-        <v>4.1</v>
+        <v>7.71</v>
       </c>
       <c r="J21" t="n">
         <v>20</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.83, 4.39, 3.83</t>
+          <t>1.39, 5.41, 7.33</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>sáb 31/10 08:30</t>
+          <t>sáb 31/10 12:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bundesliga</t>
+          <t>MLS</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Augsburg vs SC Freiburg</t>
+          <t>FC Cincinnati vs Philadelphia Union</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="E22" t="n">
-        <v>4.24</v>
+        <v>4.23</v>
       </c>
       <c r="F22" t="n">
-        <v>2.29</v>
+        <v>2.78</v>
       </c>
       <c r="G22" t="n">
-        <v>3.18</v>
+        <v>2.55</v>
       </c>
       <c r="H22" t="n">
         <v>4.15</v>
       </c>
       <c r="I22" t="n">
-        <v>2.25</v>
+        <v>2.73</v>
       </c>
       <c r="J22" t="n">
         <v>20</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>3.12, 3.85, 2.21</t>
+          <t>2.49, 3.92, 2.64</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>sáb 31/10 09:00</t>
+          <t>sáb 31/10 12:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>MLS</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brentford vs Nottingham Forest</t>
+          <t>New York City FC vs CF Montreal</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2.16</v>
+        <v>1.49</v>
       </c>
       <c r="E23" t="n">
-        <v>4.02</v>
+        <v>5.47</v>
       </c>
       <c r="F23" t="n">
-        <v>3.71</v>
+        <v>7.81</v>
       </c>
       <c r="G23" t="n">
-        <v>2.12</v>
+        <v>1.46</v>
       </c>
       <c r="H23" t="n">
-        <v>3.95</v>
+        <v>5.36</v>
       </c>
       <c r="I23" t="n">
-        <v>3.64</v>
+        <v>7.65</v>
       </c>
       <c r="J23" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2.11, 3.75, 3.42</t>
+          <t>1.46, 4.86, 6.68</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>sáb 31/10 09:00</t>
+          <t>sáb 31/10 13:00</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>MLS</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Manchester City vs Brighton and Hove Albion</t>
+          <t>Sporting Kansas City vs FC Dallas</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1.7</v>
+        <v>4.11</v>
       </c>
       <c r="E24" t="n">
-        <v>4.98</v>
+        <v>4.51</v>
       </c>
       <c r="F24" t="n">
-        <v>5.22</v>
+        <v>1.94</v>
       </c>
       <c r="G24" t="n">
-        <v>1.67</v>
+        <v>4.03</v>
       </c>
       <c r="H24" t="n">
-        <v>4.88</v>
+        <v>4.42</v>
       </c>
       <c r="I24" t="n">
-        <v>5.12</v>
+        <v>1.9</v>
       </c>
       <c r="J24" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.64, 4.64, 4.74</t>
+          <t>3.76, 4.15, 1.88</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>sáb 31/10 09:00</t>
+          <t>sáb 31/10 13:00</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Brasil Serie A</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Coventry City vs Sunderland</t>
+          <t>Coritiba vs Vitoria</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3.33</v>
+        <v>2.35</v>
       </c>
       <c r="E25" t="n">
-        <v>3.64</v>
+        <v>3.74</v>
       </c>
       <c r="F25" t="n">
-        <v>2.47</v>
+        <v>3.47</v>
       </c>
       <c r="G25" t="n">
-        <v>3.26</v>
+        <v>2.31</v>
       </c>
       <c r="H25" t="n">
-        <v>3.56</v>
+        <v>3.67</v>
       </c>
       <c r="I25" t="n">
-        <v>2.42</v>
+        <v>3.4</v>
       </c>
       <c r="J25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>3.18, 3.39, 2.36</t>
+          <t>2.23, 3.56, 3.32</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>sáb 31/10 09:00</t>
+          <t>sáb 31/10 13:00</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>MLS</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hull City vs Ipswich Town</t>
+          <t>St. Louis City SC vs San Diego FC</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2.8</v>
+        <v>1.98</v>
       </c>
       <c r="E26" t="n">
-        <v>3.64</v>
+        <v>4.76</v>
       </c>
       <c r="F26" t="n">
-        <v>2.87</v>
+        <v>3.79</v>
       </c>
       <c r="G26" t="n">
-        <v>2.75</v>
+        <v>1.94</v>
       </c>
       <c r="H26" t="n">
-        <v>3.57</v>
+        <v>4.66</v>
       </c>
       <c r="I26" t="n">
-        <v>2.81</v>
+        <v>3.71</v>
       </c>
       <c r="J26" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2.69, 3.41, 2.72</t>
+          <t>1.92, 4.47, 3.42</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>sáb 31/10 09:00</t>
+          <t>sáb 31/10 13:45</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bournemouth vs Leeds United</t>
+          <t>AC Milan vs Inter Milan</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2.24</v>
+        <v>3.89</v>
       </c>
       <c r="E27" t="n">
-        <v>3.71</v>
+        <v>3.92</v>
       </c>
       <c r="F27" t="n">
-        <v>3.78</v>
+        <v>2.13</v>
       </c>
       <c r="G27" t="n">
-        <v>2.2</v>
+        <v>3.82</v>
       </c>
       <c r="H27" t="n">
-        <v>3.64</v>
+        <v>3.85</v>
       </c>
       <c r="I27" t="n">
-        <v>3.7</v>
+        <v>2.09</v>
       </c>
       <c r="J27" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2.20, 3.41, 3.50</t>
+          <t>3.73, 3.69, 2.05</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>sáb 31/10 09:15</t>
+          <t>sáb 31/10 13:45</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Rayo Vallecano vs Celta Vigo</t>
+          <t>Troyes vs Le Mans FC</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2.54</v>
+        <v>2.34</v>
       </c>
       <c r="E28" t="n">
-        <v>3.54</v>
+        <v>3.64</v>
       </c>
       <c r="F28" t="n">
-        <v>3.29</v>
+        <v>3.58</v>
       </c>
       <c r="G28" t="n">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="H28" t="n">
-        <v>3.47</v>
+        <v>3.57</v>
       </c>
       <c r="I28" t="n">
-        <v>3.23</v>
+        <v>3.51</v>
       </c>
       <c r="J28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2.45, 3.32, 3.09</t>
+          <t>2.26, 3.38, 3.49</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>sáb 31/10 11:00</t>
+          <t>sáb 31/10 14:00</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Udinese vs AS Roma</t>
+          <t>Barcelona vs Alavés</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6.42</v>
+        <v>1.14</v>
       </c>
       <c r="E29" t="n">
-        <v>4.9</v>
+        <v>13.42</v>
       </c>
       <c r="F29" t="n">
-        <v>1.61</v>
+        <v>31.18</v>
       </c>
       <c r="G29" t="n">
-        <v>6.3</v>
+        <v>1.12</v>
       </c>
       <c r="H29" t="n">
-        <v>4.8</v>
+        <v>13.15</v>
       </c>
       <c r="I29" t="n">
-        <v>1.58</v>
+        <v>30.56</v>
       </c>
       <c r="J29" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>5.67, 4.54, 1.57</t>
+          <t>1.11, 11.16, 21.87</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>sáb 31/10 11:00</t>
+          <t>sáb 31/10 14:00</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Charlotte FC vs Orlando City SC</t>
+          <t>Aston Villa vs Fulham</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1.97</v>
+        <v>2.23</v>
       </c>
       <c r="E30" t="n">
-        <v>4.85</v>
+        <v>3.86</v>
       </c>
       <c r="F30" t="n">
-        <v>3.75</v>
+        <v>3.66</v>
       </c>
       <c r="G30" t="n">
-        <v>1.93</v>
+        <v>2.19</v>
       </c>
       <c r="H30" t="n">
-        <v>4.75</v>
+        <v>3.78</v>
       </c>
       <c r="I30" t="n">
-        <v>3.68</v>
+        <v>3.59</v>
       </c>
       <c r="J30" t="n">
         <v>21</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1.84, 4.49, 3.46</t>
+          <t>2.18, 3.62, 3.44</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>sáb 31/10 11:30</t>
+          <t>sáb 31/10 14:00</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Argentina Primera</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur vs Crystal Palace</t>
+          <t>Deportivo Riestra vs Talleres</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1.61</v>
+        <v>2.5</v>
       </c>
       <c r="E31" t="n">
-        <v>4.96</v>
+        <v>3.27</v>
       </c>
       <c r="F31" t="n">
-        <v>6.32</v>
+        <v>3.64</v>
       </c>
       <c r="G31" t="n">
-        <v>1.58</v>
+        <v>2.45</v>
       </c>
       <c r="H31" t="n">
-        <v>4.86</v>
+        <v>3.21</v>
       </c>
       <c r="I31" t="n">
-        <v>6.19</v>
+        <v>3.57</v>
       </c>
       <c r="J31" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1.58, 4.55, 5.45</t>
+          <t>2.48, 3.07, 3.31</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>sáb 31/10 11:30</t>
+          <t>sáb 31/10 15:00</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>MLS</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Real Betis vs Málaga</t>
+          <t>LA Galaxy vs Austin FC</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="E32" t="n">
-        <v>6.18</v>
+        <v>5.62</v>
       </c>
       <c r="F32" t="n">
-        <v>9.550000000000001</v>
+        <v>6.53</v>
       </c>
       <c r="G32" t="n">
-        <v>1.37</v>
+        <v>1.51</v>
       </c>
       <c r="H32" t="n">
-        <v>6.06</v>
+        <v>5.51</v>
       </c>
       <c r="I32" t="n">
-        <v>9.369999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="J32" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1.34, 5.75, 8.32</t>
+          <t>1.48, 5.13, 5.93</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>sáb 31/10 11:30</t>
+          <t>sáb 31/10 15:00</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Bundesliga</t>
+          <t>MLS</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bayern Munich vs Borussia Dortmund</t>
+          <t>San Jose Earthquakes vs Real Salt Lake</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1.38</v>
+        <v>2.48</v>
       </c>
       <c r="E33" t="n">
-        <v>6.63</v>
+        <v>4.23</v>
       </c>
       <c r="F33" t="n">
-        <v>9.31</v>
+        <v>2.93</v>
       </c>
       <c r="G33" t="n">
-        <v>1.36</v>
+        <v>2.44</v>
       </c>
       <c r="H33" t="n">
-        <v>6.5</v>
+        <v>4.15</v>
       </c>
       <c r="I33" t="n">
-        <v>9.130000000000001</v>
+        <v>2.87</v>
       </c>
       <c r="J33" t="n">
         <v>20</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1.34, 5.71, 8.53</t>
+          <t>2.41, 3.94, 2.72</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>sáb 31/10 12:00</t>
+          <t>sáb 31/10 16:15</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Argentina Primera</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FC Cincinnati vs Philadelphia Union</t>
+          <t>Velez Sarsfield BA vs San Lorenzo</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.63</v>
+        <v>2.03</v>
       </c>
       <c r="E34" t="n">
-        <v>4.47</v>
+        <v>3.57</v>
       </c>
       <c r="F34" t="n">
-        <v>2.66</v>
+        <v>4.82</v>
       </c>
       <c r="G34" t="n">
-        <v>2.58</v>
+        <v>1.99</v>
       </c>
       <c r="H34" t="n">
-        <v>4.38</v>
+        <v>3.5</v>
       </c>
       <c r="I34" t="n">
-        <v>2.61</v>
+        <v>4.73</v>
       </c>
       <c r="J34" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2.42, 4.05, 2.55</t>
+          <t>1.96, 3.39, 4.42</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>sáb 31/10 12:00</t>
+          <t>sáb 31/10 17:00</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Liga MX</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York City FC vs CF Montreal</t>
+          <t>Pachuca vs Tigres</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1.48</v>
+        <v>2.34</v>
       </c>
       <c r="E35" t="n">
-        <v>5.52</v>
+        <v>3.83</v>
       </c>
       <c r="F35" t="n">
-        <v>8.140000000000001</v>
+        <v>3.42</v>
       </c>
       <c r="G35" t="n">
-        <v>1.45</v>
+        <v>2.29</v>
       </c>
       <c r="H35" t="n">
-        <v>5.41</v>
+        <v>3.75</v>
       </c>
       <c r="I35" t="n">
-        <v>7.98</v>
+        <v>3.36</v>
       </c>
       <c r="J35" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1.40, 4.96, 6.79</t>
+          <t>2.22, 3.61, 3.29</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>sáb 31/10 12:00</t>
+          <t>sáb 31/10 18:30</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Argentina Primera</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Columbus Crew SC vs D.C. United</t>
+          <t>Estudiantes vs Instituto de Córdoba</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1.4</v>
+        <v>1.98</v>
       </c>
       <c r="E36" t="n">
-        <v>6.33</v>
+        <v>3.55</v>
       </c>
       <c r="F36" t="n">
-        <v>9.25</v>
+        <v>5.16</v>
       </c>
       <c r="G36" t="n">
-        <v>1.37</v>
+        <v>1.94</v>
       </c>
       <c r="H36" t="n">
-        <v>6.2</v>
+        <v>3.48</v>
       </c>
       <c r="I36" t="n">
-        <v>9.07</v>
+        <v>5.06</v>
       </c>
       <c r="J36" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1.34, 5.58, 7.56</t>
+          <t>1.93, 3.28, 4.73</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>sáb 31/10 13:00</t>
+          <t>sáb 31/10 19:05</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Brasil Serie A</t>
+          <t>Liga MX</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Coritiba vs Vitoria</t>
+          <t>Monterrey vs Tijuana</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2.43</v>
+        <v>1.63</v>
       </c>
       <c r="E37" t="n">
-        <v>3.71</v>
+        <v>4.85</v>
       </c>
       <c r="F37" t="n">
-        <v>3.33</v>
+        <v>6.26</v>
       </c>
       <c r="G37" t="n">
-        <v>2.39</v>
+        <v>1.6</v>
       </c>
       <c r="H37" t="n">
-        <v>3.64</v>
+        <v>4.76</v>
       </c>
       <c r="I37" t="n">
-        <v>3.26</v>
+        <v>6.14</v>
       </c>
       <c r="J37" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2.34, 3.41, 3.08</t>
+          <t>1.59, 4.40, 5.47</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>sáb 31/10 13:00</t>
+          <t>sáb 31/10 19:07</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Liga MX</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sporting Kansas City vs FC Dallas</t>
+          <t>Guadalajara vs Atlante FC</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>4.21</v>
+        <v>1.51</v>
       </c>
       <c r="E38" t="n">
-        <v>4.55</v>
+        <v>5.34</v>
       </c>
       <c r="F38" t="n">
-        <v>1.91</v>
+        <v>7.77</v>
       </c>
       <c r="G38" t="n">
-        <v>4.13</v>
+        <v>1.48</v>
       </c>
       <c r="H38" t="n">
-        <v>4.46</v>
+        <v>5.23</v>
       </c>
       <c r="I38" t="n">
-        <v>1.87</v>
+        <v>7.61</v>
       </c>
       <c r="J38" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>3.85, 4.14, 1.80</t>
+          <t>1.46, 4.90, 6.61</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>sáb 31/10 13:00</t>
+          <t>sáb 31/10 19:30</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2090,1502 +2090,1502 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>St. Louis City SC vs San Diego FC</t>
+          <t>Colorado Rapids vs Chicago Fire</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1.93</v>
+        <v>2.46</v>
       </c>
       <c r="E39" t="n">
-        <v>4.81</v>
+        <v>3.99</v>
       </c>
       <c r="F39" t="n">
-        <v>3.92</v>
+        <v>3.1</v>
       </c>
       <c r="G39" t="n">
-        <v>1.9</v>
+        <v>2.41</v>
       </c>
       <c r="H39" t="n">
-        <v>4.72</v>
+        <v>3.91</v>
       </c>
       <c r="I39" t="n">
-        <v>3.84</v>
+        <v>3.04</v>
       </c>
       <c r="J39" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>1.85, 4.55, 3.39</t>
+          <t>2.30, 3.71, 2.96</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>sáb 31/10 13:45</t>
+          <t>sáb 31/10 21:10</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Liga MX</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AC Milan vs Inter Milan</t>
+          <t>América vs Toluca</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>3.86</v>
+        <v>2.48</v>
       </c>
       <c r="E40" t="n">
-        <v>4.03</v>
+        <v>4.24</v>
       </c>
       <c r="F40" t="n">
-        <v>2.11</v>
+        <v>2.94</v>
       </c>
       <c r="G40" t="n">
-        <v>3.79</v>
+        <v>2.43</v>
       </c>
       <c r="H40" t="n">
-        <v>3.96</v>
+        <v>4.15</v>
       </c>
       <c r="I40" t="n">
-        <v>2.07</v>
+        <v>2.88</v>
       </c>
       <c r="J40" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>3.71, 3.76, 2.02</t>
+          <t>2.37, 3.93, 2.78</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>sáb 31/10 13:45</t>
+          <t>dom 01/11 05:30</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Troyes vs Le Mans FC</t>
+          <t>Como vs Venezia</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2.46</v>
+        <v>1.35</v>
       </c>
       <c r="E41" t="n">
-        <v>3.81</v>
+        <v>6.83</v>
       </c>
       <c r="F41" t="n">
-        <v>3.21</v>
+        <v>10.73</v>
       </c>
       <c r="G41" t="n">
-        <v>2.41</v>
+        <v>1.32</v>
       </c>
       <c r="H41" t="n">
-        <v>3.74</v>
+        <v>6.69</v>
       </c>
       <c r="I41" t="n">
-        <v>3.15</v>
+        <v>10.52</v>
       </c>
       <c r="J41" t="n">
         <v>20</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2.37, 3.51, 3.06</t>
+          <t>1.30, 6.32, 9.20</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>sáb 31/10 14:00</t>
+          <t>dom 01/11 07:00</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Argentina Primera</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Deportivo Riestra vs Talleres</t>
+          <t>Getafe vs Sevilla</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2.35</v>
+        <v>3.42</v>
       </c>
       <c r="E42" t="n">
-        <v>3.27</v>
+        <v>3.23</v>
       </c>
       <c r="F42" t="n">
-        <v>4.02</v>
+        <v>2.64</v>
       </c>
       <c r="G42" t="n">
-        <v>2.3</v>
+        <v>3.35</v>
       </c>
       <c r="H42" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="I42" t="n">
-        <v>3.95</v>
+        <v>2.59</v>
       </c>
       <c r="J42" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2.25, 3.06, 3.61</t>
+          <t>3.29, 3.03, 2.51</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>sáb 31/10 14:00</t>
+          <t>dom 01/11 08:00</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Barcelona vs Alavés</t>
+          <t>Lazio vs Cagliari</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1.14</v>
+        <v>1.51</v>
       </c>
       <c r="E43" t="n">
-        <v>12.99</v>
+        <v>5.06</v>
       </c>
       <c r="F43" t="n">
-        <v>37.9</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="G43" t="n">
-        <v>1.12</v>
+        <v>1.48</v>
       </c>
       <c r="H43" t="n">
-        <v>12.74</v>
+        <v>4.96</v>
       </c>
       <c r="I43" t="n">
-        <v>37.16</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="J43" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>1.10, 11.51, 20.85</t>
+          <t>1.46, 4.71, 7.28</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>sáb 31/10 14:00</t>
+          <t>dom 01/11 08:00</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Aston Villa vs Fulham</t>
+          <t>Strasbourg vs Auxerre</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="E44" t="n">
-        <v>4.07</v>
+        <v>4.37</v>
       </c>
       <c r="F44" t="n">
-        <v>4.03</v>
+        <v>4.41</v>
       </c>
       <c r="G44" t="n">
-        <v>2.01</v>
+        <v>1.87</v>
       </c>
       <c r="H44" t="n">
-        <v>3.99</v>
+        <v>4.29</v>
       </c>
       <c r="I44" t="n">
-        <v>3.96</v>
+        <v>4.32</v>
       </c>
       <c r="J44" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>1.98, 3.78, 3.78</t>
+          <t>1.85, 4.07, 4.00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>sáb 31/10 15:00</t>
+          <t>dom 01/11 08:00</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>LA Galaxy vs Austin FC</t>
+          <t>Frosinone vs Torino</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="E45" t="n">
-        <v>5.46</v>
+        <v>4.24</v>
       </c>
       <c r="F45" t="n">
-        <v>6.3</v>
+        <v>3.33</v>
       </c>
       <c r="G45" t="n">
-        <v>1.54</v>
+        <v>2.21</v>
       </c>
       <c r="H45" t="n">
-        <v>5.36</v>
+        <v>4.16</v>
       </c>
       <c r="I45" t="n">
-        <v>6.18</v>
+        <v>3.26</v>
       </c>
       <c r="J45" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>1.47, 4.99, 5.59</t>
+          <t>2.18, 3.96, 3.13</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>sáb 31/10 15:00</t>
+          <t>dom 01/11 08:30</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes vs Real Salt Lake</t>
+          <t>Union Berlin vs 1. FC Köln</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2.46</v>
+        <v>2.81</v>
       </c>
       <c r="E46" t="n">
-        <v>4.28</v>
+        <v>3.93</v>
       </c>
       <c r="F46" t="n">
-        <v>2.94</v>
+        <v>2.71</v>
       </c>
       <c r="G46" t="n">
-        <v>2.41</v>
+        <v>2.75</v>
       </c>
       <c r="H46" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="I46" t="n">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="J46" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2.32, 3.92, 2.73</t>
+          <t>2.76, 3.63, 2.53</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>sáb 31/10 16:15</t>
+          <t>dom 01/11 09:15</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Argentina Primera</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Velez Sarsfield BA vs San Lorenzo</t>
+          <t>Real Racing Club de Santander vs Real Madrid</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2.05</v>
+        <v>12.75</v>
       </c>
       <c r="E47" t="n">
-        <v>3.52</v>
+        <v>8.83</v>
       </c>
       <c r="F47" t="n">
-        <v>4.82</v>
+        <v>1.27</v>
       </c>
       <c r="G47" t="n">
-        <v>2.01</v>
+        <v>12.5</v>
       </c>
       <c r="H47" t="n">
-        <v>3.45</v>
+        <v>8.65</v>
       </c>
       <c r="I47" t="n">
-        <v>4.72</v>
+        <v>1.24</v>
       </c>
       <c r="J47" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>1.94, 3.29, 4.32</t>
+          <t>10.23, 7.96, 1.22</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>sáb 31/10 17:00</t>
+          <t>dom 01/11 10:15</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Liga MX</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Pachuca vs Tigres</t>
+          <t>Lyon vs Angers</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2.43</v>
+        <v>1.46</v>
       </c>
       <c r="E48" t="n">
-        <v>3.82</v>
+        <v>5.65</v>
       </c>
       <c r="F48" t="n">
-        <v>3.26</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="G48" t="n">
-        <v>2.38</v>
+        <v>1.43</v>
       </c>
       <c r="H48" t="n">
-        <v>3.75</v>
+        <v>5.54</v>
       </c>
       <c r="I48" t="n">
-        <v>3.2</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="J48" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2.26, 3.50, 3.13</t>
+          <t>1.40, 5.27, 7.48</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>sáb 31/10 18:30</t>
+          <t>dom 01/11 10:15</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Argentina Primera</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Estudiantes vs Instituto de Córdoba</t>
+          <t>Paris FC vs AS Monaco</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2.28</v>
+        <v>2.52</v>
       </c>
       <c r="E49" t="n">
-        <v>3.34</v>
+        <v>3.83</v>
       </c>
       <c r="F49" t="n">
-        <v>4.14</v>
+        <v>3.1</v>
       </c>
       <c r="G49" t="n">
-        <v>2.23</v>
+        <v>2.47</v>
       </c>
       <c r="H49" t="n">
-        <v>3.27</v>
+        <v>3.76</v>
       </c>
       <c r="I49" t="n">
-        <v>4.06</v>
+        <v>3.04</v>
       </c>
       <c r="J49" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2.20, 3.09, 3.72</t>
+          <t>2.46, 3.55, 2.90</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>sáb 31/10 19:05</t>
+          <t>dom 01/11 10:30</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Liga MX</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Monterrey vs Tijuana</t>
+          <t>Eintracht Frankfurt vs Hamburger SV</t>
         </is>
       </c>
       <c r="D50" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="E50" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="F50" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="G50" t="n">
         <v>1.61</v>
       </c>
-      <c r="E50" t="n">
-        <v>5.04</v>
-      </c>
-      <c r="F50" t="n">
-        <v>6.22</v>
-      </c>
-      <c r="G50" t="n">
-        <v>1.58</v>
-      </c>
       <c r="H50" t="n">
-        <v>4.94</v>
+        <v>5.01</v>
       </c>
       <c r="I50" t="n">
-        <v>6.1</v>
+        <v>5.61</v>
       </c>
       <c r="J50" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>1.57, 4.47, 5.15</t>
+          <t>1.58, 4.65, 5.26</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>sáb 31/10 19:07</t>
+          <t>dom 01/11 10:30</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Liga MX</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Guadalajara vs Atlante FC</t>
+          <t>Liverpool vs Arsenal</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1.56</v>
+        <v>3.1</v>
       </c>
       <c r="E51" t="n">
-        <v>5.11</v>
+        <v>3.7</v>
       </c>
       <c r="F51" t="n">
-        <v>7.04</v>
+        <v>2.58</v>
       </c>
       <c r="G51" t="n">
-        <v>1.53</v>
+        <v>3.04</v>
       </c>
       <c r="H51" t="n">
-        <v>5.01</v>
+        <v>3.63</v>
       </c>
       <c r="I51" t="n">
-        <v>6.9</v>
+        <v>2.53</v>
       </c>
       <c r="J51" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>1.48, 4.69, 6.13</t>
+          <t>2.93, 3.44, 2.49</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>sáb 31/10 19:30</t>
+          <t>dom 01/11 11:00</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Colorado Rapids vs Chicago Fire</t>
+          <t>Lecce vs Genoa</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2.41</v>
+        <v>3.57</v>
       </c>
       <c r="E52" t="n">
-        <v>4.03</v>
+        <v>3.31</v>
       </c>
       <c r="F52" t="n">
-        <v>3.15</v>
+        <v>2.51</v>
       </c>
       <c r="G52" t="n">
-        <v>2.37</v>
+        <v>3.5</v>
       </c>
       <c r="H52" t="n">
-        <v>3.95</v>
+        <v>3.24</v>
       </c>
       <c r="I52" t="n">
-        <v>3.09</v>
+        <v>2.46</v>
       </c>
       <c r="J52" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2.32, 3.60, 2.91</t>
+          <t>3.41, 3.05, 2.44</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>sáb 31/10 21:10</t>
+          <t>dom 01/11 11:30</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Liga MX</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>América vs Toluca</t>
+          <t>Elche CF vs Valencia</t>
         </is>
       </c>
       <c r="D53" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="E53" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="F53" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="G53" t="n">
         <v>2.44</v>
       </c>
-      <c r="E53" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="F53" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="G53" t="n">
-        <v>2.39</v>
-      </c>
       <c r="H53" t="n">
-        <v>4.1</v>
+        <v>3.58</v>
       </c>
       <c r="I53" t="n">
-        <v>2.95</v>
+        <v>3.21</v>
       </c>
       <c r="J53" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2.26, 3.80, 2.92</t>
+          <t>2.38, 3.41, 3.13</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>dom 01/11 05:30</t>
+          <t>dom 01/11 12:00</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Argentina Primera</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Como vs Venezia</t>
+          <t>Boca Juniors vs River Plate</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1.35</v>
+        <v>2.4</v>
       </c>
       <c r="E54" t="n">
-        <v>6.83</v>
+        <v>3.37</v>
       </c>
       <c r="F54" t="n">
-        <v>10.74</v>
+        <v>3.76</v>
       </c>
       <c r="G54" t="n">
-        <v>1.32</v>
+        <v>2.35</v>
       </c>
       <c r="H54" t="n">
-        <v>6.69</v>
+        <v>3.3</v>
       </c>
       <c r="I54" t="n">
-        <v>10.53</v>
+        <v>3.69</v>
       </c>
       <c r="J54" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>1.30, 6.33, 9.26</t>
+          <t>2.26, 3.15, 3.47</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>dom 01/11 07:00</t>
+          <t>dom 01/11 13:45</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Getafe vs Sevilla</t>
+          <t>Juventus vs Napoli</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>3.4</v>
+        <v>2.38</v>
       </c>
       <c r="E55" t="n">
-        <v>3.23</v>
+        <v>3.59</v>
       </c>
       <c r="F55" t="n">
-        <v>2.66</v>
+        <v>3.56</v>
       </c>
       <c r="G55" t="n">
-        <v>3.33</v>
+        <v>2.33</v>
       </c>
       <c r="H55" t="n">
-        <v>3.17</v>
+        <v>3.52</v>
       </c>
       <c r="I55" t="n">
-        <v>2.6</v>
+        <v>3.49</v>
       </c>
       <c r="J55" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>3.20, 3.03, 2.56</t>
+          <t>2.30, 3.31, 3.40</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>dom 01/11 08:00</t>
+          <t>dom 01/11 13:45</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Frosinone vs Torino</t>
+          <t>Marseille vs Toulouse</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2.28</v>
+        <v>2.01</v>
       </c>
       <c r="E56" t="n">
-        <v>4.23</v>
+        <v>4.38</v>
       </c>
       <c r="F56" t="n">
-        <v>3.28</v>
+        <v>3.93</v>
       </c>
       <c r="G56" t="n">
-        <v>2.23</v>
+        <v>1.97</v>
       </c>
       <c r="H56" t="n">
-        <v>4.15</v>
+        <v>4.29</v>
       </c>
       <c r="I56" t="n">
-        <v>3.22</v>
+        <v>3.86</v>
       </c>
       <c r="J56" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2.17, 4.04, 3.11</t>
+          <t>1.96, 4.06, 3.59</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>dom 01/11 08:00</t>
+          <t>dom 01/11 14:00</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Lazio vs Cagliari</t>
+          <t>Athletic Bilbao vs Real Sociedad</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1.51</v>
+        <v>2.25</v>
       </c>
       <c r="E57" t="n">
-        <v>4.97</v>
+        <v>3.98</v>
       </c>
       <c r="F57" t="n">
-        <v>8.460000000000001</v>
+        <v>3.5</v>
       </c>
       <c r="G57" t="n">
-        <v>1.48</v>
+        <v>2.21</v>
       </c>
       <c r="H57" t="n">
-        <v>4.87</v>
+        <v>3.9</v>
       </c>
       <c r="I57" t="n">
-        <v>8.300000000000001</v>
+        <v>3.43</v>
       </c>
       <c r="J57" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>1.49, 4.52, 7.00</t>
+          <t>2.16, 3.71, 3.32</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>dom 01/11 08:00</t>
+          <t>dom 01/11 14:30</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>MLS</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Strasbourg vs Auxerre</t>
+          <t>Vancouver Whitecaps FC vs Seattle Sounders FC</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1.91</v>
+        <v>1.66</v>
       </c>
       <c r="E58" t="n">
-        <v>4.38</v>
+        <v>5.04</v>
       </c>
       <c r="F58" t="n">
-        <v>4.4</v>
+        <v>5.59</v>
       </c>
       <c r="G58" t="n">
-        <v>1.87</v>
+        <v>1.63</v>
       </c>
       <c r="H58" t="n">
-        <v>4.29</v>
+        <v>4.94</v>
       </c>
       <c r="I58" t="n">
-        <v>4.32</v>
+        <v>5.48</v>
       </c>
       <c r="J58" t="n">
         <v>20</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>1.85, 4.10, 3.99</t>
+          <t>1.62, 4.48, 4.62</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>dom 01/11 08:30</t>
+          <t>dom 01/11 15:30</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Bundesliga</t>
+          <t>MLS</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Union Berlin vs 1. FC Köln</t>
+          <t>Atlanta United FC vs Toronto FC</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>2.73</v>
+        <v>2.33</v>
       </c>
       <c r="E59" t="n">
-        <v>3.99</v>
+        <v>4.36</v>
       </c>
       <c r="F59" t="n">
-        <v>2.75</v>
+        <v>3.11</v>
       </c>
       <c r="G59" t="n">
-        <v>2.68</v>
+        <v>2.28</v>
       </c>
       <c r="H59" t="n">
-        <v>3.91</v>
+        <v>4.28</v>
       </c>
       <c r="I59" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="J59" t="n">
         <v>20</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2.66, 3.72, 2.57</t>
+          <t>2.19, 3.99, 2.89</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>dom 01/11 09:15</t>
+          <t>dom 01/11 15:30</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>MLS</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Real Racing Club de Santander vs Real Madrid</t>
+          <t>Nashville SC vs New York Red Bulls</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>13.75</v>
+        <v>1.55</v>
       </c>
       <c r="E60" t="n">
-        <v>9.02</v>
+        <v>5.38</v>
       </c>
       <c r="F60" t="n">
-        <v>1.25</v>
+        <v>6.74</v>
       </c>
       <c r="G60" t="n">
-        <v>13.48</v>
+        <v>1.52</v>
       </c>
       <c r="H60" t="n">
-        <v>8.84</v>
+        <v>5.27</v>
       </c>
       <c r="I60" t="n">
-        <v>1.23</v>
+        <v>6.61</v>
       </c>
       <c r="J60" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>11.19, 8.20, 1.20</t>
+          <t>1.49, 4.70, 5.72</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>dom 01/11 10:15</t>
+          <t>dom 01/11 15:30</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Argentina Primera</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Paris FC vs AS Monaco</t>
+          <t>Newells Old Boys vs Union Santa Fe</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>2.43</v>
+        <v>2.1</v>
       </c>
       <c r="E61" t="n">
-        <v>3.84</v>
+        <v>3.61</v>
       </c>
       <c r="F61" t="n">
-        <v>3.24</v>
+        <v>4.41</v>
       </c>
       <c r="G61" t="n">
-        <v>2.38</v>
+        <v>2.06</v>
       </c>
       <c r="H61" t="n">
-        <v>3.77</v>
+        <v>3.54</v>
       </c>
       <c r="I61" t="n">
-        <v>3.18</v>
+        <v>4.32</v>
       </c>
       <c r="J61" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2.34, 3.57, 3.07</t>
+          <t>1.99, 3.40, 3.97</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>dom 01/11 10:15</t>
+          <t>dom 01/11 15:30</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Argentina Primera</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Lyon vs Angers</t>
+          <t>Belgrano de Cordoba vs Barracas Central</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1.46</v>
+        <v>1.96</v>
       </c>
       <c r="E62" t="n">
-        <v>5.66</v>
+        <v>3.59</v>
       </c>
       <c r="F62" t="n">
-        <v>8.539999999999999</v>
+        <v>5.22</v>
       </c>
       <c r="G62" t="n">
-        <v>1.43</v>
+        <v>1.92</v>
       </c>
       <c r="H62" t="n">
-        <v>5.55</v>
+        <v>3.52</v>
       </c>
       <c r="I62" t="n">
-        <v>8.369999999999999</v>
+        <v>5.12</v>
       </c>
       <c r="J62" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>1.42, 5.08, 7.04</t>
+          <t>1.93, 3.24, 4.50</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>dom 01/11 10:30</t>
+          <t>dom 01/11 17:00</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Bundesliga</t>
+          <t>Liga MX</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt vs Hamburger SV</t>
+          <t>Santos Laguna vs Necaxa</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1.66</v>
+        <v>1.92</v>
       </c>
       <c r="E63" t="n">
-        <v>5.05</v>
+        <v>4.49</v>
       </c>
       <c r="F63" t="n">
-        <v>5.52</v>
+        <v>4.23</v>
       </c>
       <c r="G63" t="n">
-        <v>1.63</v>
+        <v>1.88</v>
       </c>
       <c r="H63" t="n">
-        <v>4.95</v>
+        <v>4.4</v>
       </c>
       <c r="I63" t="n">
-        <v>5.41</v>
+        <v>4.15</v>
       </c>
       <c r="J63" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>1.60, 4.62, 5.15</t>
+          <t>1.81, 4.06, 3.97</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>dom 01/11 10:30</t>
+          <t>dom 01/11 17:45</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Argentina Primera</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Liverpool vs Arsenal</t>
+          <t>Lanus vs Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>3.17</v>
+        <v>1.64</v>
       </c>
       <c r="E64" t="n">
-        <v>3.73</v>
+        <v>4.36</v>
       </c>
       <c r="F64" t="n">
-        <v>2.52</v>
+        <v>7.06</v>
       </c>
       <c r="G64" t="n">
-        <v>3.11</v>
+        <v>1.61</v>
       </c>
       <c r="H64" t="n">
-        <v>3.66</v>
+        <v>4.27</v>
       </c>
       <c r="I64" t="n">
-        <v>2.47</v>
+        <v>6.93</v>
       </c>
       <c r="J64" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>3.00, 3.50, 2.41</t>
+          <t>1.56, 4.02, 6.05</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>dom 01/11 11:00</t>
+          <t>dom 01/11 18:00</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>MLS</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Lecce vs Genoa</t>
+          <t>New England Revolution vs Inter Miami CF</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>3.41</v>
+        <v>2.92</v>
       </c>
       <c r="E65" t="n">
-        <v>3.32</v>
+        <v>4.48</v>
       </c>
       <c r="F65" t="n">
-        <v>2.59</v>
+        <v>2.41</v>
       </c>
       <c r="G65" t="n">
-        <v>3.35</v>
+        <v>2.87</v>
       </c>
       <c r="H65" t="n">
-        <v>3.25</v>
+        <v>4.39</v>
       </c>
       <c r="I65" t="n">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="J65" t="n">
         <v>20</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>3.36, 3.10, 2.44</t>
+          <t>2.74, 4.05, 2.27</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>dom 01/11 11:30</t>
+          <t>dom 01/11 19:10</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Liga MX</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Elche CF vs Valencia</t>
+          <t>Cruz Azul vs León</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="E66" t="n">
-        <v>3.66</v>
+        <v>4.73</v>
       </c>
       <c r="F66" t="n">
-        <v>3.26</v>
+        <v>5.04</v>
       </c>
       <c r="G66" t="n">
-        <v>2.45</v>
+        <v>1.72</v>
       </c>
       <c r="H66" t="n">
-        <v>3.58</v>
+        <v>4.64</v>
       </c>
       <c r="I66" t="n">
-        <v>3.2</v>
+        <v>4.95</v>
       </c>
       <c r="J66" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2.32, 3.44, 3.21</t>
+          <t>1.67, 4.28, 4.57</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>dom 01/11 12:00</t>
+          <t>dom 01/11 19:30</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Argentina Primera</t>
+          <t>MLS</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Boca Juniors vs River Plate</t>
+          <t>Los Angeles FC vs Minnesota United FC</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>2.43</v>
+        <v>1.77</v>
       </c>
       <c r="E67" t="n">
-        <v>3.35</v>
+        <v>4.68</v>
       </c>
       <c r="F67" t="n">
-        <v>3.71</v>
+        <v>4.98</v>
       </c>
       <c r="G67" t="n">
-        <v>2.38</v>
+        <v>1.73</v>
       </c>
       <c r="H67" t="n">
-        <v>3.28</v>
+        <v>4.59</v>
       </c>
       <c r="I67" t="n">
-        <v>3.64</v>
+        <v>4.88</v>
       </c>
       <c r="J67" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2.36, 3.13, 3.29</t>
+          <t>1.70, 4.23, 4.28</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>dom 01/11 13:45</t>
+          <t>dom 01/11 20:45</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>MLS</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Juventus vs Napoli</t>
+          <t>Portland Timbers vs Houston Dynamo</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="E68" t="n">
-        <v>3.59</v>
+        <v>4.36</v>
       </c>
       <c r="F68" t="n">
-        <v>3.51</v>
+        <v>4.32</v>
       </c>
       <c r="G68" t="n">
-        <v>2.35</v>
+        <v>1.89</v>
       </c>
       <c r="H68" t="n">
-        <v>3.52</v>
+        <v>4.27</v>
       </c>
       <c r="I68" t="n">
-        <v>3.44</v>
+        <v>4.23</v>
       </c>
       <c r="J68" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2.32, 3.36, 3.32</t>
+          <t>1.81, 3.90, 4.05</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>dom 01/11 13:45</t>
+          <t>lun 02/11 11:30</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Marseille vs Toulouse</t>
+          <t>Sassuolo vs Fiorentina</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>2</v>
+        <v>3.05</v>
       </c>
       <c r="E69" t="n">
-        <v>4.38</v>
+        <v>3.99</v>
       </c>
       <c r="F69" t="n">
-        <v>3.98</v>
+        <v>2.49</v>
       </c>
       <c r="G69" t="n">
-        <v>1.96</v>
+        <v>2.99</v>
       </c>
       <c r="H69" t="n">
-        <v>4.29</v>
+        <v>3.92</v>
       </c>
       <c r="I69" t="n">
-        <v>3.91</v>
+        <v>2.44</v>
       </c>
       <c r="J69" t="n">
         <v>20</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>1.93, 4.12, 3.64</t>
+          <t>2.90, 3.82, 2.36</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>dom 01/11 14:00</t>
+          <t>lun 02/11 13:45</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Athletic Bilbao vs Real Sociedad</t>
+          <t>Lorient vs Brest</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>2.21</v>
+        <v>2.62</v>
       </c>
       <c r="E70" t="n">
-        <v>3.97</v>
+        <v>3.53</v>
       </c>
       <c r="F70" t="n">
-        <v>3.62</v>
+        <v>3.18</v>
       </c>
       <c r="G70" t="n">
-        <v>2.17</v>
+        <v>2.56</v>
       </c>
       <c r="H70" t="n">
-        <v>3.89</v>
+        <v>3.46</v>
       </c>
       <c r="I70" t="n">
-        <v>3.55</v>
+        <v>3.11</v>
       </c>
       <c r="J70" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2.16, 3.67, 3.34</t>
+          <t>2.54, 3.31, 2.99</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>dom 01/11 14:30</t>
+          <t>lun 02/11 13:45</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps FC vs Seattle Sounders FC</t>
+          <t>Atalanta BC vs Parma</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="E71" t="n">
         <v>5.05</v>
       </c>
       <c r="F71" t="n">
-        <v>5.55</v>
+        <v>7.13</v>
       </c>
       <c r="G71" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="H71" t="n">
         <v>4.95</v>
       </c>
       <c r="I71" t="n">
-        <v>5.44</v>
+        <v>6.99</v>
       </c>
       <c r="J71" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>1.62, 4.48, 4.62</t>
+          <t>1.52, 4.65, 6.14</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>dom 01/11 15:30</t>
+          <t>lun 02/11 14:00</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Atlanta United FC vs Toronto FC</t>
+          <t>Newcastle United vs Everton</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>2.32</v>
+        <v>2.47</v>
       </c>
       <c r="E72" t="n">
-        <v>4.37</v>
+        <v>3.87</v>
       </c>
       <c r="F72" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="G72" t="n">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="H72" t="n">
-        <v>4.28</v>
+        <v>3.79</v>
       </c>
       <c r="I72" t="n">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
       <c r="J72" t="n">
         <v>21</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2.19, 3.99, 2.89</t>
+          <t>2.44, 3.56, 2.92</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>dom 01/11 15:30</t>
+          <t>lun 02/11 14:00</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Argentina Primera</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Newells Old Boys vs Union Santa Fe</t>
+          <t>Deportivo La Coruña vs CA Osasuna</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>2.09</v>
+        <v>2.29</v>
       </c>
       <c r="E73" t="n">
-        <v>3.62</v>
+        <v>3.55</v>
       </c>
       <c r="F73" t="n">
-        <v>4.45</v>
+        <v>3.82</v>
       </c>
       <c r="G73" t="n">
-        <v>2.05</v>
+        <v>2.24</v>
       </c>
       <c r="H73" t="n">
-        <v>3.55</v>
+        <v>3.48</v>
       </c>
       <c r="I73" t="n">
-        <v>4.36</v>
+        <v>3.74</v>
       </c>
       <c r="J73" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>1.99, 3.40, 3.97</t>
+          <t>2.18, 3.30, 3.67</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>dom 01/11 15:30</t>
+          <t>lun 02/11 16:00</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3595,126 +3595,126 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belgrano de Cordoba vs Barracas Central</t>
+          <t>Platense vs Central Córdoba</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="E74" t="n">
-        <v>3.65</v>
+        <v>4.04</v>
       </c>
       <c r="F74" t="n">
-        <v>5.61</v>
+        <v>6.61</v>
       </c>
       <c r="G74" t="n">
-        <v>1.86</v>
+        <v>1.69</v>
       </c>
       <c r="H74" t="n">
-        <v>3.58</v>
+        <v>3.97</v>
       </c>
       <c r="I74" t="n">
-        <v>5.5</v>
+        <v>6.48</v>
       </c>
       <c r="J74" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>1.82, 3.42, 4.78</t>
+          <t>1.62, 3.71, 5.95</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>dom 01/11 15:30</t>
+          <t>lun 02/11 16:00</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Argentina Primera</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Nashville SC vs New York Red Bulls</t>
+          <t>Defensa y Justicia vs Independiente</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1.54</v>
+        <v>2.39</v>
       </c>
       <c r="E75" t="n">
-        <v>5.39</v>
+        <v>3.51</v>
       </c>
       <c r="F75" t="n">
-        <v>6.81</v>
+        <v>3.62</v>
       </c>
       <c r="G75" t="n">
-        <v>1.51</v>
+        <v>2.34</v>
       </c>
       <c r="H75" t="n">
-        <v>5.29</v>
+        <v>3.44</v>
       </c>
       <c r="I75" t="n">
-        <v>6.67</v>
+        <v>3.54</v>
       </c>
       <c r="J75" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>1.49, 4.71, 5.70</t>
+          <t>2.26, 3.26, 3.35</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>dom 01/11 17:00</t>
+          <t>lun 02/11 17:00</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Liga MX</t>
+          <t>Brasil Serie A</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Santos Laguna vs Necaxa</t>
+          <t>Bragantino-SP vs Santos</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="E76" t="n">
-        <v>4.54</v>
+        <v>4.09</v>
       </c>
       <c r="F76" t="n">
-        <v>4.24</v>
+        <v>3.69</v>
       </c>
       <c r="G76" t="n">
-        <v>1.87</v>
+        <v>2.11</v>
       </c>
       <c r="H76" t="n">
-        <v>4.45</v>
+        <v>4.01</v>
       </c>
       <c r="I76" t="n">
-        <v>4.16</v>
+        <v>3.62</v>
       </c>
       <c r="J76" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>1.80, 4.12, 3.97</t>
+          <t>2.06, 3.76, 3.38</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>dom 01/11 17:45</t>
+          <t>lun 02/11 18:15</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3724,513 +3724,513 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Lanus vs Gimnasia Mendoza</t>
+          <t>Independiente Rivadavia vs Banfield</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="E77" t="n">
-        <v>4.34</v>
+        <v>4.55</v>
       </c>
       <c r="F77" t="n">
-        <v>7.08</v>
+        <v>6.91</v>
       </c>
       <c r="G77" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="H77" t="n">
-        <v>4.25</v>
+        <v>4.46</v>
       </c>
       <c r="I77" t="n">
-        <v>6.94</v>
+        <v>6.78</v>
       </c>
       <c r="J77" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>1.58, 3.96, 6.03</t>
+          <t>1.58, 4.07, 5.75</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>dom 01/11 18:00</t>
+          <t>lun 02/11 18:15</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Argentina Primera</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>New England Revolution vs Inter Miami CF</t>
+          <t>Atlético Tucuman vs Argentinos Juniors</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>2.94</v>
+        <v>3.24</v>
       </c>
       <c r="E78" t="n">
-        <v>4.47</v>
+        <v>3.28</v>
       </c>
       <c r="F78" t="n">
-        <v>2.4</v>
+        <v>2.73</v>
       </c>
       <c r="G78" t="n">
-        <v>2.88</v>
+        <v>3.17</v>
       </c>
       <c r="H78" t="n">
-        <v>4.38</v>
+        <v>3.22</v>
       </c>
       <c r="I78" t="n">
-        <v>2.35</v>
+        <v>2.67</v>
       </c>
       <c r="J78" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2.79, 3.95, 2.26</t>
+          <t>2.99, 3.03, 2.62</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>dom 01/11 19:10</t>
+          <t>mar 03/11 11:45</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Liga MX</t>
+          <t>Champions League</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Cruz Azul vs León</t>
+          <t>Shakhtar Donetsk vs Sporting Lisbon</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1.75</v>
+        <v>3.96</v>
       </c>
       <c r="E79" t="n">
-        <v>4.72</v>
+        <v>4.13</v>
       </c>
       <c r="F79" t="n">
-        <v>5.06</v>
+        <v>2.06</v>
       </c>
       <c r="G79" t="n">
-        <v>1.72</v>
+        <v>3.88</v>
       </c>
       <c r="H79" t="n">
-        <v>4.63</v>
+        <v>4.05</v>
       </c>
       <c r="I79" t="n">
-        <v>4.96</v>
+        <v>2.02</v>
       </c>
       <c r="J79" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>1.67, 4.28, 4.57</t>
+          <t>3.62, 3.87, 1.93</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>dom 01/11 19:30</t>
+          <t>mar 03/11 11:45</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Champions League</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Los Angeles FC vs Minnesota United FC</t>
+          <t>Galatasaray vs VfB Stuttgart</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1.79</v>
+        <v>2.32</v>
       </c>
       <c r="E80" t="n">
-        <v>4.63</v>
+        <v>4.44</v>
       </c>
       <c r="F80" t="n">
-        <v>4.89</v>
+        <v>3.09</v>
       </c>
       <c r="G80" t="n">
-        <v>1.75</v>
+        <v>2.27</v>
       </c>
       <c r="H80" t="n">
-        <v>4.54</v>
+        <v>4.36</v>
       </c>
       <c r="I80" t="n">
-        <v>4.8</v>
+        <v>3.03</v>
       </c>
       <c r="J80" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>1.69, 4.18, 4.43</t>
+          <t>2.14, 4.22, 2.89</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>dom 01/11 20:45</t>
+          <t>mar 03/11 14:00</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Champions League</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portland Timbers vs Houston Dynamo</t>
+          <t>Manchester United vs AS Roma</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1.95</v>
+        <v>2.47</v>
       </c>
       <c r="E81" t="n">
-        <v>4.35</v>
+        <v>4.27</v>
       </c>
       <c r="F81" t="n">
-        <v>4.2</v>
+        <v>2.93</v>
       </c>
       <c r="G81" t="n">
-        <v>1.91</v>
+        <v>2.42</v>
       </c>
       <c r="H81" t="n">
-        <v>4.27</v>
+        <v>4.19</v>
       </c>
       <c r="I81" t="n">
-        <v>4.12</v>
+        <v>2.88</v>
       </c>
       <c r="J81" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>1.83, 3.88, 3.97</t>
+          <t>2.30, 4.06, 2.71</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>lun 02/11 11:30</t>
+          <t>mar 03/11 14:00</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Champions League</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Sassuolo vs Fiorentina</t>
+          <t>Atlético Madrid vs Bayern Munich</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>3.01</v>
+        <v>3.55</v>
       </c>
       <c r="E82" t="n">
-        <v>3.99</v>
+        <v>4.52</v>
       </c>
       <c r="F82" t="n">
-        <v>2.51</v>
+        <v>2.09</v>
       </c>
       <c r="G82" t="n">
-        <v>2.95</v>
+        <v>3.48</v>
       </c>
       <c r="H82" t="n">
-        <v>3.91</v>
+        <v>4.44</v>
       </c>
       <c r="I82" t="n">
-        <v>2.47</v>
+        <v>2.05</v>
       </c>
       <c r="J82" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2.89, 3.81, 2.37</t>
+          <t>3.25, 4.22, 1.97</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>lun 02/11 13:45</t>
+          <t>mar 03/11 14:00</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Champions League</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Lorient vs Brest</t>
+          <t>Bodø/Glimt vs Lille</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>2.6</v>
+        <v>1.94</v>
       </c>
       <c r="E83" t="n">
-        <v>3.59</v>
+        <v>4.41</v>
       </c>
       <c r="F83" t="n">
-        <v>3.15</v>
+        <v>4.21</v>
       </c>
       <c r="G83" t="n">
-        <v>2.55</v>
+        <v>1.9</v>
       </c>
       <c r="H83" t="n">
-        <v>3.52</v>
+        <v>4.33</v>
       </c>
       <c r="I83" t="n">
-        <v>3.09</v>
+        <v>4.13</v>
       </c>
       <c r="J83" t="n">
         <v>18</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2.53, 3.34, 2.98</t>
+          <t>1.83, 4.06, 3.86</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>lun 02/11 13:45</t>
+          <t>mar 03/11 14:00</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Champions League</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Atalanta BC vs Parma</t>
+          <t>Feyenoord vs Inter Milan</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1.55</v>
+        <v>4.85</v>
       </c>
       <c r="E84" t="n">
-        <v>5.05</v>
+        <v>4.78</v>
       </c>
       <c r="F84" t="n">
-        <v>7.31</v>
+        <v>1.77</v>
       </c>
       <c r="G84" t="n">
-        <v>1.52</v>
+        <v>4.76</v>
       </c>
       <c r="H84" t="n">
-        <v>4.95</v>
+        <v>4.69</v>
       </c>
       <c r="I84" t="n">
-        <v>7.17</v>
+        <v>1.73</v>
       </c>
       <c r="J84" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>1.52, 4.68, 6.17</t>
+          <t>4.32, 4.37, 1.68</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>lun 02/11 14:00</t>
+          <t>mar 03/11 14:00</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Champions League</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Newcastle United vs Everton</t>
+          <t>Villarreal vs Paris Saint Germain</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>2.44</v>
+        <v>5.35</v>
       </c>
       <c r="E85" t="n">
-        <v>3.9</v>
+        <v>5.15</v>
       </c>
       <c r="F85" t="n">
-        <v>3.19</v>
+        <v>1.67</v>
       </c>
       <c r="G85" t="n">
-        <v>2.39</v>
+        <v>5.24</v>
       </c>
       <c r="H85" t="n">
-        <v>3.82</v>
+        <v>5.05</v>
       </c>
       <c r="I85" t="n">
-        <v>3.12</v>
+        <v>1.64</v>
       </c>
       <c r="J85" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2.36, 3.61, 3.00</t>
+          <t>4.88, 4.69, 1.57</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>lun 02/11 14:00</t>
+          <t>mar 03/11 14:00</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Champions League</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña vs CA Osasuna</t>
+          <t>Barcelona vs Aston Villa</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>2.29</v>
+        <v>1.3</v>
       </c>
       <c r="E86" t="n">
-        <v>3.54</v>
+        <v>7.96</v>
       </c>
       <c r="F86" t="n">
-        <v>3.84</v>
+        <v>12.06</v>
       </c>
       <c r="G86" t="n">
-        <v>2.24</v>
+        <v>1.27</v>
       </c>
       <c r="H86" t="n">
-        <v>3.47</v>
+        <v>7.8</v>
       </c>
       <c r="I86" t="n">
-        <v>3.77</v>
+        <v>11.83</v>
       </c>
       <c r="J86" t="n">
         <v>18</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2.18, 3.31, 3.67</t>
+          <t>1.25, 6.98, 8.96</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>lun 02/11 16:00</t>
+          <t>mar 03/11 14:00</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Argentina Primera</t>
+          <t>Champions League</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Platense vs Central Córdoba</t>
+          <t>LASK vs ŠK Slovan Bratislava</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="E87" t="n">
-        <v>3.84</v>
+        <v>5.63</v>
       </c>
       <c r="F87" t="n">
-        <v>6.11</v>
+        <v>7.46</v>
       </c>
       <c r="G87" t="n">
-        <v>1.76</v>
+        <v>1.47</v>
       </c>
       <c r="H87" t="n">
-        <v>3.76</v>
+        <v>5.52</v>
       </c>
       <c r="I87" t="n">
-        <v>5.99</v>
+        <v>7.31</v>
       </c>
       <c r="J87" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>1.69, 3.57, 5.45</t>
+          <t>1.43, 5.07, 6.32</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>lun 02/11 16:00</t>
+          <t>mar 03/11 16:30</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Argentina Primera</t>
+          <t>Brasil Serie A</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Defensa y Justicia vs Independiente</t>
+          <t>Chapecoense vs Mirassol</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>2.38</v>
+        <v>3.77</v>
       </c>
       <c r="E88" t="n">
-        <v>3.54</v>
+        <v>4.09</v>
       </c>
       <c r="F88" t="n">
-        <v>3.61</v>
+        <v>2.12</v>
       </c>
       <c r="G88" t="n">
-        <v>2.33</v>
+        <v>3.69</v>
       </c>
       <c r="H88" t="n">
-        <v>3.47</v>
+        <v>4.01</v>
       </c>
       <c r="I88" t="n">
-        <v>3.54</v>
+        <v>2.08</v>
       </c>
       <c r="J88" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2.26, 3.25, 3.34</t>
+          <t>3.56, 3.77, 2.00</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>lun 02/11 17:00</t>
+          <t>mar 03/11 18:30</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4240,126 +4240,122 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Bragantino-SP vs Santos</t>
+          <t>Internacional vs Coritiba</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>2.1</v>
+        <v>1.66</v>
       </c>
       <c r="E89" t="n">
-        <v>4.07</v>
+        <v>4.54</v>
       </c>
       <c r="F89" t="n">
-        <v>3.87</v>
+        <v>6.3</v>
       </c>
       <c r="G89" t="n">
-        <v>2.06</v>
+        <v>1.63</v>
       </c>
       <c r="H89" t="n">
-        <v>3.99</v>
+        <v>4.45</v>
       </c>
       <c r="I89" t="n">
-        <v>3.79</v>
+        <v>6.17</v>
       </c>
       <c r="J89" t="n">
-        <v>20</v>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>2.06, 3.76, 3.38</t>
-        </is>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="K89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>lun 02/11 18:15</t>
+          <t>mié 04/11 09:30</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Argentina Primera</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Atlético Tucuman vs Argentinos Juniors</t>
+          <t>Rennes vs Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>3.25</v>
+        <v>2.24</v>
       </c>
       <c r="E90" t="n">
-        <v>3.3</v>
+        <v>3.94</v>
       </c>
       <c r="F90" t="n">
-        <v>2.71</v>
+        <v>3.57</v>
       </c>
       <c r="G90" t="n">
-        <v>3.18</v>
+        <v>2.2</v>
       </c>
       <c r="H90" t="n">
-        <v>3.24</v>
+        <v>3.86</v>
       </c>
       <c r="I90" t="n">
-        <v>2.65</v>
+        <v>3.5</v>
       </c>
       <c r="J90" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2.90, 3.03, 2.67</t>
+          <t>2.17, 3.60, 3.22</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>lun 02/11 18:15</t>
+          <t>mié 04/11 11:45</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Argentina Primera</t>
+          <t>Champions League</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia vs Banfield</t>
+          <t>Fenerbahce vs Liverpool</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1.58</v>
+        <v>5.44</v>
       </c>
       <c r="E91" t="n">
-        <v>4.72</v>
+        <v>4.85</v>
       </c>
       <c r="F91" t="n">
-        <v>7.42</v>
+        <v>1.69</v>
       </c>
       <c r="G91" t="n">
-        <v>1.55</v>
+        <v>5.33</v>
       </c>
       <c r="H91" t="n">
-        <v>4.63</v>
+        <v>4.76</v>
       </c>
       <c r="I91" t="n">
-        <v>7.28</v>
+        <v>1.66</v>
       </c>
       <c r="J91" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>1.53, 4.20, 6.01</t>
+          <t>4.86, 4.43, 1.60</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>mar 03/11 11:45</t>
+          <t>mié 04/11 11:45</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4369,40 +4365,40 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk vs Sporting Lisbon</t>
+          <t>AEK Athens vs Real Madrid</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>3.97</v>
+        <v>10.42</v>
       </c>
       <c r="E92" t="n">
-        <v>4.18</v>
+        <v>7.02</v>
       </c>
       <c r="F92" t="n">
-        <v>2.04</v>
+        <v>1.35</v>
       </c>
       <c r="G92" t="n">
-        <v>3.89</v>
+        <v>10.22</v>
       </c>
       <c r="H92" t="n">
-        <v>4.1</v>
+        <v>6.88</v>
       </c>
       <c r="I92" t="n">
-        <v>2</v>
+        <v>1.32</v>
       </c>
       <c r="J92" t="n">
         <v>18</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>3.62, 3.87, 1.93</t>
+          <t>8.81, 6.35, 1.27</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>mar 03/11 11:45</t>
+          <t>mié 04/11 14:00</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4412,40 +4408,40 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Galatasaray vs VfB Stuttgart</t>
+          <t>PSV Eindhoven vs Club Brugge</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="E93" t="n">
-        <v>4.4</v>
+        <v>4.55</v>
       </c>
       <c r="F93" t="n">
-        <v>3.07</v>
+        <v>3.19</v>
       </c>
       <c r="G93" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="H93" t="n">
-        <v>4.32</v>
+        <v>4.46</v>
       </c>
       <c r="I93" t="n">
-        <v>3.01</v>
+        <v>3.13</v>
       </c>
       <c r="J93" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2.17, 4.19, 2.84</t>
+          <t>2.06, 4.33, 2.99</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>mar 03/11 14:00</t>
+          <t>mié 04/11 14:00</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4455,40 +4451,40 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Feyenoord vs Inter Milan</t>
+          <t>RC Lens vs Como</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>4.8</v>
+        <v>3.14</v>
       </c>
       <c r="E94" t="n">
-        <v>4.76</v>
+        <v>4.27</v>
       </c>
       <c r="F94" t="n">
-        <v>1.78</v>
+        <v>2.34</v>
       </c>
       <c r="G94" t="n">
-        <v>4.7</v>
+        <v>3.08</v>
       </c>
       <c r="H94" t="n">
-        <v>4.67</v>
+        <v>4.19</v>
       </c>
       <c r="I94" t="n">
-        <v>1.74</v>
+        <v>2.29</v>
       </c>
       <c r="J94" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>4.32, 4.37, 1.68</t>
+          <t>2.91, 4.06, 2.17</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>mar 03/11 14:00</t>
+          <t>mié 04/11 14:00</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4498,40 +4494,40 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Atlético Madrid vs Bayern Munich</t>
+          <t>RB Leipzig vs Manchester City</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>3.54</v>
+        <v>6.21</v>
       </c>
       <c r="E95" t="n">
-        <v>4.53</v>
+        <v>5.32</v>
       </c>
       <c r="F95" t="n">
-        <v>2.1</v>
+        <v>1.58</v>
       </c>
       <c r="G95" t="n">
-        <v>3.47</v>
+        <v>6.09</v>
       </c>
       <c r="H95" t="n">
-        <v>4.44</v>
+        <v>5.22</v>
       </c>
       <c r="I95" t="n">
-        <v>2.06</v>
+        <v>1.55</v>
       </c>
       <c r="J95" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>3.25, 4.22, 1.97</t>
+          <t>5.66, 4.95, 1.48</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>mar 03/11 14:00</t>
+          <t>mié 04/11 14:00</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4541,40 +4537,40 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bodø/Glimt vs Lille</t>
+          <t>Porto vs Napoli</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="E96" t="n">
-        <v>4.4</v>
+        <v>3.94</v>
       </c>
       <c r="F96" t="n">
-        <v>4.16</v>
+        <v>3.42</v>
       </c>
       <c r="G96" t="n">
-        <v>1.91</v>
+        <v>2.26</v>
       </c>
       <c r="H96" t="n">
-        <v>4.31</v>
+        <v>3.87</v>
       </c>
       <c r="I96" t="n">
-        <v>4.08</v>
+        <v>3.36</v>
       </c>
       <c r="J96" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>1.83, 4.06, 3.86</t>
+          <t>2.15, 3.74, 3.14</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>mar 03/11 14:00</t>
+          <t>mié 04/11 14:00</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4584,40 +4580,40 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Barcelona vs Aston Villa</t>
+          <t>Viking FK vs Sabah FK</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1.29</v>
+        <v>1.54</v>
       </c>
       <c r="E97" t="n">
-        <v>8.18</v>
+        <v>5.37</v>
       </c>
       <c r="F97" t="n">
-        <v>12.39</v>
+        <v>6.83</v>
       </c>
       <c r="G97" t="n">
-        <v>1.26</v>
+        <v>1.51</v>
       </c>
       <c r="H97" t="n">
-        <v>8.02</v>
+        <v>5.27</v>
       </c>
       <c r="I97" t="n">
-        <v>12.15</v>
+        <v>6.69</v>
       </c>
       <c r="J97" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>1.23, 7.25, 9.58</t>
+          <t>1.47, 4.83, 5.90</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>mar 03/11 14:00</t>
+          <t>mié 04/11 14:00</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4627,40 +4623,40 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Manchester United vs AS Roma</t>
+          <t>Slavia Praha vs Arsenal</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>2.47</v>
+        <v>10.82</v>
       </c>
       <c r="E98" t="n">
-        <v>4.24</v>
+        <v>6.44</v>
       </c>
       <c r="F98" t="n">
-        <v>2.94</v>
+        <v>1.36</v>
       </c>
       <c r="G98" t="n">
-        <v>2.42</v>
+        <v>10.61</v>
       </c>
       <c r="H98" t="n">
-        <v>4.16</v>
+        <v>6.31</v>
       </c>
       <c r="I98" t="n">
-        <v>2.88</v>
+        <v>1.34</v>
       </c>
       <c r="J98" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2.30, 4.06, 2.71</t>
+          <t>8.67, 5.50, 1.32</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>mar 03/11 14:00</t>
+          <t>mié 04/11 14:00</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4670,83 +4666,83 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>LASK vs ŠK Slovan Bratislava</t>
+          <t>Borussia Dortmund vs Real Betis</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1.5</v>
+        <v>1.84</v>
       </c>
       <c r="E99" t="n">
-        <v>5.61</v>
+        <v>4.44</v>
       </c>
       <c r="F99" t="n">
-        <v>7.43</v>
+        <v>4.72</v>
       </c>
       <c r="G99" t="n">
-        <v>1.47</v>
+        <v>1.81</v>
       </c>
       <c r="H99" t="n">
-        <v>5.5</v>
+        <v>4.35</v>
       </c>
       <c r="I99" t="n">
-        <v>7.28</v>
+        <v>4.62</v>
       </c>
       <c r="J99" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>1.43, 5.07, 6.32</t>
+          <t>1.72, 4.12, 4.32</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>mar 03/11 14:00</t>
+          <t>mié 04/11 16:30</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Champions League</t>
+          <t>Brasil Serie A</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Villarreal vs Paris Saint Germain</t>
+          <t>Flamengo vs Grêmio</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>5.32</v>
+        <v>1.22</v>
       </c>
       <c r="E100" t="n">
-        <v>5.08</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="F100" t="n">
-        <v>1.68</v>
+        <v>21.2</v>
       </c>
       <c r="G100" t="n">
-        <v>5.22</v>
+        <v>1.19</v>
       </c>
       <c r="H100" t="n">
-        <v>4.98</v>
+        <v>8.69</v>
       </c>
       <c r="I100" t="n">
-        <v>1.65</v>
+        <v>20.78</v>
       </c>
       <c r="J100" t="n">
         <v>19</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>4.67, 4.46, 1.62</t>
+          <t>1.18, 8.00, 14.01</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>mar 03/11 16:30</t>
+          <t>mié 04/11 16:30</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4756,36 +4752,40 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chapecoense vs Mirassol</t>
+          <t>Atletico Paranaense vs Vasco da Gama</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>3.44</v>
+        <v>2.27</v>
       </c>
       <c r="E101" t="n">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="F101" t="n">
-        <v>2.27</v>
+        <v>3.55</v>
       </c>
       <c r="G101" t="n">
-        <v>3.38</v>
+        <v>2.23</v>
       </c>
       <c r="H101" t="n">
-        <v>3.93</v>
+        <v>3.8</v>
       </c>
       <c r="I101" t="n">
-        <v>2.23</v>
+        <v>3.48</v>
       </c>
       <c r="J101" t="n">
-        <v>18</v>
-      </c>
-      <c r="K101" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>2.18, 3.51, 3.31</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>mar 03/11 18:30</t>
+          <t>mié 04/11 18:30</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4795,634 +4795,642 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Internacional vs Coritiba</t>
+          <t>Sao Paulo vs Corinthians</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1.66</v>
+        <v>2.27</v>
       </c>
       <c r="E102" t="n">
-        <v>4.55</v>
+        <v>3.49</v>
       </c>
       <c r="F102" t="n">
-        <v>6.39</v>
+        <v>3.95</v>
       </c>
       <c r="G102" t="n">
-        <v>1.62</v>
+        <v>2.23</v>
       </c>
       <c r="H102" t="n">
-        <v>4.46</v>
+        <v>3.42</v>
       </c>
       <c r="I102" t="n">
-        <v>6.26</v>
+        <v>3.87</v>
       </c>
       <c r="J102" t="n">
-        <v>18</v>
-      </c>
-      <c r="K102" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>2.19, 3.21, 3.60</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>mié 04/11 09:30</t>
+          <t>mié 04/11 18:30</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>Brasil Serie A</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Rennes vs Olympiakos Piraeus</t>
+          <t>Botafogo vs Atletico Mineiro</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="E103" t="n">
-        <v>3.94</v>
+        <v>4.03</v>
       </c>
       <c r="F103" t="n">
-        <v>3.59</v>
+        <v>3.73</v>
       </c>
       <c r="G103" t="n">
-        <v>2.19</v>
+        <v>2.11</v>
       </c>
       <c r="H103" t="n">
-        <v>3.86</v>
+        <v>3.95</v>
       </c>
       <c r="I103" t="n">
-        <v>3.52</v>
+        <v>3.65</v>
       </c>
       <c r="J103" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2.14, 3.63, 3.25</t>
+          <t>2.00, 3.74, 3.56</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>mié 04/11 11:45</t>
+          <t>jue 05/11 11:45</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Champions League</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Fenerbahce vs Liverpool</t>
+          <t>Crystal Palace vs TSG Hoffenheim</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>5.39</v>
+        <v>2.04</v>
       </c>
       <c r="E104" t="n">
-        <v>4.82</v>
+        <v>4.24</v>
       </c>
       <c r="F104" t="n">
-        <v>1.7</v>
+        <v>3.94</v>
       </c>
       <c r="G104" t="n">
-        <v>5.28</v>
+        <v>2</v>
       </c>
       <c r="H104" t="n">
-        <v>4.73</v>
+        <v>4.16</v>
       </c>
       <c r="I104" t="n">
-        <v>1.67</v>
+        <v>3.86</v>
       </c>
       <c r="J104" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>4.86, 4.43, 1.60</t>
+          <t>1.93, 3.95, 3.55</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>mié 04/11 11:45</t>
+          <t>jue 05/11 11:45</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Champions League</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>AEK Athens vs Real Madrid</t>
+          <t>PFC Levski Sofia vs Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>9.94</v>
+        <v>2.1</v>
       </c>
       <c r="E105" t="n">
-        <v>6.83</v>
+        <v>3.93</v>
       </c>
       <c r="F105" t="n">
-        <v>1.36</v>
+        <v>3.99</v>
       </c>
       <c r="G105" t="n">
-        <v>9.74</v>
+        <v>2.06</v>
       </c>
       <c r="H105" t="n">
-        <v>6.7</v>
+        <v>3.86</v>
       </c>
       <c r="I105" t="n">
-        <v>1.34</v>
+        <v>3.91</v>
       </c>
       <c r="J105" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>8.48, 6.25, 1.28</t>
+          <t>1.99, 3.58, 3.71</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>mié 04/11 14:00</t>
+          <t>jue 05/11 11:45</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Champions League</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>RB Leipzig vs Manchester City</t>
+          <t>Lillestrom vs Viktoria Plzeň</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>5.92</v>
+        <v>2.95</v>
       </c>
       <c r="E106" t="n">
-        <v>5.2</v>
+        <v>4.07</v>
       </c>
       <c r="F106" t="n">
-        <v>1.61</v>
+        <v>2.53</v>
       </c>
       <c r="G106" t="n">
-        <v>5.81</v>
+        <v>2.89</v>
       </c>
       <c r="H106" t="n">
-        <v>5.1</v>
+        <v>3.99</v>
       </c>
       <c r="I106" t="n">
-        <v>1.58</v>
+        <v>2.48</v>
       </c>
       <c r="J106" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>5.19, 4.80, 1.53</t>
+          <t>2.70, 3.77, 2.41</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>mié 04/11 14:00</t>
+          <t>jue 05/11 11:45</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Champions League</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Borussia Dortmund vs Real Betis</t>
+          <t>Real Sociedad vs Lyon</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1.86</v>
+        <v>2.03</v>
       </c>
       <c r="E107" t="n">
-        <v>4.39</v>
+        <v>4.25</v>
       </c>
       <c r="F107" t="n">
-        <v>4.64</v>
+        <v>3.96</v>
       </c>
       <c r="G107" t="n">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="H107" t="n">
-        <v>4.31</v>
+        <v>4.17</v>
       </c>
       <c r="I107" t="n">
-        <v>4.55</v>
+        <v>3.88</v>
       </c>
       <c r="J107" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>1.78, 4.04, 4.09</t>
+          <t>1.93, 3.86, 3.66</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>mié 04/11 14:00</t>
+          <t>jue 05/11 11:45</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Champions League</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Club Brugge</t>
+          <t>NEC Nijmegen vs Omonoia FC</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>2.25</v>
+        <v>1.88</v>
       </c>
       <c r="E108" t="n">
-        <v>4.52</v>
+        <v>4.41</v>
       </c>
       <c r="F108" t="n">
-        <v>3.19</v>
+        <v>4.48</v>
       </c>
       <c r="G108" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="H108" t="n">
-        <v>4.43</v>
+        <v>4.32</v>
       </c>
       <c r="I108" t="n">
-        <v>3.12</v>
+        <v>4.4</v>
       </c>
       <c r="J108" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>2.06, 4.33, 2.99</t>
+          <t>1.81, 3.95, 4.06</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>mié 04/11 14:00</t>
+          <t>jue 05/11 11:45</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Champions League</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>RC Lens vs Como</t>
+          <t>Anderlecht vs Salzburg</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>3.16</v>
+        <v>2.01</v>
       </c>
       <c r="E109" t="n">
-        <v>4.24</v>
+        <v>4.27</v>
       </c>
       <c r="F109" t="n">
-        <v>2.33</v>
+        <v>4.02</v>
       </c>
       <c r="G109" t="n">
-        <v>3.1</v>
+        <v>1.97</v>
       </c>
       <c r="H109" t="n">
-        <v>4.16</v>
+        <v>4.19</v>
       </c>
       <c r="I109" t="n">
-        <v>2.29</v>
+        <v>3.95</v>
       </c>
       <c r="J109" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>2.90, 4.10, 2.17</t>
+          <t>1.90, 3.88, 3.73</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>mié 04/11 14:00</t>
+          <t>jue 05/11 11:45</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Champions League</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Viking FK vs Sabah FK</t>
+          <t>AC Milan vs Ferencváros TC</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="E110" t="n">
-        <v>5.37</v>
+        <v>6.12</v>
       </c>
       <c r="F110" t="n">
-        <v>6.81</v>
+        <v>10.73</v>
       </c>
       <c r="G110" t="n">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="H110" t="n">
-        <v>5.27</v>
+        <v>6</v>
       </c>
       <c r="I110" t="n">
-        <v>6.68</v>
+        <v>10.52</v>
       </c>
       <c r="J110" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>1.47, 4.83, 5.90</t>
+          <t>1.28, 4.89, 7.32</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>mié 04/11 14:00</t>
+          <t>jue 05/11 11:45</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Champions League</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Porto vs Napoli</t>
+          <t>Sparta Prague vs Bournemouth</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>2.31</v>
+        <v>5.89</v>
       </c>
       <c r="E111" t="n">
-        <v>3.93</v>
+        <v>4.82</v>
       </c>
       <c r="F111" t="n">
-        <v>3.42</v>
+        <v>1.66</v>
       </c>
       <c r="G111" t="n">
-        <v>2.26</v>
+        <v>5.77</v>
       </c>
       <c r="H111" t="n">
-        <v>3.85</v>
+        <v>4.72</v>
       </c>
       <c r="I111" t="n">
-        <v>3.36</v>
+        <v>1.63</v>
       </c>
       <c r="J111" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>2.17, 3.66, 3.16</t>
+          <t>5.24, 4.35, 1.57</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>mié 04/11 14:00</t>
+          <t>jue 05/11 14:00</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Champions League</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Slavia Praha vs Arsenal</t>
+          <t>Torreense vs FC Ararat-Armenia</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>10.61</v>
+        <v>1.86</v>
       </c>
       <c r="E112" t="n">
-        <v>6.31</v>
+        <v>4.15</v>
       </c>
       <c r="F112" t="n">
-        <v>1.37</v>
+        <v>4.96</v>
       </c>
       <c r="G112" t="n">
-        <v>10.41</v>
+        <v>1.82</v>
       </c>
       <c r="H112" t="n">
-        <v>6.19</v>
+        <v>4.07</v>
       </c>
       <c r="I112" t="n">
-        <v>1.35</v>
+        <v>4.87</v>
       </c>
       <c r="J112" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>8.32, 5.41, 1.33</t>
+          <t>1.78, 3.90, 4.24</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>mié 04/11 16:30</t>
+          <t>jue 05/11 14:00</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Brasil Serie A</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Atletico Paranaense vs Vasco da Gama</t>
+          <t>SK Sturm Graz vs NK Celje</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>2.28</v>
+        <v>1.67</v>
       </c>
       <c r="E113" t="n">
-        <v>3.82</v>
+        <v>4.75</v>
       </c>
       <c r="F113" t="n">
-        <v>3.56</v>
+        <v>5.83</v>
       </c>
       <c r="G113" t="n">
-        <v>2.24</v>
+        <v>1.64</v>
       </c>
       <c r="H113" t="n">
-        <v>3.75</v>
+        <v>4.65</v>
       </c>
       <c r="I113" t="n">
-        <v>3.5</v>
+        <v>5.71</v>
       </c>
       <c r="J113" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>2.20, 3.49, 3.29</t>
+          <t>1.57, 4.39, 5.20</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>mié 04/11 16:30</t>
+          <t>jue 05/11 14:00</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Brasil Serie A</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Flamengo vs Grêmio</t>
+          <t>Hapoel Be'er Sheva vs OFI Crete</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1.24</v>
+        <v>2.25</v>
       </c>
       <c r="E114" t="n">
-        <v>8.26</v>
+        <v>3.93</v>
       </c>
       <c r="F114" t="n">
-        <v>19.39</v>
+        <v>3.56</v>
       </c>
       <c r="G114" t="n">
-        <v>1.21</v>
+        <v>2.2</v>
       </c>
       <c r="H114" t="n">
-        <v>8.09</v>
+        <v>3.86</v>
       </c>
       <c r="I114" t="n">
-        <v>19.01</v>
+        <v>3.49</v>
       </c>
       <c r="J114" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>1.21, 7.30, 12.34</t>
+          <t>2.15, 3.61, 3.24</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>mié 04/11 18:30</t>
+          <t>jue 05/11 14:00</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Brasil Serie A</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Sao Paulo vs Corinthians</t>
+          <t>Sunderland vs Dinamo Zagreb</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>2.21</v>
+        <v>1.52</v>
       </c>
       <c r="E115" t="n">
-        <v>3.47</v>
+        <v>5.17</v>
       </c>
       <c r="F115" t="n">
-        <v>4.16</v>
+        <v>7.64</v>
       </c>
       <c r="G115" t="n">
-        <v>2.17</v>
+        <v>1.49</v>
       </c>
       <c r="H115" t="n">
-        <v>3.4</v>
+        <v>5.07</v>
       </c>
       <c r="I115" t="n">
-        <v>4.08</v>
+        <v>7.49</v>
       </c>
       <c r="J115" t="n">
-        <v>18</v>
-      </c>
-      <c r="K115" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>1.45, 4.69, 6.53</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>mié 04/11 18:30</t>
+          <t>jue 05/11 14:00</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Brasil Serie A</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Botafogo vs Atletico Mineiro</t>
+          <t>Celtic vs Besiktas JK</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>2.19</v>
+        <v>3.11</v>
       </c>
       <c r="E116" t="n">
-        <v>4.02</v>
+        <v>4.03</v>
       </c>
       <c r="F116" t="n">
-        <v>3.64</v>
+        <v>2.43</v>
       </c>
       <c r="G116" t="n">
-        <v>2.14</v>
+        <v>3.05</v>
       </c>
       <c r="H116" t="n">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="I116" t="n">
-        <v>3.57</v>
+        <v>2.38</v>
       </c>
       <c r="J116" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>2.00, 3.74, 3.56</t>
+          <t>2.94, 3.82, 2.23</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>jue 05/11 11:45</t>
+          <t>jue 05/11 14:00</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5432,40 +5440,40 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Lillestrom vs Viktoria Plzeň</t>
+          <t>Benfica vs Lech Poznań</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>2.97</v>
+        <v>1.22</v>
       </c>
       <c r="E117" t="n">
-        <v>4.06</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="F117" t="n">
-        <v>2.52</v>
+        <v>20.09</v>
       </c>
       <c r="G117" t="n">
-        <v>2.91</v>
+        <v>1.2</v>
       </c>
       <c r="H117" t="n">
-        <v>3.98</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I117" t="n">
-        <v>2.47</v>
+        <v>19.69</v>
       </c>
       <c r="J117" t="n">
         <v>17</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>2.74, 3.77, 2.38</t>
+          <t>1.15, 6.37, 11.08</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>jue 05/11 11:45</t>
+          <t>jue 05/11 14:00</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5475,40 +5483,40 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>PFC Levski Sofia vs Jagiellonia Białystok</t>
+          <t>Bayer Leverkusen vs Marseille</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>2.14</v>
+        <v>1.49</v>
       </c>
       <c r="E118" t="n">
-        <v>3.91</v>
+        <v>5.58</v>
       </c>
       <c r="F118" t="n">
-        <v>3.89</v>
+        <v>7.62</v>
       </c>
       <c r="G118" t="n">
-        <v>2.1</v>
+        <v>1.46</v>
       </c>
       <c r="H118" t="n">
-        <v>3.84</v>
+        <v>5.47</v>
       </c>
       <c r="I118" t="n">
-        <v>3.81</v>
+        <v>7.47</v>
       </c>
       <c r="J118" t="n">
         <v>17</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>1.99, 3.60, 3.70</t>
+          <t>1.41, 5.14, 6.61</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>jue 05/11 11:45</t>
+          <t>jue 05/11 14:00</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5518,40 +5526,40 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Crystal Palace vs TSG Hoffenheim</t>
+          <t>AZ Alkmaar vs Juventus</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1.99</v>
+        <v>3.9</v>
       </c>
       <c r="E119" t="n">
-        <v>4.29</v>
+        <v>4.03</v>
       </c>
       <c r="F119" t="n">
-        <v>4.09</v>
+        <v>2.1</v>
       </c>
       <c r="G119" t="n">
-        <v>1.95</v>
+        <v>3.82</v>
       </c>
       <c r="H119" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="I119" t="n">
-        <v>4.01</v>
+        <v>2.06</v>
       </c>
       <c r="J119" t="n">
         <v>17</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>1.88, 4.00, 3.68</t>
+          <t>3.71, 3.78, 1.93</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>jue 05/11 11:45</t>
+          <t>jue 05/11 14:00</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5561,814 +5569,810 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Sparta Prague vs Bournemouth</t>
+          <t>Celta Vigo vs Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>5.8</v>
+        <v>2.16</v>
       </c>
       <c r="E120" t="n">
-        <v>4.75</v>
+        <v>4.06</v>
       </c>
       <c r="F120" t="n">
-        <v>1.67</v>
+        <v>3.69</v>
       </c>
       <c r="G120" t="n">
-        <v>5.69</v>
+        <v>2.12</v>
       </c>
       <c r="H120" t="n">
-        <v>4.66</v>
+        <v>3.98</v>
       </c>
       <c r="I120" t="n">
-        <v>1.64</v>
+        <v>3.62</v>
       </c>
       <c r="J120" t="n">
         <v>17</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>5.24, 4.35, 1.57</t>
+          <t>2.01, 3.79, 3.44</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>jue 05/11 11:45</t>
+          <t>jue 05/11 16:30</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>Brasil Serie A</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Anderlecht vs Salzburg</t>
+          <t>Palmeiras vs Remo</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>2</v>
+        <v>1.27</v>
       </c>
       <c r="E121" t="n">
-        <v>4.3</v>
+        <v>7.43</v>
       </c>
       <c r="F121" t="n">
-        <v>4.04</v>
+        <v>16.74</v>
       </c>
       <c r="G121" t="n">
-        <v>1.96</v>
+        <v>1.25</v>
       </c>
       <c r="H121" t="n">
-        <v>4.21</v>
+        <v>7.29</v>
       </c>
       <c r="I121" t="n">
-        <v>3.96</v>
+        <v>16.41</v>
       </c>
       <c r="J121" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>1.90, 3.88, 3.73</t>
+          <t>1.24, 6.52, 11.49</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>jue 05/11 11:45</t>
+          <t>jue 05/11 18:30</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>Brasil Serie A</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>AC Milan vs Ferencváros TC</t>
+          <t>Cruzeiro vs Bahia</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1.38</v>
+        <v>1.81</v>
       </c>
       <c r="E122" t="n">
-        <v>6.14</v>
+        <v>4.51</v>
       </c>
       <c r="F122" t="n">
-        <v>10.94</v>
+        <v>4.88</v>
       </c>
       <c r="G122" t="n">
-        <v>1.35</v>
+        <v>1.77</v>
       </c>
       <c r="H122" t="n">
-        <v>6.02</v>
+        <v>4.42</v>
       </c>
       <c r="I122" t="n">
-        <v>10.73</v>
+        <v>4.79</v>
       </c>
       <c r="J122" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>1.28, 4.89, 7.32</t>
+          <t>1.72, 4.20, 4.36</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>jue 05/11 11:45</t>
+          <t>vie 06/11 13:30</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>NEC Nijmegen vs Omonoia FC</t>
+          <t>Hamburger SV vs Borussia Monchengladbach</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1.88</v>
+        <v>2.5</v>
       </c>
       <c r="E123" t="n">
-        <v>4.42</v>
+        <v>4.11</v>
       </c>
       <c r="F123" t="n">
-        <v>4.52</v>
+        <v>2.96</v>
       </c>
       <c r="G123" t="n">
-        <v>1.84</v>
+        <v>2.46</v>
       </c>
       <c r="H123" t="n">
-        <v>4.33</v>
+        <v>4.03</v>
       </c>
       <c r="I123" t="n">
-        <v>4.43</v>
+        <v>2.9</v>
       </c>
       <c r="J123" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>1.77, 4.00, 4.18</t>
+          <t>2.40, 3.74, 2.74</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>jue 05/11 11:45</t>
+          <t>vie 06/11 13:45</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Real Sociedad vs Lyon</t>
+          <t>Toulouse vs Strasbourg</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="E124" t="n">
-        <v>4.25</v>
+        <v>4.18</v>
       </c>
       <c r="F124" t="n">
-        <v>3.92</v>
+        <v>3.63</v>
       </c>
       <c r="G124" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="H124" t="n">
-        <v>4.16</v>
+        <v>4.1</v>
       </c>
       <c r="I124" t="n">
-        <v>3.84</v>
+        <v>3.56</v>
       </c>
       <c r="J124" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>1.93, 3.86, 3.66</t>
+          <t>2.08, 3.70, 3.34</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>jue 05/11 14:00</t>
+          <t>vie 06/11 14:00</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Celtic vs Besiktas JK</t>
+          <t>Everton vs Coventry City</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>3.11</v>
+        <v>1.8</v>
       </c>
       <c r="E125" t="n">
-        <v>4.02</v>
+        <v>4.35</v>
       </c>
       <c r="F125" t="n">
-        <v>2.44</v>
+        <v>5.16</v>
       </c>
       <c r="G125" t="n">
-        <v>3.05</v>
+        <v>1.76</v>
       </c>
       <c r="H125" t="n">
-        <v>3.94</v>
+        <v>4.26</v>
       </c>
       <c r="I125" t="n">
-        <v>2.39</v>
+        <v>5.06</v>
       </c>
       <c r="J125" t="n">
         <v>17</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>2.87, 3.78, 2.29</t>
+          <t>1.71, 3.98, 4.59</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>jue 05/11 14:00</t>
+          <t>vie 06/11 14:00</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Celta Vigo vs Union Saint-Gilloise</t>
+          <t>Sevilla vs Alavés</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="E126" t="n">
-        <v>4.06</v>
+        <v>3.61</v>
       </c>
       <c r="F126" t="n">
-        <v>3.7</v>
+        <v>4.18</v>
       </c>
       <c r="G126" t="n">
         <v>2.11</v>
       </c>
       <c r="H126" t="n">
-        <v>3.98</v>
+        <v>3.54</v>
       </c>
       <c r="I126" t="n">
-        <v>3.62</v>
+        <v>4.1</v>
       </c>
       <c r="J126" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>2.01, 3.79, 3.44</t>
+          <t>2.07, 3.30, 3.77</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>jue 05/11 14:00</t>
+          <t>vie 06/11 17:00</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>Brasil Serie A</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Sunderland vs Dinamo Zagreb</t>
+          <t>Vitoria vs Fluminense</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1.52</v>
+        <v>3.29</v>
       </c>
       <c r="E127" t="n">
-        <v>5.15</v>
+        <v>3.65</v>
       </c>
       <c r="F127" t="n">
-        <v>7.7</v>
+        <v>2.49</v>
       </c>
       <c r="G127" t="n">
-        <v>1.49</v>
+        <v>3.22</v>
       </c>
       <c r="H127" t="n">
-        <v>5.05</v>
+        <v>3.58</v>
       </c>
       <c r="I127" t="n">
-        <v>7.54</v>
+        <v>2.44</v>
       </c>
       <c r="J127" t="n">
-        <v>17</v>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>1.45, 4.69, 6.53</t>
-        </is>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="K127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>jue 05/11 14:00</t>
+          <t>vie 06/11 19:00</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>Liga MX</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Torreense vs FC Ararat-Armenia</t>
+          <t>Atlético San Luis vs FC Juárez</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="E128" t="n">
-        <v>4.15</v>
+        <v>4.4</v>
       </c>
       <c r="F128" t="n">
-        <v>5.06</v>
+        <v>5.19</v>
       </c>
       <c r="G128" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="H128" t="n">
-        <v>4.07</v>
+        <v>4.32</v>
       </c>
       <c r="I128" t="n">
-        <v>4.96</v>
+        <v>5.09</v>
       </c>
       <c r="J128" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>1.78, 3.90, 4.24</t>
+          <t>1.75, 3.93, 4.47</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>jue 05/11 14:00</t>
+          <t>sáb 07/11 06:30</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva vs OFI Crete</t>
+          <t>Leeds United vs Tottenham Hotspur</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>2.23</v>
+        <v>2.69</v>
       </c>
       <c r="E129" t="n">
-        <v>3.97</v>
+        <v>3.72</v>
       </c>
       <c r="F129" t="n">
-        <v>3.58</v>
+        <v>2.94</v>
       </c>
       <c r="G129" t="n">
-        <v>2.18</v>
+        <v>2.64</v>
       </c>
       <c r="H129" t="n">
-        <v>3.89</v>
+        <v>3.65</v>
       </c>
       <c r="I129" t="n">
-        <v>3.51</v>
+        <v>2.88</v>
       </c>
       <c r="J129" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>2.15, 3.61, 3.24</t>
+          <t>2.58, 3.35, 2.76</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>jue 05/11 14:00</t>
+          <t>sáb 07/11 07:00</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>SK Sturm Graz vs NK Celje</t>
+          <t>Málaga vs Real Racing Club de Santander</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1.67</v>
+        <v>2.54</v>
       </c>
       <c r="E130" t="n">
-        <v>4.73</v>
+        <v>3.93</v>
       </c>
       <c r="F130" t="n">
-        <v>5.85</v>
+        <v>3.01</v>
       </c>
       <c r="G130" t="n">
-        <v>1.64</v>
+        <v>2.49</v>
       </c>
       <c r="H130" t="n">
-        <v>4.64</v>
+        <v>3.85</v>
       </c>
       <c r="I130" t="n">
-        <v>5.73</v>
+        <v>2.95</v>
       </c>
       <c r="J130" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>1.57, 4.39, 5.20</t>
+          <t>2.42, 3.51, 2.84</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>jue 05/11 14:00</t>
+          <t>sáb 07/11 08:30</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen vs Marseille</t>
+          <t>SC Paderborn vs Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1.5</v>
+        <v>3.19</v>
       </c>
       <c r="E131" t="n">
-        <v>5.51</v>
+        <v>4.29</v>
       </c>
       <c r="F131" t="n">
-        <v>7.61</v>
+        <v>2.3</v>
       </c>
       <c r="G131" t="n">
-        <v>1.47</v>
+        <v>3.13</v>
       </c>
       <c r="H131" t="n">
-        <v>5.4</v>
+        <v>4.21</v>
       </c>
       <c r="I131" t="n">
-        <v>7.46</v>
+        <v>2.26</v>
       </c>
       <c r="J131" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>1.41, 5.14, 6.61</t>
+          <t>3.03, 3.84, 2.17</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>jue 05/11 14:00</t>
+          <t>sáb 07/11 08:30</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Benfica vs Lech Poznań</t>
+          <t>FSV Mainz 05 vs Bayern Munich</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1.23</v>
+        <v>6.67</v>
       </c>
       <c r="E132" t="n">
-        <v>8.59</v>
+        <v>6.64</v>
       </c>
       <c r="F132" t="n">
-        <v>19.83</v>
+        <v>1.47</v>
       </c>
       <c r="G132" t="n">
-        <v>1.21</v>
+        <v>6.53</v>
       </c>
       <c r="H132" t="n">
-        <v>8.42</v>
+        <v>6.51</v>
       </c>
       <c r="I132" t="n">
-        <v>19.44</v>
+        <v>1.44</v>
       </c>
       <c r="J132" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>1.16, 6.18, 10.81</t>
+          <t>5.12, 6.32, 1.42</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>jue 05/11 14:00</t>
+          <t>sáb 07/11 08:30</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>AZ Alkmaar vs Juventus</t>
+          <t>RB Leipzig vs Augsburg</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>3.88</v>
+        <v>1.52</v>
       </c>
       <c r="E133" t="n">
-        <v>3.96</v>
+        <v>5.98</v>
       </c>
       <c r="F133" t="n">
-        <v>2.13</v>
+        <v>6.38</v>
       </c>
       <c r="G133" t="n">
-        <v>3.8</v>
+        <v>1.49</v>
       </c>
       <c r="H133" t="n">
-        <v>3.89</v>
+        <v>5.87</v>
       </c>
       <c r="I133" t="n">
-        <v>2.08</v>
+        <v>6.25</v>
       </c>
       <c r="J133" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>3.66, 3.76, 1.95</t>
+          <t>1.44, 5.43, 5.58</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>jue 05/11 16:30</t>
+          <t>sáb 07/11 08:30</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Brasil Serie A</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Palmeiras vs Remo</t>
+          <t>Borussia Dortmund vs Elversberg</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="E134" t="n">
-        <v>7.53</v>
+        <v>7.27</v>
       </c>
       <c r="F134" t="n">
-        <v>18.41</v>
+        <v>10.66</v>
       </c>
       <c r="G134" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="H134" t="n">
-        <v>7.38</v>
+        <v>7.13</v>
       </c>
       <c r="I134" t="n">
-        <v>18.05</v>
+        <v>10.45</v>
       </c>
       <c r="J134" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>1.24, 6.52, 11.49</t>
+          <t>1.26, 6.53, 8.74</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>jue 05/11 18:30</t>
+          <t>sáb 07/11 09:00</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Brasil Serie A</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Cruzeiro vs Bahia</t>
+          <t>Arsenal vs Hull City</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1.86</v>
+        <v>1.21</v>
       </c>
       <c r="E135" t="n">
-        <v>4.39</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="F135" t="n">
-        <v>4.65</v>
+        <v>23.81</v>
       </c>
       <c r="G135" t="n">
-        <v>1.82</v>
+        <v>1.19</v>
       </c>
       <c r="H135" t="n">
-        <v>4.31</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="I135" t="n">
-        <v>4.56</v>
+        <v>23.34</v>
       </c>
       <c r="J135" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>1.72, 4.19, 4.35</t>
+          <t>1.16, 7.57, 15.23</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>vie 06/11 13:30</t>
+          <t>sáb 07/11 09:00</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Bundesliga</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Hamburger SV vs Borussia Monchengladbach</t>
+          <t>Fulham vs Newcastle United</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>2.51</v>
+        <v>2.37</v>
       </c>
       <c r="E136" t="n">
-        <v>4.1</v>
+        <v>3.93</v>
       </c>
       <c r="F136" t="n">
-        <v>2.96</v>
+        <v>3.28</v>
       </c>
       <c r="G136" t="n">
-        <v>2.46</v>
+        <v>2.33</v>
       </c>
       <c r="H136" t="n">
-        <v>4.02</v>
+        <v>3.85</v>
       </c>
       <c r="I136" t="n">
-        <v>2.9</v>
+        <v>3.22</v>
       </c>
       <c r="J136" t="n">
         <v>16</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>2.40, 3.74, 2.74</t>
+          <t>2.24, 3.55, 3.12</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>vie 06/11 13:45</t>
+          <t>sáb 07/11 09:15</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Toulouse vs Strasbourg</t>
+          <t>Espanyol vs Deportivo La Coruña</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="E137" t="n">
-        <v>4.17</v>
+        <v>3.75</v>
       </c>
       <c r="F137" t="n">
-        <v>3.66</v>
+        <v>3.63</v>
       </c>
       <c r="G137" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="H137" t="n">
-        <v>4.09</v>
+        <v>3.67</v>
       </c>
       <c r="I137" t="n">
-        <v>3.59</v>
+        <v>3.56</v>
       </c>
       <c r="J137" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>2.08, 3.70, 3.34</t>
+          <t>2.17, 3.50, 3.28</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>vie 06/11 14:00</t>
+          <t>sáb 07/11 10:15</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Sevilla vs Alavés</t>
+          <t>Auxerre vs Paris FC</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>2.2</v>
+        <v>3.94</v>
       </c>
       <c r="E138" t="n">
-        <v>3.58</v>
+        <v>4.13</v>
       </c>
       <c r="F138" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="G138" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="H138" t="n">
         <v>4.05</v>
       </c>
-      <c r="G138" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="H138" t="n">
-        <v>3.51</v>
-      </c>
       <c r="I138" t="n">
-        <v>3.97</v>
+        <v>2.03</v>
       </c>
       <c r="J138" t="n">
         <v>15</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>2.07, 3.30, 3.77</t>
+          <t>3.68, 3.81, 1.93</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>vie 06/11 14:00</t>
+          <t>sáb 07/11 11:30</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -6378,380 +6382,384 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Everton vs Coventry City</t>
+          <t>Nottingham Forest vs Manchester City</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1.79</v>
+        <v>5.19</v>
       </c>
       <c r="E139" t="n">
-        <v>4.34</v>
+        <v>4.54</v>
       </c>
       <c r="F139" t="n">
-        <v>5.2</v>
+        <v>1.76</v>
       </c>
       <c r="G139" t="n">
-        <v>1.76</v>
+        <v>5.09</v>
       </c>
       <c r="H139" t="n">
-        <v>4.26</v>
+        <v>4.45</v>
       </c>
       <c r="I139" t="n">
-        <v>5.1</v>
+        <v>1.73</v>
       </c>
       <c r="J139" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>1.70, 4.02, 4.59</t>
+          <t>4.70, 4.01, 1.69</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>vie 06/11 17:00</t>
+          <t>sáb 07/11 11:30</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Brasil Serie A</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Vitoria vs Fluminense</t>
+          <t>VfB Stuttgart vs Werder Bremen</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>3.27</v>
+        <v>1.53</v>
       </c>
       <c r="E140" t="n">
-        <v>3.66</v>
+        <v>5.86</v>
       </c>
       <c r="F140" t="n">
-        <v>2.49</v>
+        <v>6.45</v>
       </c>
       <c r="G140" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="H140" t="n">
-        <v>3.59</v>
+        <v>5.75</v>
       </c>
       <c r="I140" t="n">
-        <v>2.44</v>
+        <v>6.32</v>
       </c>
       <c r="J140" t="n">
-        <v>16</v>
-      </c>
-      <c r="K140" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>1.49, 5.10, 5.29</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>sáb 07/11 06:30</t>
+          <t>sáb 07/11 11:30</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Leeds United vs Tottenham Hotspur</t>
+          <t>CA Osasuna vs Athletic Bilbao</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>2.76</v>
+        <v>3.6</v>
       </c>
       <c r="E141" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="F141" t="n">
-        <v>2.88</v>
+        <v>2.34</v>
       </c>
       <c r="G141" t="n">
-        <v>2.7</v>
+        <v>3.53</v>
       </c>
       <c r="H141" t="n">
-        <v>3.63</v>
+        <v>3.57</v>
       </c>
       <c r="I141" t="n">
-        <v>2.82</v>
+        <v>2.29</v>
       </c>
       <c r="J141" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>2.58, 3.35, 2.76</t>
+          <t>3.29, 3.35, 2.23</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>sáb 07/11 07:00</t>
+          <t>sáb 07/11 13:45</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Málaga vs Real Racing Club de Santander</t>
+          <t>Paris Saint Germain vs Troyes</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>2.54</v>
+        <v>1.18</v>
       </c>
       <c r="E142" t="n">
-        <v>3.93</v>
+        <v>11.31</v>
       </c>
       <c r="F142" t="n">
-        <v>3.01</v>
+        <v>23.84</v>
       </c>
       <c r="G142" t="n">
-        <v>2.49</v>
+        <v>1.15</v>
       </c>
       <c r="H142" t="n">
-        <v>3.85</v>
+        <v>11.09</v>
       </c>
       <c r="I142" t="n">
-        <v>2.95</v>
+        <v>23.38</v>
       </c>
       <c r="J142" t="n">
         <v>15</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>2.42, 3.51, 2.84</t>
+          <t>1.13, 9.97, 14.06</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>sáb 07/11 08:30</t>
+          <t>sáb 07/11 14:00</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Bundesliga</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Borussia Dortmund vs Elversberg</t>
+          <t>Valencia vs Real Madrid</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1.34</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="E143" t="n">
-        <v>7.2</v>
+        <v>6.26</v>
       </c>
       <c r="F143" t="n">
-        <v>10.67</v>
+        <v>1.4</v>
       </c>
       <c r="G143" t="n">
-        <v>1.31</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="H143" t="n">
-        <v>7.06</v>
+        <v>6.14</v>
       </c>
       <c r="I143" t="n">
-        <v>10.46</v>
+        <v>1.38</v>
       </c>
       <c r="J143" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>1.26, 6.53, 8.74</t>
+          <t>6.91, 5.83, 1.35</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>sáb 07/11 08:30</t>
+          <t>dom 08/11 07:00</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Bundesliga</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>SC Paderborn vs Eintracht Frankfurt</t>
+          <t>Elche CF vs Real Betis</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>3.13</v>
+        <v>3.44</v>
       </c>
       <c r="E144" t="n">
-        <v>4.28</v>
+        <v>4.05</v>
       </c>
       <c r="F144" t="n">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="G144" t="n">
-        <v>3.07</v>
+        <v>3.37</v>
       </c>
       <c r="H144" t="n">
-        <v>4.2</v>
+        <v>3.97</v>
       </c>
       <c r="I144" t="n">
-        <v>2.29</v>
+        <v>2.21</v>
       </c>
       <c r="J144" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>2.94, 3.84, 2.22</t>
+          <t>3.08, 3.78, 2.17</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>sáb 07/11 08:30</t>
+          <t>dom 08/11 08:00</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Bundesliga</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>FSV Mainz 05 vs Bayern Munich</t>
+          <t>Ipswich Town vs Bournemouth</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>6.21</v>
+        <v>4</v>
       </c>
       <c r="E145" t="n">
-        <v>6.36</v>
+        <v>4.11</v>
       </c>
       <c r="F145" t="n">
-        <v>1.51</v>
+        <v>2.05</v>
       </c>
       <c r="G145" t="n">
-        <v>6.09</v>
+        <v>3.92</v>
       </c>
       <c r="H145" t="n">
-        <v>6.23</v>
+        <v>4.03</v>
       </c>
       <c r="I145" t="n">
-        <v>1.48</v>
+        <v>2.01</v>
       </c>
       <c r="J145" t="n">
         <v>16</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>4.69, 6.09, 1.47</t>
+          <t>3.77, 3.67, 1.94</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>sáb 07/11 08:30</t>
+          <t>dom 08/11 08:00</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Bundesliga</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>RB Leipzig vs Augsburg</t>
+          <t>Sunderland vs Chelsea</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1.54</v>
+        <v>3.6</v>
       </c>
       <c r="E146" t="n">
-        <v>5.88</v>
+        <v>3.85</v>
       </c>
       <c r="F146" t="n">
-        <v>6.23</v>
+        <v>2.26</v>
       </c>
       <c r="G146" t="n">
-        <v>1.51</v>
+        <v>3.53</v>
       </c>
       <c r="H146" t="n">
-        <v>5.77</v>
+        <v>3.78</v>
       </c>
       <c r="I146" t="n">
-        <v>6.1</v>
+        <v>2.21</v>
       </c>
       <c r="J146" t="n">
         <v>16</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>1.44, 5.43, 5.58</t>
+          <t>3.27, 3.63, 2.13</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>sáb 07/11 09:00</t>
+          <t>dom 08/11 08:00</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Arsenal vs Hull City</t>
+          <t>Rennes vs Lille</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1.21</v>
+        <v>2.11</v>
       </c>
       <c r="E147" t="n">
-        <v>8.779999999999999</v>
+        <v>4.17</v>
       </c>
       <c r="F147" t="n">
-        <v>23.77</v>
+        <v>3.77</v>
       </c>
       <c r="G147" t="n">
-        <v>1.19</v>
+        <v>2.06</v>
       </c>
       <c r="H147" t="n">
-        <v>8.6</v>
+        <v>4.08</v>
       </c>
       <c r="I147" t="n">
-        <v>23.3</v>
+        <v>3.69</v>
       </c>
       <c r="J147" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>1.16, 7.57, 15.23</t>
+          <t>2.01, 3.70, 3.55</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>sáb 07/11 09:00</t>
+          <t>dom 08/11 08:00</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6761,126 +6769,126 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Fulham vs Newcastle United</t>
+          <t>Brighton and Hove Albion vs Brentford</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>2.37</v>
+        <v>2.03</v>
       </c>
       <c r="E148" t="n">
-        <v>3.93</v>
+        <v>4.23</v>
       </c>
       <c r="F148" t="n">
-        <v>3.29</v>
+        <v>3.99</v>
       </c>
       <c r="G148" t="n">
-        <v>2.32</v>
+        <v>1.99</v>
       </c>
       <c r="H148" t="n">
-        <v>3.85</v>
+        <v>4.15</v>
       </c>
       <c r="I148" t="n">
-        <v>3.23</v>
+        <v>3.91</v>
       </c>
       <c r="J148" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>2.24, 3.55, 3.12</t>
+          <t>1.95, 3.84, 3.59</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>sáb 07/11 09:15</t>
+          <t>dom 08/11 08:00</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Espanyol vs Deportivo La Coruña</t>
+          <t>Crystal Palace vs Liverpool</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>2.29</v>
+        <v>4.9</v>
       </c>
       <c r="E149" t="n">
-        <v>3.76</v>
+        <v>4.53</v>
       </c>
       <c r="F149" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="G149" t="n">
-        <v>2.25</v>
+        <v>4.8</v>
       </c>
       <c r="H149" t="n">
-        <v>3.68</v>
+        <v>4.44</v>
       </c>
       <c r="I149" t="n">
-        <v>3.53</v>
+        <v>1.77</v>
       </c>
       <c r="J149" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>2.18, 3.50, 3.28</t>
+          <t>4.50, 4.04, 1.71</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>sáb 07/11 10:15</t>
+          <t>dom 08/11 08:30</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Auxerre vs Paris FC</t>
+          <t>1. FC Köln vs Bayer Leverkusen</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>3.96</v>
+        <v>4.85</v>
       </c>
       <c r="E150" t="n">
-        <v>4.12</v>
+        <v>4.88</v>
       </c>
       <c r="F150" t="n">
-        <v>2.06</v>
+        <v>1.76</v>
       </c>
       <c r="G150" t="n">
-        <v>3.88</v>
+        <v>4.76</v>
       </c>
       <c r="H150" t="n">
-        <v>4.04</v>
+        <v>4.79</v>
       </c>
       <c r="I150" t="n">
-        <v>2.02</v>
+        <v>1.72</v>
       </c>
       <c r="J150" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>3.68, 3.81, 1.93</t>
+          <t>4.51, 4.39, 1.65</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>sáb 07/11 11:30</t>
+          <t>dom 08/11 09:15</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6890,126 +6898,126 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>CA Osasuna vs Athletic Bilbao</t>
+          <t>Real Sociedad vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>3.6</v>
+        <v>1.86</v>
       </c>
       <c r="E151" t="n">
-        <v>3.63</v>
+        <v>4.33</v>
       </c>
       <c r="F151" t="n">
-        <v>2.34</v>
+        <v>4.73</v>
       </c>
       <c r="G151" t="n">
-        <v>3.53</v>
+        <v>1.82</v>
       </c>
       <c r="H151" t="n">
-        <v>3.56</v>
+        <v>4.25</v>
       </c>
       <c r="I151" t="n">
-        <v>2.3</v>
+        <v>4.64</v>
       </c>
       <c r="J151" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>3.29, 3.35, 2.23</t>
+          <t>1.76, 3.98, 4.29</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>sáb 07/11 11:30</t>
+          <t>dom 08/11 10:15</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Bundesliga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>VfB Stuttgart vs Werder Bremen</t>
+          <t>Le Havre vs Lorient</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1.53</v>
+        <v>2.98</v>
       </c>
       <c r="E152" t="n">
-        <v>5.8</v>
+        <v>3.66</v>
       </c>
       <c r="F152" t="n">
-        <v>6.46</v>
+        <v>2.69</v>
       </c>
       <c r="G152" t="n">
-        <v>1.5</v>
+        <v>2.93</v>
       </c>
       <c r="H152" t="n">
-        <v>5.68</v>
+        <v>3.59</v>
       </c>
       <c r="I152" t="n">
-        <v>6.34</v>
+        <v>2.63</v>
       </c>
       <c r="J152" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>1.49, 5.10, 5.29</t>
+          <t>2.85, 3.37, 2.49</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>sáb 07/11 11:30</t>
+          <t>dom 08/11 10:15</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Nottingham Forest vs Manchester City</t>
+          <t>Le Mans FC vs AS Monaco</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>5.56</v>
+        <v>4.65</v>
       </c>
       <c r="E153" t="n">
-        <v>4.66</v>
+        <v>4.55</v>
       </c>
       <c r="F153" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="G153" t="n">
-        <v>5.45</v>
+        <v>4.56</v>
       </c>
       <c r="H153" t="n">
-        <v>4.57</v>
+        <v>4.46</v>
       </c>
       <c r="I153" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="J153" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>4.95, 4.10, 1.64</t>
+          <t>4.01, 4.20, 1.77</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>sáb 07/11 13:45</t>
+          <t>dom 08/11 10:15</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -7019,1207 +7027,691 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Paris Saint Germain vs Troyes</t>
+          <t>Angers vs Nice</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1.18</v>
+        <v>3.7</v>
       </c>
       <c r="E154" t="n">
-        <v>11.17</v>
+        <v>4</v>
       </c>
       <c r="F154" t="n">
-        <v>23.64</v>
+        <v>2.17</v>
       </c>
       <c r="G154" t="n">
-        <v>1.16</v>
+        <v>3.63</v>
       </c>
       <c r="H154" t="n">
-        <v>10.95</v>
+        <v>3.92</v>
       </c>
       <c r="I154" t="n">
-        <v>23.17</v>
+        <v>2.13</v>
       </c>
       <c r="J154" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>1.13, 9.97, 14.06</t>
+          <t>3.56, 3.60, 2.03</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>sáb 07/11 14:00</t>
+          <t>dom 08/11 10:15</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Valencia vs Real Madrid</t>
+          <t>Brest vs Lyon</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>8.48</v>
+        <v>3.09</v>
       </c>
       <c r="E155" t="n">
-        <v>6.12</v>
+        <v>4</v>
       </c>
       <c r="F155" t="n">
-        <v>1.43</v>
+        <v>2.46</v>
       </c>
       <c r="G155" t="n">
-        <v>8.32</v>
+        <v>3.03</v>
       </c>
       <c r="H155" t="n">
-        <v>6</v>
+        <v>3.92</v>
       </c>
       <c r="I155" t="n">
-        <v>1.4</v>
+        <v>2.41</v>
       </c>
       <c r="J155" t="n">
         <v>15</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>6.58, 5.70, 1.37</t>
+          <t>2.90, 3.65, 2.32</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>dom 08/11 07:00</t>
+          <t>dom 08/11 10:30</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Elche CF vs Real Betis</t>
+          <t>Manchester United vs Aston Villa</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>3.52</v>
+        <v>2.31</v>
       </c>
       <c r="E156" t="n">
-        <v>3.99</v>
+        <v>4.13</v>
       </c>
       <c r="F156" t="n">
-        <v>2.24</v>
+        <v>3.27</v>
       </c>
       <c r="G156" t="n">
-        <v>3.45</v>
+        <v>2.27</v>
       </c>
       <c r="H156" t="n">
-        <v>3.91</v>
+        <v>4.05</v>
       </c>
       <c r="I156" t="n">
-        <v>2.2</v>
+        <v>3.21</v>
       </c>
       <c r="J156" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>3.08, 3.78, 2.17</t>
+          <t>2.17, 3.81, 3.06</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>dom 08/11 08:00</t>
+          <t>dom 08/11 10:30</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Crystal Palace vs Liverpool</t>
+          <t>SC Freiburg vs Union Berlin</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>4.93</v>
+        <v>1.55</v>
       </c>
       <c r="E157" t="n">
-        <v>4.49</v>
+        <v>5.22</v>
       </c>
       <c r="F157" t="n">
-        <v>1.8</v>
+        <v>6.91</v>
       </c>
       <c r="G157" t="n">
-        <v>4.83</v>
+        <v>1.52</v>
       </c>
       <c r="H157" t="n">
-        <v>4.4</v>
+        <v>5.12</v>
       </c>
       <c r="I157" t="n">
-        <v>1.77</v>
+        <v>6.78</v>
       </c>
       <c r="J157" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>4.50, 4.04, 1.71</t>
+          <t>1.50, 4.57, 5.88</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>dom 08/11 08:00</t>
+          <t>dom 08/11 11:30</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Brighton and Hove Albion vs Brentford</t>
+          <t>Villarreal vs Getafe</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>2.02</v>
+        <v>1.55</v>
       </c>
       <c r="E158" t="n">
-        <v>4.22</v>
+        <v>4.83</v>
       </c>
       <c r="F158" t="n">
-        <v>4.03</v>
+        <v>7.87</v>
       </c>
       <c r="G158" t="n">
-        <v>1.98</v>
+        <v>1.52</v>
       </c>
       <c r="H158" t="n">
-        <v>4.14</v>
+        <v>4.73</v>
       </c>
       <c r="I158" t="n">
-        <v>3.96</v>
+        <v>7.72</v>
       </c>
       <c r="J158" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>1.95, 3.84, 3.59</t>
+          <t>1.47, 4.37, 6.68</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>dom 08/11 08:00</t>
+          <t>dom 08/11 11:30</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Rennes vs Lille</t>
+          <t>Celta Vigo vs Levante</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="E159" t="n">
-        <v>4.17</v>
+        <v>4.18</v>
       </c>
       <c r="F159" t="n">
-        <v>3.79</v>
+        <v>4.8</v>
       </c>
       <c r="G159" t="n">
-        <v>2.06</v>
+        <v>1.84</v>
       </c>
       <c r="H159" t="n">
-        <v>4.09</v>
+        <v>4.1</v>
       </c>
       <c r="I159" t="n">
-        <v>3.72</v>
+        <v>4.71</v>
       </c>
       <c r="J159" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>2.01, 3.70, 3.55</t>
+          <t>1.76, 4.00, 4.25</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>dom 08/11 08:00</t>
+          <t>dom 08/11 12:30</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Sunderland vs Chelsea</t>
+          <t>TSG Hoffenheim vs FC Schalke 04</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>3.64</v>
+        <v>1.7</v>
       </c>
       <c r="E160" t="n">
-        <v>3.85</v>
+        <v>4.91</v>
       </c>
       <c r="F160" t="n">
-        <v>2.25</v>
+        <v>5.29</v>
       </c>
       <c r="G160" t="n">
-        <v>3.56</v>
+        <v>1.67</v>
       </c>
       <c r="H160" t="n">
-        <v>3.77</v>
+        <v>4.82</v>
       </c>
       <c r="I160" t="n">
-        <v>2.2</v>
+        <v>5.18</v>
       </c>
       <c r="J160" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>3.27, 3.63, 2.13</t>
+          <t>1.62, 4.46, 4.63</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>dom 08/11 08:00</t>
+          <t>dom 08/11 13:45</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Ipswich Town vs Bournemouth</t>
+          <t>RC Lens vs Marseille</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>4</v>
+        <v>2.18</v>
       </c>
       <c r="E161" t="n">
-        <v>4.12</v>
+        <v>4.32</v>
       </c>
       <c r="F161" t="n">
-        <v>2.05</v>
+        <v>3.45</v>
       </c>
       <c r="G161" t="n">
-        <v>3.92</v>
+        <v>2.13</v>
       </c>
       <c r="H161" t="n">
-        <v>4.04</v>
+        <v>4.24</v>
       </c>
       <c r="I161" t="n">
-        <v>2.01</v>
+        <v>3.39</v>
       </c>
       <c r="J161" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>3.77, 3.67, 1.94</t>
+          <t>2.07, 3.91, 3.21</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>dom 08/11 08:30</t>
+          <t>dom 08/11 14:00</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Bundesliga</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>1. FC Köln vs Bayer Leverkusen</t>
+          <t>Atlético Madrid vs Barcelona</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>4.86</v>
+        <v>4</v>
       </c>
       <c r="E162" t="n">
-        <v>4.87</v>
+        <v>4.63</v>
       </c>
       <c r="F162" t="n">
-        <v>1.76</v>
+        <v>1.94</v>
       </c>
       <c r="G162" t="n">
-        <v>4.76</v>
+        <v>3.92</v>
       </c>
       <c r="H162" t="n">
-        <v>4.77</v>
+        <v>4.54</v>
       </c>
       <c r="I162" t="n">
-        <v>1.72</v>
+        <v>1.91</v>
       </c>
       <c r="J162" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>4.51, 4.39, 1.65</t>
+          <t>3.80, 4.23, 1.81</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>dom 08/11 09:15</t>
+          <t>jue 12/11 11:00</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Nations League</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Real Sociedad vs Rayo Vallecano</t>
+          <t>Turkey vs Belgium</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1.9</v>
+        <v>4.73</v>
       </c>
       <c r="E163" t="n">
-        <v>4.27</v>
+        <v>4.58</v>
       </c>
       <c r="F163" t="n">
-        <v>4.57</v>
+        <v>1.82</v>
       </c>
       <c r="G163" t="n">
-        <v>1.86</v>
+        <v>4.64</v>
       </c>
       <c r="H163" t="n">
-        <v>4.19</v>
+        <v>4.49</v>
       </c>
       <c r="I163" t="n">
-        <v>4.48</v>
+        <v>1.78</v>
       </c>
       <c r="J163" t="n">
-        <v>15</v>
-      </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>1.76, 3.98, 4.29</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="K163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>dom 08/11 10:15</t>
+          <t>jue 12/11 13:45</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Nations League</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Le Havre vs Lorient</t>
+          <t>Italy vs France</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>2.92</v>
+        <v>4.43</v>
       </c>
       <c r="E164" t="n">
-        <v>3.65</v>
+        <v>4.15</v>
       </c>
       <c r="F164" t="n">
-        <v>2.75</v>
+        <v>1.95</v>
       </c>
       <c r="G164" t="n">
-        <v>2.86</v>
+        <v>4.34</v>
       </c>
       <c r="H164" t="n">
-        <v>3.58</v>
+        <v>4.07</v>
       </c>
       <c r="I164" t="n">
-        <v>2.69</v>
+        <v>1.91</v>
       </c>
       <c r="J164" t="n">
-        <v>16</v>
-      </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>2.72, 3.32, 2.63</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="K164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>dom 08/11 10:15</t>
+          <t>jue 12/11 13:45</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Nations League</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Le Mans FC vs AS Monaco</t>
+          <t>Czech Republic vs Spain</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>4.63</v>
+        <v>49.28</v>
       </c>
       <c r="E165" t="n">
-        <v>4.58</v>
+        <v>9.75</v>
       </c>
       <c r="F165" t="n">
-        <v>1.83</v>
+        <v>1.17</v>
       </c>
       <c r="G165" t="n">
-        <v>4.54</v>
+        <v>48.31</v>
       </c>
       <c r="H165" t="n">
-        <v>4.49</v>
+        <v>9.56</v>
       </c>
       <c r="I165" t="n">
-        <v>1.8</v>
+        <v>1.14</v>
       </c>
       <c r="J165" t="n">
-        <v>16</v>
-      </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>4.01, 4.20, 1.77</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="K165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>dom 08/11 10:15</t>
+          <t>jue 12/11 13:45</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Nations League</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Angers vs Nice</t>
+          <t>England vs Croatia</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>3.6</v>
+        <v>1.29</v>
       </c>
       <c r="E166" t="n">
-        <v>3.98</v>
+        <v>7.32</v>
       </c>
       <c r="F166" t="n">
-        <v>2.21</v>
+        <v>14.82</v>
       </c>
       <c r="G166" t="n">
-        <v>3.53</v>
+        <v>1.26</v>
       </c>
       <c r="H166" t="n">
-        <v>3.9</v>
+        <v>7.18</v>
       </c>
       <c r="I166" t="n">
-        <v>2.17</v>
+        <v>14.53</v>
       </c>
       <c r="J166" t="n">
-        <v>16</v>
-      </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>3.35, 3.53, 2.13</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="K166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>dom 08/11 10:15</t>
+          <t>vie 13/11 13:45</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Nations League</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Brest vs Lyon</t>
+          <t>Netherlands vs Greece</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>3.09</v>
+        <v>1.49</v>
       </c>
       <c r="E167" t="n">
-        <v>4</v>
+        <v>5.44</v>
       </c>
       <c r="F167" t="n">
-        <v>2.46</v>
+        <v>7.89</v>
       </c>
       <c r="G167" t="n">
-        <v>3.03</v>
+        <v>1.46</v>
       </c>
       <c r="H167" t="n">
-        <v>3.92</v>
+        <v>5.33</v>
       </c>
       <c r="I167" t="n">
-        <v>2.41</v>
+        <v>7.73</v>
       </c>
       <c r="J167" t="n">
-        <v>16</v>
-      </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>2.90, 3.65, 2.32</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="K167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>dom 08/11 10:30</t>
+          <t>vie 13/11 13:45</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Bundesliga</t>
+          <t>Nations League</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>SC Freiburg vs Union Berlin</t>
+          <t>Serbia vs Germany</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>1.55</v>
+        <v>13.43</v>
       </c>
       <c r="E168" t="n">
-        <v>5.2</v>
+        <v>7.03</v>
       </c>
       <c r="F168" t="n">
-        <v>6.92</v>
+        <v>1.31</v>
       </c>
       <c r="G168" t="n">
-        <v>1.52</v>
+        <v>13.16</v>
       </c>
       <c r="H168" t="n">
-        <v>5.1</v>
+        <v>6.89</v>
       </c>
       <c r="I168" t="n">
-        <v>6.78</v>
+        <v>1.28</v>
       </c>
       <c r="J168" t="n">
-        <v>16</v>
-      </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>1.50, 4.57, 5.88</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="K168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>dom 08/11 10:30</t>
+          <t>sáb 14/11 11:00</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Nations League</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Manchester United vs Aston Villa</t>
+          <t>Norway vs Wales</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>2.34</v>
+        <v>1.28</v>
       </c>
       <c r="E169" t="n">
-        <v>4.13</v>
+        <v>7.69</v>
       </c>
       <c r="F169" t="n">
-        <v>3.22</v>
+        <v>14.95</v>
       </c>
       <c r="G169" t="n">
-        <v>2.29</v>
+        <v>1.25</v>
       </c>
       <c r="H169" t="n">
-        <v>4.05</v>
+        <v>7.54</v>
       </c>
       <c r="I169" t="n">
-        <v>3.15</v>
+        <v>14.66</v>
       </c>
       <c r="J169" t="n">
-        <v>17</v>
-      </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>2.18, 3.81, 3.03</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="K169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>dom 08/11 11:30</t>
+          <t>sáb 14/11 13:45</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Nations League</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Celta Vigo vs Levante</t>
+          <t>Portugal vs Denmark</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1.87</v>
+        <v>1.46</v>
       </c>
       <c r="E170" t="n">
-        <v>4.2</v>
+        <v>5.57</v>
       </c>
       <c r="F170" t="n">
-        <v>4.79</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="G170" t="n">
-        <v>1.84</v>
+        <v>1.43</v>
       </c>
       <c r="H170" t="n">
-        <v>4.12</v>
+        <v>5.47</v>
       </c>
       <c r="I170" t="n">
-        <v>4.7</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="J170" t="n">
-        <v>15</v>
-      </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>1.76, 4.00, 4.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>dom 08/11 11:30</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>Villarreal vs Getafe</t>
-        </is>
-      </c>
-      <c r="D171" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="E171" t="n">
-        <v>4.81</v>
-      </c>
-      <c r="F171" t="n">
-        <v>7.84</v>
-      </c>
-      <c r="G171" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="H171" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="I171" t="n">
-        <v>7.69</v>
-      </c>
-      <c r="J171" t="n">
-        <v>15</v>
-      </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>1.47, 4.37, 6.68</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>dom 08/11 12:30</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>TSG Hoffenheim vs FC Schalke 04</t>
-        </is>
-      </c>
-      <c r="D172" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="E172" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="F172" t="n">
-        <v>5.36</v>
-      </c>
-      <c r="G172" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="H172" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="I172" t="n">
-        <v>5.26</v>
-      </c>
-      <c r="J172" t="n">
-        <v>16</v>
-      </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t>1.62, 4.46, 4.63</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>dom 08/11 13:45</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>RC Lens vs Marseille</t>
-        </is>
-      </c>
-      <c r="D173" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="E173" t="n">
-        <v>4.32</v>
-      </c>
-      <c r="F173" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="G173" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="H173" t="n">
-        <v>4.24</v>
-      </c>
-      <c r="I173" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="J173" t="n">
-        <v>16</v>
-      </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>2.07, 3.91, 3.21</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>dom 08/11 14:00</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Atlético Madrid vs Barcelona</t>
-        </is>
-      </c>
-      <c r="D174" t="n">
-        <v>4</v>
-      </c>
-      <c r="E174" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="F174" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="G174" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="H174" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="I174" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J174" t="n">
-        <v>14</v>
-      </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t>3.80, 4.23, 1.81</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>jue 12/11 11:00</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Nations League</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Turkey vs Belgium</t>
-        </is>
-      </c>
-      <c r="D175" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="E175" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="F175" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="G175" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="H175" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="I175" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J175" t="n">
-        <v>9</v>
-      </c>
-      <c r="K175" t="inlineStr"/>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>jue 12/11 13:45</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Nations League</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>England vs Croatia</t>
-        </is>
-      </c>
-      <c r="D176" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E176" t="n">
-        <v>7.21</v>
-      </c>
-      <c r="F176" t="n">
-        <v>14.87</v>
-      </c>
-      <c r="G176" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="H176" t="n">
-        <v>7.06</v>
-      </c>
-      <c r="I176" t="n">
-        <v>14.58</v>
-      </c>
-      <c r="J176" t="n">
-        <v>9</v>
-      </c>
-      <c r="K176" t="inlineStr"/>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>jue 12/11 13:45</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>Nations League</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>Czech Republic vs Spain</t>
-        </is>
-      </c>
-      <c r="D177" t="n">
-        <v>52.74</v>
-      </c>
-      <c r="E177" t="n">
-        <v>9.85</v>
-      </c>
-      <c r="F177" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="G177" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="H177" t="n">
-        <v>9.66</v>
-      </c>
-      <c r="I177" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="J177" t="n">
-        <v>9</v>
-      </c>
-      <c r="K177" t="inlineStr"/>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>jue 12/11 13:45</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>Nations League</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Italy vs France</t>
-        </is>
-      </c>
-      <c r="D178" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="E178" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="F178" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="G178" t="n">
-        <v>4.24</v>
-      </c>
-      <c r="H178" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="I178" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="J178" t="n">
-        <v>9</v>
-      </c>
-      <c r="K178" t="inlineStr"/>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>vie 13/11 13:45</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Nations League</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Serbia vs Germany</t>
-        </is>
-      </c>
-      <c r="D179" t="n">
-        <v>12.04</v>
-      </c>
-      <c r="E179" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="F179" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="G179" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="H179" t="n">
-        <v>6.66</v>
-      </c>
-      <c r="I179" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="J179" t="n">
-        <v>9</v>
-      </c>
-      <c r="K179" t="inlineStr"/>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>vie 13/11 13:45</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Nations League</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>Netherlands vs Greece</t>
-        </is>
-      </c>
-      <c r="D180" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="E180" t="n">
-        <v>5.43</v>
-      </c>
-      <c r="F180" t="n">
-        <v>8.07</v>
-      </c>
-      <c r="G180" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="H180" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="I180" t="n">
-        <v>7.91</v>
-      </c>
-      <c r="J180" t="n">
-        <v>9</v>
-      </c>
-      <c r="K180" t="inlineStr"/>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>sáb 14/11 11:00</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>Nations League</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>Norway vs Wales</t>
-        </is>
-      </c>
-      <c r="D181" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E181" t="n">
-        <v>7.05</v>
-      </c>
-      <c r="F181" t="n">
-        <v>15.45</v>
-      </c>
-      <c r="G181" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="H181" t="n">
-        <v>6.91</v>
-      </c>
-      <c r="I181" t="n">
-        <v>15.14</v>
-      </c>
-      <c r="J181" t="n">
-        <v>9</v>
-      </c>
-      <c r="K181" t="inlineStr"/>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>sáb 14/11 13:45</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>Nations League</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Portugal vs Denmark</t>
-        </is>
-      </c>
-      <c r="D182" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="E182" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="F182" t="n">
-        <v>8.73</v>
-      </c>
-      <c r="G182" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="H182" t="n">
-        <v>5.44</v>
-      </c>
-      <c r="I182" t="n">
-        <v>8.550000000000001</v>
-      </c>
-      <c r="J182" t="n">
-        <v>9</v>
-      </c>
-      <c r="K182" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="K170" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
